--- a/src/attributions/attributions_saliency_traj_431.xlsx
+++ b/src/attributions/attributions_saliency_traj_431.xlsx
@@ -1568,1709 +1568,1709 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1.011876520351507e-06</v>
+        <v>0.07077882438898087</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0002511100610718131</v>
+        <v>0.3692451417446136</v>
       </c>
       <c r="C3" t="n">
-        <v>5.527026587515138e-05</v>
+        <v>0.05876513570547104</v>
       </c>
       <c r="D3" t="n">
-        <v>5.828854773426428e-05</v>
+        <v>0.03577808290719986</v>
       </c>
       <c r="E3" t="n">
-        <v>1.50739597302163e-05</v>
+        <v>0.1100008264183998</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000293624383630231</v>
+        <v>0.1670794486999512</v>
       </c>
       <c r="G3" t="n">
-        <v>1.271593282581307e-05</v>
+        <v>0.07029248774051666</v>
       </c>
       <c r="H3" t="n">
-        <v>7.995306077646092e-05</v>
+        <v>0.01880336552858353</v>
       </c>
       <c r="I3" t="n">
-        <v>3.11965704895556e-05</v>
+        <v>0.01410225499421358</v>
       </c>
       <c r="J3" t="n">
-        <v>5.610641528619453e-05</v>
+        <v>0.03988561034202576</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001778974401531741</v>
+        <v>0.4141021072864532</v>
       </c>
       <c r="L3" t="n">
-        <v>5.982065704301931e-05</v>
+        <v>0.08866786956787109</v>
       </c>
       <c r="M3" t="n">
-        <v>3.020120857399888e-05</v>
+        <v>0.05509673058986664</v>
       </c>
       <c r="N3" t="n">
-        <v>5.209786468185484e-05</v>
+        <v>0.1690515428781509</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001811717811506242</v>
+        <v>0.1519585996866226</v>
       </c>
       <c r="P3" t="n">
-        <v>5.199204679229297e-06</v>
+        <v>0.05897817015647888</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.727080522570759e-05</v>
+        <v>0.08876609057188034</v>
       </c>
       <c r="R3" t="n">
-        <v>1.003152920020511e-05</v>
+        <v>0.06998523324728012</v>
       </c>
       <c r="S3" t="n">
-        <v>2.466022124281153e-06</v>
+        <v>0.005256379954516888</v>
       </c>
       <c r="T3" t="n">
-        <v>1.161040700026206e-06</v>
+        <v>0.01930685341358185</v>
       </c>
       <c r="U3" t="n">
-        <v>4.022840585093945e-05</v>
+        <v>0.003057699650526047</v>
       </c>
       <c r="V3" t="n">
-        <v>3.973947968916036e-05</v>
+        <v>0.0635177418589592</v>
       </c>
       <c r="W3" t="n">
-        <v>4.918516788166016e-05</v>
+        <v>0.07749560475349426</v>
       </c>
       <c r="X3" t="n">
-        <v>3.328774982946925e-05</v>
+        <v>0.07393013685941696</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.312554690637626e-05</v>
+        <v>0.0225862693041563</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.616163353901356e-05</v>
+        <v>0.08421493321657181</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.780590173439123e-05</v>
+        <v>0.07333043217658997</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.204394619795494e-05</v>
+        <v>0.003511697985231876</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.401904319209279e-05</v>
+        <v>0.03658922761678696</v>
       </c>
       <c r="AD3" t="n">
-        <v>3.981869667768478e-05</v>
+        <v>0.0130022969096899</v>
       </c>
       <c r="AE3" t="n">
-        <v>4.967872519046068e-05</v>
+        <v>0.04473203420639038</v>
       </c>
       <c r="AF3" t="n">
-        <v>3.515363277983852e-05</v>
+        <v>0.08152791112661362</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.00259266118519e-05</v>
+        <v>0.01332129817456007</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.985292692552321e-05</v>
+        <v>0.01046539098024368</v>
       </c>
       <c r="AI3" t="n">
-        <v>2.171684718632605e-05</v>
+        <v>0.05973900109529495</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.453343040542677e-05</v>
+        <v>0.01285616401582956</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.418255760654574e-05</v>
+        <v>0.003914577420800924</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.072578172374051e-05</v>
+        <v>0.07855670154094696</v>
       </c>
       <c r="AM3" t="n">
-        <v>3.828790431725793e-05</v>
+        <v>0.03199850022792816</v>
       </c>
       <c r="AN3" t="n">
-        <v>4.22059019911103e-06</v>
+        <v>0.01938290521502495</v>
       </c>
       <c r="AO3" t="n">
-        <v>2.367853085161187e-05</v>
+        <v>0.113253079354763</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.786775677232072e-05</v>
+        <v>0.01843617670238018</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.451783075230196e-05</v>
+        <v>0.04470878839492798</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.398459698975785e-05</v>
+        <v>0.02180106192827225</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.148112253053114e-05</v>
+        <v>0.06564625352621078</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.732489338086452e-05</v>
+        <v>0.004838650114834309</v>
       </c>
       <c r="AU3" t="n">
-        <v>8.829925354802981e-05</v>
+        <v>0.2430246770381927</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.860755896312185e-05</v>
+        <v>0.01130390353500843</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.78041615174152e-05</v>
+        <v>0.02189663425087929</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0001100697918445803</v>
+        <v>0.07095453888177872</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0001928609854076058</v>
+        <v>0.02125142887234688</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.781348277698271e-05</v>
+        <v>0.01991774514317513</v>
       </c>
       <c r="BA3" t="n">
-        <v>8.462537152809091e-06</v>
+        <v>0.1013646349310875</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.571020690491423e-05</v>
+        <v>0.07728811353445053</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.111897578695789e-05</v>
+        <v>0.00491893058642745</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0001081301961676218</v>
+        <v>0.0603945404291153</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.521685696090572e-05</v>
+        <v>0.04994445294141769</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.308226147666574e-05</v>
+        <v>0.01097037643194199</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.281315341359004e-06</v>
+        <v>0.06565630435943604</v>
       </c>
       <c r="BH3" t="n">
-        <v>4.839640678255819e-05</v>
+        <v>0.02637920528650284</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.41806378653564e-06</v>
+        <v>0.1206421405076981</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1.706950206425972e-05</v>
+        <v>0.03460156172513962</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.190451803267933e-05</v>
+        <v>0.08308137208223343</v>
       </c>
       <c r="BL3" t="n">
-        <v>2.610658884805162e-05</v>
+        <v>0.007028551306575537</v>
       </c>
       <c r="BM3" t="n">
-        <v>2.446556754875928e-05</v>
+        <v>0.03319729119539261</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.203064236207865e-05</v>
+        <v>0.006786159705370665</v>
       </c>
       <c r="BO3" t="n">
-        <v>2.48259530053474e-05</v>
+        <v>0.05452026054263115</v>
       </c>
       <c r="BP3" t="n">
-        <v>2.558532651164569e-05</v>
+        <v>0.01617714576423168</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.629146936465986e-05</v>
+        <v>0.006696963682770729</v>
       </c>
       <c r="BR3" t="n">
-        <v>1.631403210922144e-05</v>
+        <v>0.07937233150005341</v>
       </c>
       <c r="BS3" t="n">
-        <v>6.415329698938876e-05</v>
+        <v>0.01251231785863638</v>
       </c>
       <c r="BT3" t="n">
-        <v>2.024776404141448e-05</v>
+        <v>0.005622525699436665</v>
       </c>
       <c r="BU3" t="n">
-        <v>2.684494938876014e-05</v>
+        <v>0.01266660168766975</v>
       </c>
       <c r="BV3" t="n">
-        <v>3.541835030773655e-05</v>
+        <v>0.1693683862686157</v>
       </c>
       <c r="BW3" t="n">
-        <v>3.376284075784497e-05</v>
+        <v>0.02836548909544945</v>
       </c>
       <c r="BX3" t="n">
-        <v>5.490480907610618e-05</v>
+        <v>0.007205326575785875</v>
       </c>
       <c r="BY3" t="n">
-        <v>6.42797676846385e-05</v>
+        <v>0.02856740541756153</v>
       </c>
       <c r="BZ3" t="n">
-        <v>8.293511928059161e-05</v>
+        <v>0.107335202395916</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.277787982369773e-05</v>
+        <v>0.01777065545320511</v>
       </c>
       <c r="CB3" t="n">
-        <v>1.106223680835683e-05</v>
+        <v>0.01026144344359636</v>
       </c>
       <c r="CC3" t="n">
-        <v>7.976949746080209e-06</v>
+        <v>0.06495568156242371</v>
       </c>
       <c r="CD3" t="n">
-        <v>1.384491042699665e-05</v>
+        <v>0.01589445024728775</v>
       </c>
       <c r="CE3" t="n">
-        <v>2.477279485901818e-05</v>
+        <v>0.1172879040241241</v>
       </c>
       <c r="CF3" t="n">
-        <v>1.131982207880355e-05</v>
+        <v>0.01592920906841755</v>
       </c>
       <c r="CG3" t="n">
-        <v>7.165986062318552e-06</v>
+        <v>0.007795743644237518</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.400370183546329e-05</v>
+        <v>0.006911042612046003</v>
       </c>
       <c r="CI3" t="n">
-        <v>4.379220627015457e-05</v>
+        <v>0.06930779665708542</v>
       </c>
       <c r="CJ3" t="n">
-        <v>3.007288569278899e-06</v>
+        <v>0.01014904957264662</v>
       </c>
       <c r="CK3" t="n">
-        <v>2.910528201027773e-05</v>
+        <v>0.01639920473098755</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.586472990311449e-06</v>
+        <v>0.01248365174978971</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.480500941397622e-06</v>
+        <v>0.06899433583021164</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.968444121303037e-05</v>
+        <v>0.1687807440757751</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.896073990792502e-05</v>
+        <v>0.05908629670739174</v>
       </c>
       <c r="CP3" t="n">
-        <v>5.717820022255182e-05</v>
+        <v>0.02393648028373718</v>
       </c>
       <c r="CQ3" t="n">
-        <v>6.208849663380533e-05</v>
+        <v>0.07873841375112534</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.496032382419799e-05</v>
+        <v>0.02999697625637054</v>
       </c>
       <c r="CS3" t="n">
-        <v>6.389000191120431e-07</v>
+        <v>0.04377502202987671</v>
       </c>
       <c r="CT3" t="n">
-        <v>4.109665678697638e-05</v>
+        <v>0.01487361546605825</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.113330927182687e-05</v>
+        <v>0.006300297565758228</v>
       </c>
       <c r="CV3" t="n">
-        <v>6.461127668444533e-07</v>
+        <v>0.008469042368233204</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.676387157407589e-05</v>
+        <v>0.1130349189043045</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.066926051862538e-05</v>
+        <v>0.01613852195441723</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.323248852713732e-06</v>
+        <v>0.01420734729617834</v>
       </c>
       <c r="CZ3" t="n">
-        <v>9.961695468518883e-07</v>
+        <v>0.02016272954642773</v>
       </c>
       <c r="DA3" t="n">
-        <v>4.597341467160732e-05</v>
+        <v>0.07380877435207367</v>
       </c>
       <c r="DB3" t="n">
-        <v>7.874034963606391e-06</v>
+        <v>0.01529313437640667</v>
       </c>
       <c r="DC3" t="n">
-        <v>3.870268483296968e-05</v>
+        <v>0.00576317124068737</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.153144123440143e-06</v>
+        <v>0.0001234367955476046</v>
       </c>
       <c r="DE3" t="n">
-        <v>4.494724998949096e-05</v>
+        <v>0.04546071961522102</v>
       </c>
       <c r="DF3" t="n">
-        <v>4.598901068675332e-05</v>
+        <v>0.0359581895172596</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.893913551815785e-05</v>
+        <v>0.01656671613454819</v>
       </c>
       <c r="DH3" t="n">
-        <v>6.3071318436414e-05</v>
+        <v>0.01476448774337769</v>
       </c>
       <c r="DI3" t="n">
-        <v>4.698442808148684e-06</v>
+        <v>0.02685902453958988</v>
       </c>
       <c r="DJ3" t="n">
-        <v>9.291506103181746e-06</v>
+        <v>0.03702764585614204</v>
       </c>
       <c r="DK3" t="n">
-        <v>1.731155316520017e-05</v>
+        <v>0.001015037298202515</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.0001312979875365272</v>
+        <v>0.001931584440171719</v>
       </c>
       <c r="DM3" t="n">
-        <v>2.450944703014102e-05</v>
+        <v>0.03073054179549217</v>
       </c>
       <c r="DN3" t="n">
-        <v>2.186629717471078e-05</v>
+        <v>0.02006484381854534</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.082502032862976e-05</v>
+        <v>0.07930002361536026</v>
       </c>
       <c r="DP3" t="n">
-        <v>5.400876034400426e-05</v>
+        <v>0.02375949174165726</v>
       </c>
       <c r="DQ3" t="n">
-        <v>1.6517769836355e-05</v>
+        <v>0.08627108484506607</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.241511098574847e-05</v>
+        <v>0.03035318851470947</v>
       </c>
       <c r="DS3" t="n">
-        <v>1.785432505130302e-05</v>
+        <v>0.02803309261798859</v>
       </c>
       <c r="DT3" t="n">
-        <v>1.290454747504555e-07</v>
+        <v>0.0186153594404459</v>
       </c>
       <c r="DU3" t="n">
-        <v>7.466673196176998e-06</v>
+        <v>0.04352949187159538</v>
       </c>
       <c r="DV3" t="n">
-        <v>8.929331670515239e-06</v>
+        <v>0.04471463337540627</v>
       </c>
       <c r="DW3" t="n">
-        <v>1.48622993947356e-05</v>
+        <v>0.002999984193593264</v>
       </c>
       <c r="DX3" t="n">
-        <v>1.594117566128261e-05</v>
+        <v>0.06735144555568695</v>
       </c>
       <c r="DY3" t="n">
-        <v>7.287251719390042e-06</v>
+        <v>0.006971966009587049</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.845571750891395e-05</v>
+        <v>0.05940711870789528</v>
       </c>
       <c r="EA3" t="n">
-        <v>4.830608304473571e-06</v>
+        <v>0.04161768034100533</v>
       </c>
       <c r="EB3" t="n">
-        <v>4.940280632581562e-05</v>
+        <v>0.1031328141689301</v>
       </c>
       <c r="EC3" t="n">
-        <v>7.212476248241728e-06</v>
+        <v>0.0006507313810288906</v>
       </c>
       <c r="ED3" t="n">
-        <v>4.078986603417434e-05</v>
+        <v>0.08913804590702057</v>
       </c>
       <c r="EE3" t="n">
-        <v>1.874305780802388e-06</v>
+        <v>0.01570016704499722</v>
       </c>
       <c r="EF3" t="n">
-        <v>1.084890391211957e-05</v>
+        <v>0.0255306102335453</v>
       </c>
       <c r="EG3" t="n">
-        <v>9.289272384194192e-06</v>
+        <v>0.07914631068706512</v>
       </c>
       <c r="EH3" t="n">
-        <v>2.12416925933212e-05</v>
+        <v>0.01043851859867573</v>
       </c>
       <c r="EI3" t="n">
-        <v>1.968108153960202e-05</v>
+        <v>0.167867511510849</v>
       </c>
       <c r="EJ3" t="n">
-        <v>4.824232746614143e-06</v>
+        <v>0.03042924404144287</v>
       </c>
       <c r="EK3" t="n">
-        <v>7.118987559806556e-05</v>
+        <v>0.06409907341003418</v>
       </c>
       <c r="EL3" t="n">
-        <v>7.805220775480848e-06</v>
+        <v>0.009088493883609772</v>
       </c>
       <c r="EM3" t="n">
-        <v>1.420216631231597e-05</v>
+        <v>0.01378461252897978</v>
       </c>
       <c r="EN3" t="n">
-        <v>6.993641818553442e-06</v>
+        <v>0.02359009347856045</v>
       </c>
       <c r="EO3" t="n">
-        <v>7.518551683460828e-07</v>
+        <v>0.01443284284323454</v>
       </c>
       <c r="EP3" t="n">
-        <v>2.05937321879901e-05</v>
+        <v>0.06418547034263611</v>
       </c>
       <c r="EQ3" t="n">
-        <v>2.433536064927466e-05</v>
+        <v>0.005057963542640209</v>
       </c>
       <c r="ER3" t="n">
-        <v>2.931747803813778e-05</v>
+        <v>0.05396338924765587</v>
       </c>
       <c r="ES3" t="n">
-        <v>4.076919867657125e-05</v>
+        <v>0.03572069853544235</v>
       </c>
       <c r="ET3" t="n">
-        <v>4.274068487575278e-05</v>
+        <v>0.02316110022366047</v>
       </c>
       <c r="EU3" t="n">
-        <v>6.288795702857897e-06</v>
+        <v>0.03159165009856224</v>
       </c>
       <c r="EV3" t="n">
-        <v>5.150189826963469e-05</v>
+        <v>0.05767400935292244</v>
       </c>
       <c r="EW3" t="n">
-        <v>5.518959369510412e-06</v>
+        <v>0.01502380147576332</v>
       </c>
       <c r="EX3" t="n">
-        <v>3.511185695970198e-06</v>
+        <v>0.01106900908052921</v>
       </c>
       <c r="EY3" t="n">
-        <v>2.258668610011227e-05</v>
+        <v>0.1238921955227852</v>
       </c>
       <c r="EZ3" t="n">
-        <v>5.871306711924262e-06</v>
+        <v>0.01618589460849762</v>
       </c>
       <c r="FA3" t="n">
-        <v>3.662448534669238e-06</v>
+        <v>0.002628224901854992</v>
       </c>
       <c r="FB3" t="n">
-        <v>7.916213689895812e-06</v>
+        <v>0.007470720447599888</v>
       </c>
       <c r="FC3" t="n">
-        <v>3.702265894389711e-05</v>
+        <v>0.0695604532957077</v>
       </c>
       <c r="FD3" t="n">
-        <v>5.024380243412452e-06</v>
+        <v>0.01592393778264523</v>
       </c>
       <c r="FE3" t="n">
-        <v>3.649205609690398e-05</v>
+        <v>0.008616004139184952</v>
       </c>
       <c r="FF3" t="n">
-        <v>2.419493284833152e-06</v>
+        <v>0.009060638956725597</v>
       </c>
       <c r="FG3" t="n">
-        <v>5.858032636751886e-06</v>
+        <v>0.01421594433486462</v>
       </c>
       <c r="FH3" t="n">
-        <v>3.793265932472423e-05</v>
+        <v>0.007586889900267124</v>
       </c>
       <c r="FI3" t="n">
-        <v>3.55269257852342e-05</v>
+        <v>0.00957842729985714</v>
       </c>
       <c r="FJ3" t="n">
-        <v>3.735306381713599e-05</v>
+        <v>0.009024587459862232</v>
       </c>
       <c r="FK3" t="n">
-        <v>1.047552086674841e-05</v>
+        <v>0.02825995907187462</v>
       </c>
       <c r="FL3" t="n">
-        <v>6.335942453006282e-05</v>
+        <v>0.02497685886919498</v>
       </c>
       <c r="FM3" t="n">
-        <v>1.771454117260873e-05</v>
+        <v>0.02536973729729652</v>
       </c>
       <c r="FN3" t="n">
-        <v>1.266246090381173e-05</v>
+        <v>0.0579054057598114</v>
       </c>
       <c r="FO3" t="n">
-        <v>2.449073144816794e-05</v>
+        <v>0.07910133898258209</v>
       </c>
       <c r="FP3" t="n">
-        <v>1.336581954092253e-05</v>
+        <v>0.05996642261743546</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.000111103116068989</v>
+        <v>0.1011224016547203</v>
       </c>
       <c r="FR3" t="n">
-        <v>1.749271541484632e-05</v>
+        <v>0.01834793575108051</v>
       </c>
       <c r="FS3" t="n">
-        <v>2.070629489026032e-05</v>
+        <v>0.05744893103837967</v>
       </c>
       <c r="FT3" t="n">
-        <v>7.747279596515e-06</v>
+        <v>0.08349435031414032</v>
       </c>
       <c r="FU3" t="n">
-        <v>5.144399619894102e-05</v>
+        <v>0.1722579598426819</v>
       </c>
       <c r="FV3" t="n">
-        <v>2.328142727492377e-06</v>
+        <v>0.1673979908227921</v>
       </c>
       <c r="FW3" t="n">
-        <v>1.41392411023844e-06</v>
+        <v>0.07296802848577499</v>
       </c>
       <c r="FX3" t="n">
-        <v>2.723013858485501e-05</v>
+        <v>0.03048693388700485</v>
       </c>
       <c r="FY3" t="n">
-        <v>2.807479904731736e-05</v>
+        <v>0.02279551886022091</v>
       </c>
       <c r="FZ3" t="n">
-        <v>1.003518445941154e-05</v>
+        <v>0.06683482229709625</v>
       </c>
       <c r="GA3" t="n">
-        <v>2.127417974406853e-05</v>
+        <v>0.005769411101937294</v>
       </c>
       <c r="GB3" t="n">
-        <v>1.096832056646235e-05</v>
+        <v>0.005741370841860771</v>
       </c>
       <c r="GC3" t="n">
-        <v>8.693657582625747e-05</v>
+        <v>0.02541691996157169</v>
       </c>
       <c r="GD3" t="n">
-        <v>2.551965008024126e-05</v>
+        <v>0.03502104431390762</v>
       </c>
       <c r="GE3" t="n">
-        <v>3.233673487557098e-05</v>
+        <v>0.07900805771350861</v>
       </c>
       <c r="GF3" t="n">
-        <v>2.312106880708598e-05</v>
+        <v>0.02507907338440418</v>
       </c>
       <c r="GG3" t="n">
-        <v>2.514634434191976e-05</v>
+        <v>0.008835239335894585</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2.273508187267126e-10</v>
+        <v>0.003648868761956692</v>
       </c>
       <c r="B4" t="n">
-        <v>2.637219609358255e-10</v>
+        <v>0.002080798614770174</v>
       </c>
       <c r="C4" t="n">
-        <v>2.378370000943875e-10</v>
+        <v>0.009603753685951233</v>
       </c>
       <c r="D4" t="n">
-        <v>1.524349535486635e-10</v>
+        <v>0.008087006397545338</v>
       </c>
       <c r="E4" t="n">
-        <v>5.01246211204176e-10</v>
+        <v>0.003568595508113503</v>
       </c>
       <c r="F4" t="n">
-        <v>1.437918895064172e-09</v>
+        <v>0.01240694895386696</v>
       </c>
       <c r="G4" t="n">
-        <v>2.234214202534446e-11</v>
+        <v>0.001893246895633638</v>
       </c>
       <c r="H4" t="n">
-        <v>1.021665863021326e-09</v>
+        <v>0.01490754634141922</v>
       </c>
       <c r="I4" t="n">
-        <v>6.498514226738195e-11</v>
+        <v>0.003139604348689318</v>
       </c>
       <c r="J4" t="n">
-        <v>3.424258099293809e-11</v>
+        <v>0.001543358783237636</v>
       </c>
       <c r="K4" t="n">
-        <v>3.429379280550648e-10</v>
+        <v>0.007150862831622362</v>
       </c>
       <c r="L4" t="n">
-        <v>5.041045358922247e-11</v>
+        <v>0.0009686111006885767</v>
       </c>
       <c r="M4" t="n">
-        <v>3.647285806707146e-10</v>
+        <v>0.01165937911719084</v>
       </c>
       <c r="N4" t="n">
-        <v>2.844757485132021e-10</v>
+        <v>0.007123663555830717</v>
       </c>
       <c r="O4" t="n">
-        <v>1.012275041567534e-09</v>
+        <v>0.01943747885525227</v>
       </c>
       <c r="P4" t="n">
-        <v>2.333830351197719e-10</v>
+        <v>0.002430172637104988</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.570280123938346e-10</v>
+        <v>0.009416718035936356</v>
       </c>
       <c r="R4" t="n">
-        <v>1.986539405196552e-11</v>
+        <v>0.004060419742017984</v>
       </c>
       <c r="S4" t="n">
-        <v>1.72220127048206e-10</v>
+        <v>0.003585205180570483</v>
       </c>
       <c r="T4" t="n">
-        <v>1.053724468791373e-10</v>
+        <v>0.0008872945327311754</v>
       </c>
       <c r="U4" t="n">
-        <v>1.54850285372099e-10</v>
+        <v>0.004123636987060308</v>
       </c>
       <c r="V4" t="n">
-        <v>2.412843813637267e-10</v>
+        <v>0.0107222655788064</v>
       </c>
       <c r="W4" t="n">
-        <v>3.801899350897031e-10</v>
+        <v>0.004251861479133368</v>
       </c>
       <c r="X4" t="n">
-        <v>4.470537828815679e-10</v>
+        <v>0.005593341775238514</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.863384332036262e-11</v>
+        <v>0.002890274859964848</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.71305089505347e-10</v>
+        <v>0.001385255251079798</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.116719879020962e-11</v>
+        <v>0.0007619221578352153</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.291458967018656e-10</v>
+        <v>0.002535652369260788</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.893342683496503e-11</v>
+        <v>0.001050597755238414</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.404553695572019e-10</v>
+        <v>0.004144832491874695</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.980196367463606e-10</v>
+        <v>0.007049621548503637</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.74687134149687e-10</v>
+        <v>0.006852017249912024</v>
       </c>
       <c r="AG4" t="n">
-        <v>7.40533953602629e-11</v>
+        <v>0.001154715777374804</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.869703086272324e-11</v>
+        <v>0.005138227250427008</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.493734441693206e-10</v>
+        <v>0.002270033583045006</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.118961520663042e-11</v>
+        <v>0.0008938300888985395</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.246343861449617e-10</v>
+        <v>0.004969072062522173</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.635759305784745e-10</v>
+        <v>0.001419095788151026</v>
       </c>
       <c r="AM4" t="n">
-        <v>4.26982477153004e-11</v>
+        <v>0.005321759264916182</v>
       </c>
       <c r="AN4" t="n">
-        <v>3.239346291206147e-12</v>
+        <v>0.0007520769722759724</v>
       </c>
       <c r="AO4" t="n">
-        <v>2.243774332999493e-10</v>
+        <v>0.0009651331347413361</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.993368968835398e-10</v>
+        <v>0.003348259720951319</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9.014950591579307e-11</v>
+        <v>0.00378177291713655</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.358350486066698e-12</v>
+        <v>0.004884714260697365</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.441694901822444e-10</v>
+        <v>0.003871932392939925</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.474540596521308e-11</v>
+        <v>0.01396412495523691</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.643197965530476e-10</v>
+        <v>0.01239921059459448</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.433425488363895e-10</v>
+        <v>0.01207821816205978</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.148841742905972e-10</v>
+        <v>0.005886157974600792</v>
       </c>
       <c r="AX4" t="n">
-        <v>9.016571933528894e-10</v>
+        <v>0.003423034679144621</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.125516790878578e-09</v>
+        <v>0.01846959814429283</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.398651136192314e-11</v>
+        <v>0.009127222001552582</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.88221077612738e-10</v>
+        <v>0.007220241241157055</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.70636760066634e-10</v>
+        <v>0.001241096993908286</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.197767883822422e-10</v>
+        <v>0.01060628425329924</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.142293898359625e-10</v>
+        <v>0.01067537721246481</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8899878857831e-11</v>
+        <v>0.000840868684463203</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.080033255693394e-10</v>
+        <v>0.009380715899169445</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.691344980736531e-10</v>
+        <v>0.01754601486027241</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.412831046072483e-10</v>
+        <v>0.003844300983473659</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.180664676609823e-10</v>
+        <v>0.002128244144842029</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3.514041002627977e-10</v>
+        <v>0.005361234303563833</v>
       </c>
       <c r="BK4" t="n">
-        <v>3.308948948177459e-10</v>
+        <v>0.001353773172013462</v>
       </c>
       <c r="BL4" t="n">
-        <v>1.653548270530436e-10</v>
+        <v>0.001396176056005061</v>
       </c>
       <c r="BM4" t="n">
-        <v>3.822229199812455e-10</v>
+        <v>0.0006361810956150293</v>
       </c>
       <c r="BN4" t="n">
-        <v>7.101040588874952e-11</v>
+        <v>0.004740242846310139</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.252149495201138e-10</v>
+        <v>9.025534382089972e-05</v>
       </c>
       <c r="BP4" t="n">
-        <v>2.267287607660151e-10</v>
+        <v>0.002032120013609529</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.177250543361936e-12</v>
+        <v>0.003004058497026563</v>
       </c>
       <c r="BR4" t="n">
-        <v>1.81928014320043e-10</v>
+        <v>0.001330715138465166</v>
       </c>
       <c r="BS4" t="n">
-        <v>3.753746480317233e-10</v>
+        <v>0.004608788527548313</v>
       </c>
       <c r="BT4" t="n">
-        <v>2.585145292277602e-11</v>
+        <v>0.002782580675557256</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.312688830527712e-11</v>
+        <v>0.00590981962159276</v>
       </c>
       <c r="BV4" t="n">
-        <v>9.474239448525879e-11</v>
+        <v>0.001291032298468053</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.016013939647564e-10</v>
+        <v>0.00549458060413599</v>
       </c>
       <c r="BX4" t="n">
-        <v>1.332696730749205e-10</v>
+        <v>0.008582633920013905</v>
       </c>
       <c r="BY4" t="n">
-        <v>7.048377992369126e-10</v>
+        <v>0.007532007060945034</v>
       </c>
       <c r="BZ4" t="n">
-        <v>7.782098299102813e-10</v>
+        <v>0.007835700176656246</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.168216738622885e-11</v>
+        <v>0.008734849281609058</v>
       </c>
       <c r="CB4" t="n">
-        <v>2.603712523363555e-10</v>
+        <v>0.008389173075556755</v>
       </c>
       <c r="CC4" t="n">
-        <v>1.12568086796383e-10</v>
+        <v>0.001851739245466888</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.034093206371157e-11</v>
+        <v>0.001999478554353118</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.810731703466573e-10</v>
+        <v>0.002486431039869785</v>
       </c>
       <c r="CF4" t="n">
-        <v>1.108516230197143e-11</v>
+        <v>0.004824363626539707</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.71969356757662e-11</v>
+        <v>0.0006020912551321089</v>
       </c>
       <c r="CH4" t="n">
-        <v>5.567799693517728e-12</v>
+        <v>0.001265076221898198</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.391860043360339e-10</v>
+        <v>0.002653436036780477</v>
       </c>
       <c r="CJ4" t="n">
-        <v>5.891130638868702e-11</v>
+        <v>0.002709269756451249</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.495344958968303e-10</v>
+        <v>0.004339725710451603</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.694085496883879e-11</v>
+        <v>0.0004992400063201785</v>
       </c>
       <c r="CM4" t="n">
-        <v>4.16504677969165e-11</v>
+        <v>0.000750249600969255</v>
       </c>
       <c r="CN4" t="n">
-        <v>3.256253600092407e-10</v>
+        <v>0.0003248716238886118</v>
       </c>
       <c r="CO4" t="n">
-        <v>3.536423584526993e-11</v>
+        <v>0.01701680943369865</v>
       </c>
       <c r="CP4" t="n">
-        <v>5.617826204229459e-10</v>
+        <v>0.001931746257469058</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.968600170711767e-10</v>
+        <v>0.008452919311821461</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.542571903545564e-10</v>
+        <v>0.0009037955896928906</v>
       </c>
       <c r="CS4" t="n">
-        <v>4.208940834748987e-11</v>
+        <v>0.007849683053791523</v>
       </c>
       <c r="CT4" t="n">
-        <v>4.873387804416041e-11</v>
+        <v>0.01035015005618334</v>
       </c>
       <c r="CU4" t="n">
-        <v>2.528944276214418e-10</v>
+        <v>0.004226538352668285</v>
       </c>
       <c r="CV4" t="n">
-        <v>6.856662460030805e-11</v>
+        <v>0.002714336849749088</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.850548048132339e-10</v>
+        <v>0.001107523799873888</v>
       </c>
       <c r="CX4" t="n">
-        <v>8.831940387366011e-12</v>
+        <v>0.002242185873910785</v>
       </c>
       <c r="CY4" t="n">
-        <v>4.479593779249669e-13</v>
+        <v>0.0003175414749421179</v>
       </c>
       <c r="CZ4" t="n">
-        <v>6.007039310418349e-11</v>
+        <v>0.001961414702236652</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.913636554247034e-10</v>
+        <v>0.00454053794965148</v>
       </c>
       <c r="DB4" t="n">
-        <v>5.479572698363633e-11</v>
+        <v>0.001261845929548144</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.528881548613526e-10</v>
+        <v>0.004635676275938749</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.854421114559472e-11</v>
+        <v>0.0003905899357050657</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.883212752407104e-10</v>
+        <v>0.002300121355801821</v>
       </c>
       <c r="DF4" t="n">
-        <v>4.04796057784651e-11</v>
+        <v>0.007083763834089041</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.915124808211544e-10</v>
+        <v>0.006730579771101475</v>
       </c>
       <c r="DH4" t="n">
-        <v>4.923634278064526e-10</v>
+        <v>0.0003382374998182058</v>
       </c>
       <c r="DI4" t="n">
-        <v>1.695644180621514e-10</v>
+        <v>0.004563993774354458</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.413335364881419e-10</v>
+        <v>0.002911036368459463</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.246456394325527e-11</v>
+        <v>0.005787066649645567</v>
       </c>
       <c r="DL4" t="n">
-        <v>2.136071181046972e-10</v>
+        <v>0.004232439678162336</v>
       </c>
       <c r="DM4" t="n">
-        <v>1.349123035510047e-10</v>
+        <v>0.0005776727921329439</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.386652875856598e-10</v>
+        <v>0.003551271511241794</v>
       </c>
       <c r="DO4" t="n">
-        <v>9.201119033352967e-11</v>
+        <v>0.0003826748579740524</v>
       </c>
       <c r="DP4" t="n">
-        <v>1.475539829209893e-10</v>
+        <v>0.00885518454015255</v>
       </c>
       <c r="DQ4" t="n">
-        <v>5.31904346956491e-11</v>
+        <v>0.006589668337255716</v>
       </c>
       <c r="DR4" t="n">
-        <v>1.948627370573774e-11</v>
+        <v>0.005843108519911766</v>
       </c>
       <c r="DS4" t="n">
-        <v>9.460414396311734e-11</v>
+        <v>0.006852423306554556</v>
       </c>
       <c r="DT4" t="n">
-        <v>1.762137311067669e-11</v>
+        <v>0.002525141928344965</v>
       </c>
       <c r="DU4" t="n">
-        <v>2.008934962827169e-10</v>
+        <v>0.0005981017602607608</v>
       </c>
       <c r="DV4" t="n">
-        <v>2.174983804170694e-11</v>
+        <v>0.00120065116789192</v>
       </c>
       <c r="DW4" t="n">
-        <v>1.341521060904682e-10</v>
+        <v>0.002885563066229224</v>
       </c>
       <c r="DX4" t="n">
-        <v>2.094650668194031e-11</v>
+        <v>0.00101291760802269</v>
       </c>
       <c r="DY4" t="n">
-        <v>3.134057735554308e-10</v>
+        <v>0.004676522687077522</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1.923357306754525e-12</v>
+        <v>0.004136119969189167</v>
       </c>
       <c r="EA4" t="n">
-        <v>9.360259095592127e-11</v>
+        <v>0.002661665668711066</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.498147994549726e-10</v>
+        <v>0.009076807647943497</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.694456463503414e-11</v>
+        <v>0.004014573525637388</v>
       </c>
       <c r="ED4" t="n">
-        <v>1.266011878664486e-10</v>
+        <v>0.007118881214410067</v>
       </c>
       <c r="EE4" t="n">
-        <v>4.651258891930077e-11</v>
+        <v>0.00605828920379281</v>
       </c>
       <c r="EF4" t="n">
-        <v>3.875566881306192e-11</v>
+        <v>0.0008711627451702952</v>
       </c>
       <c r="EG4" t="n">
-        <v>2.098664575456155e-10</v>
+        <v>0.005163305439054966</v>
       </c>
       <c r="EH4" t="n">
-        <v>3.888019420306144e-11</v>
+        <v>0.001999370753765106</v>
       </c>
       <c r="EI4" t="n">
-        <v>1.806971239304289e-10</v>
+        <v>5.216003046371043e-05</v>
       </c>
       <c r="EJ4" t="n">
-        <v>1.429940194030976e-10</v>
+        <v>0.002004755195230246</v>
       </c>
       <c r="EK4" t="n">
-        <v>9.716199372844514e-11</v>
+        <v>0.002803870011121035</v>
       </c>
       <c r="EL4" t="n">
-        <v>4.53280191159422e-11</v>
+        <v>0.0002272387791890651</v>
       </c>
       <c r="EM4" t="n">
-        <v>3.796794476040866e-11</v>
+        <v>0.004788008984178305</v>
       </c>
       <c r="EN4" t="n">
-        <v>1.046198544463195e-10</v>
+        <v>0.0007258819532580674</v>
       </c>
       <c r="EO4" t="n">
-        <v>2.280646504981831e-10</v>
+        <v>0.002742491429671645</v>
       </c>
       <c r="EP4" t="n">
-        <v>2.751173594495171e-11</v>
+        <v>0.003304002806544304</v>
       </c>
       <c r="EQ4" t="n">
-        <v>2.969523238416372e-11</v>
+        <v>0.002064818516373634</v>
       </c>
       <c r="ER4" t="n">
-        <v>5.013374090867551e-11</v>
+        <v>0.003578638192266226</v>
       </c>
       <c r="ES4" t="n">
-        <v>1.090038059814447e-10</v>
+        <v>0.001591646112501621</v>
       </c>
       <c r="ET4" t="n">
-        <v>2.00578220699299e-10</v>
+        <v>0.009165780618786812</v>
       </c>
       <c r="EU4" t="n">
-        <v>1.002442434616668e-10</v>
+        <v>0.002780397888273001</v>
       </c>
       <c r="EV4" t="n">
-        <v>2.531217457857338e-10</v>
+        <v>0.005284006241708994</v>
       </c>
       <c r="EW4" t="n">
-        <v>1.553634998430198e-11</v>
+        <v>0.001863772631622851</v>
       </c>
       <c r="EX4" t="n">
-        <v>6.219782328065193e-11</v>
+        <v>0.002759959548711777</v>
       </c>
       <c r="EY4" t="n">
-        <v>1.620522466216912e-10</v>
+        <v>0.001846709055826068</v>
       </c>
       <c r="EZ4" t="n">
-        <v>6.199972479858928e-11</v>
+        <v>0.001775801414623857</v>
       </c>
       <c r="FA4" t="n">
-        <v>1.328028659264291e-11</v>
+        <v>0.000834847625810653</v>
       </c>
       <c r="FB4" t="n">
-        <v>9.746922019493454e-12</v>
+        <v>0.000388832064345479</v>
       </c>
       <c r="FC4" t="n">
-        <v>2.365771467616185e-10</v>
+        <v>0.002926647197455168</v>
       </c>
       <c r="FD4" t="n">
-        <v>1.919520965787402e-12</v>
+        <v>0.002166996710002422</v>
       </c>
       <c r="FE4" t="n">
-        <v>2.621399486368858e-10</v>
+        <v>0.00440572714433074</v>
       </c>
       <c r="FF4" t="n">
-        <v>8.897151765330236e-11</v>
+        <v>6.344428402371705e-05</v>
       </c>
       <c r="FG4" t="n">
-        <v>8.843636239985742e-11</v>
+        <v>0.001490767812356353</v>
       </c>
       <c r="FH4" t="n">
-        <v>1.885180345162496e-10</v>
+        <v>0.002232111990451813</v>
       </c>
       <c r="FI4" t="n">
-        <v>2.690504208313627e-10</v>
+        <v>0.002964808139950037</v>
       </c>
       <c r="FJ4" t="n">
-        <v>1.075939823347305e-10</v>
+        <v>0.003980592358857393</v>
       </c>
       <c r="FK4" t="n">
-        <v>2.869755266754481e-10</v>
+        <v>0.001616246532648802</v>
       </c>
       <c r="FL4" t="n">
-        <v>3.831742700910468e-10</v>
+        <v>0.0002843552792910486</v>
       </c>
       <c r="FM4" t="n">
-        <v>1.041857572436911e-12</v>
+        <v>0.002344794338569045</v>
       </c>
       <c r="FN4" t="n">
-        <v>1.448733633058197e-10</v>
+        <v>0.01055166963487864</v>
       </c>
       <c r="FO4" t="n">
-        <v>8.74304517672897e-11</v>
+        <v>0.008553836494684219</v>
       </c>
       <c r="FP4" t="n">
-        <v>1.422106876702856e-11</v>
+        <v>0.009833669289946556</v>
       </c>
       <c r="FQ4" t="n">
-        <v>4.548074694632476e-10</v>
+        <v>0.007563996128737926</v>
       </c>
       <c r="FR4" t="n">
-        <v>8.157124281593653e-12</v>
+        <v>0.006608310155570507</v>
       </c>
       <c r="FS4" t="n">
-        <v>2.482835048667198e-10</v>
+        <v>0.01114525180310011</v>
       </c>
       <c r="FT4" t="n">
-        <v>3.230818113042488e-10</v>
+        <v>0.004186667501926422</v>
       </c>
       <c r="FU4" t="n">
-        <v>3.622684097148721e-10</v>
+        <v>0.009780889376997948</v>
       </c>
       <c r="FV4" t="n">
-        <v>7.048270994625128e-11</v>
+        <v>0.01126016397029161</v>
       </c>
       <c r="FW4" t="n">
-        <v>1.520565617862957e-10</v>
+        <v>0.01349346060305834</v>
       </c>
       <c r="FX4" t="n">
-        <v>8.065147161229191e-11</v>
+        <v>0.005425112321972847</v>
       </c>
       <c r="FY4" t="n">
-        <v>4.954200244489115e-12</v>
+        <v>0.001259999698959291</v>
       </c>
       <c r="FZ4" t="n">
-        <v>1.878900368623704e-10</v>
+        <v>0.0002177194692194462</v>
       </c>
       <c r="GA4" t="n">
-        <v>5.711017422860287e-11</v>
+        <v>0.001821312122046947</v>
       </c>
       <c r="GB4" t="n">
-        <v>3.132548109796573e-10</v>
+        <v>0.004595833364874125</v>
       </c>
       <c r="GC4" t="n">
-        <v>4.862473756972463e-10</v>
+        <v>0.002655522199347615</v>
       </c>
       <c r="GD4" t="n">
-        <v>4.069829195874064e-11</v>
+        <v>0.002396417781710625</v>
       </c>
       <c r="GE4" t="n">
-        <v>3.024664130268917e-10</v>
+        <v>0.006625412963330746</v>
       </c>
       <c r="GF4" t="n">
-        <v>8.407395613030388e-11</v>
+        <v>0.002670079935342073</v>
       </c>
       <c r="GG4" t="n">
-        <v>7.592847878212794e-11</v>
+        <v>0.0009364832658320665</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.003612342989072204</v>
+        <v>1.39736439450644e-05</v>
       </c>
       <c r="B5" t="n">
-        <v>0.001840982236899436</v>
+        <v>1.329296355834231e-05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00399397499859333</v>
+        <v>0.0003652314771898091</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005461623892188072</v>
+        <v>0.0007288003107532859</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0008948013419285417</v>
+        <v>0.0001335575943812728</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000941765436436981</v>
+        <v>7.181870023487136e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001582265249453485</v>
+        <v>0.0002407538268016651</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002175670117139816</v>
+        <v>1.821849946281873e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0003829143824987113</v>
+        <v>6.058294093236327e-05</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004935326986014843</v>
+        <v>1.921236253110692e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002295063575729728</v>
+        <v>9.84707148745656e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002985646715387702</v>
+        <v>0.000279089726973325</v>
       </c>
       <c r="M5" t="n">
-        <v>0.005411553662270308</v>
+        <v>0.0007723356829956174</v>
       </c>
       <c r="N5" t="n">
-        <v>0.002603028435260057</v>
+        <v>5.673329724231735e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0003677151398733258</v>
+        <v>8.329858974320814e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001845266902819276</v>
+        <v>9.302693069912493e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002432157285511494</v>
+        <v>0.0002569353382568806</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001416730927303433</v>
+        <v>0.0001465626846766099</v>
       </c>
       <c r="S5" t="n">
-        <v>0.001602310803718865</v>
+        <v>7.935611210996285e-05</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0003577343886718154</v>
+        <v>8.692251140018925e-05</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001349475205643103</v>
+        <v>6.973309064051136e-05</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0003535111609380692</v>
+        <v>0.0001525999541627243</v>
       </c>
       <c r="W5" t="n">
-        <v>0.002544644987210631</v>
+        <v>4.306421396904625e-05</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003779677499551326</v>
+        <v>0.0003109871177002788</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0002785962133202702</v>
+        <v>8.204911864595488e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.003470602445304394</v>
+        <v>1.365202388114994e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0001365561329293996</v>
+        <v>3.900046795024537e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0002946184540633112</v>
+        <v>9.678435162641108e-05</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.001411896664649248</v>
+        <v>4.031874050269835e-05</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.000113229158159811</v>
+        <v>0.0001239826815435663</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0005054940702393651</v>
+        <v>0.000261260662227869</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.0001502459490438923</v>
+        <v>0.0001787903602235019</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0003644372918643057</v>
+        <v>7.894579175626859e-05</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0005778743652626872</v>
+        <v>0.0001735343248583376</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0008810579311102629</v>
+        <v>0.0001936350163305178</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0004095965996384621</v>
+        <v>0.0001548951986478642</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0002051341580227017</v>
+        <v>0.0001299168798141181</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.001077129156328738</v>
+        <v>1.917671397677623e-06</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.0001730679941829294</v>
+        <v>6.610847776755691e-05</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.000604055414441973</v>
+        <v>0.0003004718746524304</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.000246436073211953</v>
+        <v>0.000136550675961189</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.0003396242391318083</v>
+        <v>5.089119076728821e-05</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0009131194092333317</v>
+        <v>0.000131063352455385</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0002842878457158804</v>
+        <v>9.027649866766296e-06</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.0001926019467646256</v>
+        <v>5.620822412311099e-05</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0002090171910822392</v>
+        <v>5.871207758900709e-05</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.00153340573888272</v>
+        <v>0.000132826084154658</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.002633955096825957</v>
+        <v>0.0004255469830241054</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.004518758971244097</v>
+        <v>0.0005453495541587472</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.0003065929922740906</v>
+        <v>0.0002736156166065484</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.001108634984120727</v>
+        <v>0.0001421230554115027</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.0006841336726211011</v>
+        <v>0.000153690023580566</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.002505290089175105</v>
+        <v>8.653730037622154e-05</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.001044144970364869</v>
+        <v>0.0001211445196531713</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.004639721009880304</v>
+        <v>0.0001184699794976041</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.001492271665483713</v>
+        <v>4.084530883119442e-05</v>
       </c>
       <c r="BE5" t="n">
-        <v>8.521636482328176e-05</v>
+        <v>6.731352186761796e-05</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0009702524403110147</v>
+        <v>0.0002572322264313698</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.003328041639178991</v>
+        <v>0.0002421893586870283</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0005362302181310952</v>
+        <v>0.0001965823757927865</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.002840403001755476</v>
+        <v>9.231167496182024e-05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.004918910562992096</v>
+        <v>5.683923154720105e-05</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0002785791293717921</v>
+        <v>0.0001759614096954465</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0008470146567560732</v>
+        <v>9.980090544559062e-05</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.00102606660220772</v>
+        <v>2.279283944517374e-05</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.001486157882027328</v>
+        <v>7.433576229232131e-06</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.001037088688462973</v>
+        <v>7.824753993190825e-06</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.002214370062574744</v>
+        <v>0.0001344982883892953</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0005643414915539324</v>
+        <v>0.0001252540678251535</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.001428563380613923</v>
+        <v>8.831943705445156e-05</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.0007353530381806195</v>
+        <v>1.642567076487467e-05</v>
       </c>
       <c r="BT5" t="n">
-        <v>0.0008292952552437782</v>
+        <v>1.667001197347417e-05</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0005117499968037009</v>
+        <v>9.313089321949519e-06</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.001539550023153424</v>
+        <v>4.229673504596576e-05</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.001109508564695716</v>
+        <v>0.0001863801007857546</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.002036664867773652</v>
+        <v>0.0003517554432619363</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.001024712924845517</v>
+        <v>9.436353866476566e-05</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.176728230551817e-05</v>
+        <v>0.0001534219190943986</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.00103622511960566</v>
+        <v>0.0001081882510334253</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.003783388761803508</v>
+        <v>9.448587661609054e-06</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.001517244148999453</v>
+        <v>6.516882422147319e-05</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.0008127366891130805</v>
+        <v>4.619693208951503e-05</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0009006640175357461</v>
+        <v>7.675216329516843e-05</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0009212256991304457</v>
+        <v>6.641507934546098e-05</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.00113995629362762</v>
+        <v>0.0001652144710533321</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.0006857533007860184</v>
+        <v>1.165053072327282e-05</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.0005412035970948637</v>
+        <v>2.921072336903308e-05</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.000559788488317281</v>
+        <v>4.473012813832611e-05</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0008566770702600479</v>
+        <v>6.087112706154585e-05</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0007677740650251508</v>
+        <v>3.001808545377571e-05</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.002170360647141933</v>
+        <v>4.991645710106241e-07</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.0007884387159720063</v>
+        <v>5.599616633844562e-05</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.0002554228994995356</v>
+        <v>3.40491023962386e-05</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.001128375064581633</v>
+        <v>9.254721226170659e-05</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.0008138670236803591</v>
+        <v>0.0003343071148265153</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0007435812149196863</v>
+        <v>4.353719850769266e-05</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.0004078431229572743</v>
+        <v>0.0001617189700482413</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.0008601672016084194</v>
+        <v>6.06509784120135e-05</v>
       </c>
       <c r="CU5" t="n">
-        <v>0.001019747345708311</v>
+        <v>0.0001816768053686246</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0007569427834823728</v>
+        <v>5.913423228776082e-05</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0005188635550439358</v>
+        <v>1.934840474859811e-05</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0003799686674028635</v>
+        <v>7.588564039906487e-05</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0008145645260810852</v>
+        <v>0.0002002062101382762</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0005587047198787332</v>
+        <v>1.355704989691731e-05</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0004362317849881947</v>
+        <v>6.035344995325431e-05</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0001106274430640042</v>
+        <v>4.723179881693795e-05</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0006998652825132012</v>
+        <v>7.654268119949847e-05</v>
       </c>
       <c r="DD5" t="n">
-        <v>0.0009722859249450266</v>
+        <v>6.680222668364877e-06</v>
       </c>
       <c r="DE5" t="n">
-        <v>4.687381442636251e-05</v>
+        <v>0.0001201711929752491</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.004201879259198904</v>
+        <v>0.0001248156186193228</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0008913470082916319</v>
+        <v>0.0003682247188407928</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.001936646411195397</v>
+        <v>0.0002396642521489412</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.001382234506309032</v>
+        <v>0.0001736909907776862</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.003412523306906223</v>
+        <v>5.003461410524324e-05</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.003782617626711726</v>
+        <v>8.384515240322798e-06</v>
       </c>
       <c r="DL5" t="n">
-        <v>2.828688593581319e-06</v>
+        <v>0.000422750017605722</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0009106856305152178</v>
+        <v>8.265387805295177e-06</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0001926503027789295</v>
+        <v>7.805526547599584e-05</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0005699479952454567</v>
+        <v>3.139894033665769e-08</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.001053008018061519</v>
+        <v>4.446921229828149e-05</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0001003772849799134</v>
+        <v>0.000140523916343227</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.001725738286040723</v>
+        <v>0.0001010849009617232</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.000219051114981994</v>
+        <v>2.4163477064576e-05</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.0007735998369753361</v>
+        <v>4.121781967114657e-05</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0006588787073269486</v>
+        <v>1.707483897916973e-05</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0008912214543670416</v>
+        <v>0.0002440393582219258</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0003862731682602316</v>
+        <v>8.29761047498323e-05</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.0001541816891403869</v>
+        <v>6.572118581971154e-05</v>
       </c>
       <c r="DY5" t="n">
-        <v>0.0007659962284378707</v>
+        <v>1.2821985365008e-05</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0008790125139057636</v>
+        <v>0.0001192568015540019</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.0001819617173168808</v>
+        <v>1.496437835157849e-05</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.002364482032135129</v>
+        <v>0.0002654139534570277</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0002041210245806724</v>
+        <v>8.524658187525347e-05</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.001356647815555334</v>
+        <v>0.0002105740422848612</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.001439508399926126</v>
+        <v>0.0001256498071597889</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0007569307927042246</v>
+        <v>6.857980770291761e-05</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.00040996796451509</v>
+        <v>3.066179488087073e-06</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.001001246157102287</v>
+        <v>5.149481148691848e-05</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.001540538971312344</v>
+        <v>0.0001643685827730224</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.0001831853296607733</v>
+        <v>0.0001019392220769078</v>
       </c>
       <c r="EK5" t="n">
-        <v>2.108910848619416e-05</v>
+        <v>3.621371070039459e-05</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0003835102543234825</v>
+        <v>2.837162537616678e-05</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.000826245523057878</v>
+        <v>6.554482388310134e-05</v>
       </c>
       <c r="EN5" t="n">
-        <v>0.001333388616330922</v>
+        <v>3.681275120470673e-05</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0006641207728534937</v>
+        <v>3.920853851013817e-05</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0002024931600317359</v>
+        <v>0.0001225039450218901</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.001117983018048108</v>
+        <v>1.823949060053565e-05</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0007326772902160883</v>
+        <v>0.0001451524440199137</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0002552925725467503</v>
+        <v>1.132286524807569e-05</v>
       </c>
       <c r="ET5" t="n">
-        <v>3.744874993572012e-05</v>
+        <v>0.0002265158836962655</v>
       </c>
       <c r="EU5" t="n">
-        <v>7.920827192720026e-05</v>
+        <v>0.0001708569034235552</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.00312290689907968</v>
+        <v>2.804468385875225e-05</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0009772460907697678</v>
+        <v>0.0001491803559474647</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0006501569878309965</v>
+        <v>5.028382292948663e-05</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0006732683395966887</v>
+        <v>7.309531792998314e-05</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0006984809879213572</v>
+        <v>7.494804594898596e-05</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0009336633956991136</v>
+        <v>0.0001827297965064645</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0004101575468666852</v>
+        <v>1.7648606444709e-05</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.0006215039175003767</v>
+        <v>3.691980964504182e-05</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0002334385353606194</v>
+        <v>5.094577500130981e-05</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0006519975140690804</v>
+        <v>9.545011562295258e-05</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.001138007384724915</v>
+        <v>8.0358108789369e-07</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0002829140285030007</v>
+        <v>3.168151306454092e-05</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0008570585632696748</v>
+        <v>4.85166056023445e-05</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0005231237737461925</v>
+        <v>0.0002248959790449589</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.001287636696361005</v>
+        <v>0.0001614039647392929</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.000817715423181653</v>
+        <v>5.39557404408697e-05</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.001156199024990201</v>
+        <v>0.000271079974481836</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0003672209859360009</v>
+        <v>4.955555050401017e-05</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0001208021785714664</v>
+        <v>4.842146154260263e-05</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.001874469104222953</v>
+        <v>0.0001331857347395271</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.001710722455754876</v>
+        <v>0.0002217973960796371</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.00174214446451515</v>
+        <v>0.0001851023844210431</v>
       </c>
       <c r="FR5" t="n">
-        <v>0.003411841578781605</v>
+        <v>0.0001054463282343931</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.002000667853280902</v>
+        <v>3.95838069380261e-05</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0008770973654463887</v>
+        <v>0.000222318121814169</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.001789228990674019</v>
+        <v>9.985076758312061e-06</v>
       </c>
       <c r="FV5" t="n">
-        <v>5.193964170757681e-05</v>
+        <v>3.546273364918306e-05</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0005463939742185175</v>
+        <v>0.0001039053604472429</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.001530876383185387</v>
+        <v>5.064102879259735e-05</v>
       </c>
       <c r="FY5" t="n">
-        <v>0.0007330211228691041</v>
+        <v>7.30027568351943e-06</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0005293359281495214</v>
+        <v>0.0001678767439443618</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.001310971798375249</v>
+        <v>0.0001121514214901254</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.001224699430167675</v>
+        <v>0.0001483364030718803</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.002661708509549499</v>
+        <v>0.0002533879596740007</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.00214392296038568</v>
+        <v>7.460900815203786e-05</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0002140473516192287</v>
+        <v>0.0002357288467464969</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0007512457668781281</v>
+        <v>6.47413071419578e-06</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.000487363402498886</v>
+        <v>5.474470526678488e-05</v>
       </c>
     </row>
     <row r="6">
@@ -3844,5123 +3844,5123 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0005528159090317786</v>
+        <v>0.0008408001740463078</v>
       </c>
       <c r="B7" t="n">
-        <v>0.009762567467987537</v>
+        <v>0.001597689464688301</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008330729906447232</v>
+        <v>0.0001200065307784826</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00641211774200201</v>
+        <v>0.0002391757152508944</v>
       </c>
       <c r="E7" t="n">
-        <v>0.006284113973379135</v>
+        <v>0.0001583756529726088</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005126436706632376</v>
+        <v>0.001439476269297302</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001373717677779496</v>
+        <v>0.000603833410423249</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001362519804388285</v>
+        <v>0.0005824825493618846</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001549969078041613</v>
+        <v>0.0001560701784910634</v>
       </c>
       <c r="J7" t="n">
-        <v>9.350714390166104e-05</v>
+        <v>0.0008005357231013477</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007836278527975082</v>
+        <v>0.002206407254561782</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00106665666680783</v>
+        <v>0.000325823319144547</v>
       </c>
       <c r="M7" t="n">
-        <v>0.006135539151728153</v>
+        <v>0.0001649143669055775</v>
       </c>
       <c r="N7" t="n">
-        <v>0.007412026636302471</v>
+        <v>0.000840266584418714</v>
       </c>
       <c r="O7" t="n">
-        <v>0.007509549614042044</v>
+        <v>0.00151034165173769</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0004072845913469791</v>
+        <v>0.0002414231275906786</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00146266573574394</v>
+        <v>0.0001707546762190759</v>
       </c>
       <c r="R7" t="n">
-        <v>0.00161795224994421</v>
+        <v>0.0009200708591379225</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008669422240927815</v>
+        <v>4.98421723023057e-05</v>
       </c>
       <c r="T7" t="n">
-        <v>0.00256852270103991</v>
+        <v>9.970967948902398e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0001270211942028254</v>
+        <v>0.0002948801557067782</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000285015266854316</v>
+        <v>0.0004050662682857364</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001763950102031231</v>
+        <v>0.0002276191953569651</v>
       </c>
       <c r="X7" t="n">
-        <v>0.002622355474159122</v>
+        <v>0.0001907868718262762</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0009363463614135981</v>
+        <v>4.087734851054847e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0001651784405112267</v>
+        <v>0.0004214245418552309</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0006355125806294382</v>
+        <v>1.720289219520055e-05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.001388519071042538</v>
+        <v>0.000183046591700986</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.002152820350602269</v>
+        <v>0.000236327585298568</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.001475569792091846</v>
+        <v>0.000194880340131931</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.001578835537657142</v>
+        <v>0.0004176150250714272</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.001855801674537361</v>
+        <v>0.0005376742919906974</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.002318391343578696</v>
+        <v>0.0006194580346345901</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.001698572770692408</v>
+        <v>0.0001035019668051973</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0004372821422293782</v>
+        <v>0.001078704837709665</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.854660851880908e-05</v>
+        <v>0.0002215901622548699</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0005361663061194122</v>
+        <v>0.0002285612572450191</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.002448146929964423</v>
+        <v>0.000209734178497456</v>
       </c>
       <c r="AM7" t="n">
-        <v>5.815312033519149e-05</v>
+        <v>0.0003877035051118582</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0002302908105775714</v>
+        <v>0.0003860198485199362</v>
       </c>
       <c r="AO7" t="n">
-        <v>6.392753857653588e-05</v>
+        <v>0.0002496011729817837</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.0005128612974658608</v>
+        <v>0.000175654306076467</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.001217215671204031</v>
+        <v>0.0002114414382958785</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0007145541021600366</v>
+        <v>0.000428347266279161</v>
       </c>
       <c r="AS7" t="n">
-        <v>0.0006351916235871613</v>
+        <v>8.351395808858797e-05</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.001995445927605033</v>
+        <v>0.0005471408367156982</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.007228387519717216</v>
+        <v>0.0017327576642856</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.246563083957881e-05</v>
+        <v>0.0003966315998695791</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.002281544497236609</v>
+        <v>0.0001489043643232435</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.001773629919625819</v>
+        <v>0.0006390925846062601</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0008966709719970822</v>
+        <v>0.001171596813946962</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.002465762430801988</v>
+        <v>7.210906915133819e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.0005254622083157301</v>
+        <v>0.000134828471345827</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.001243089442141354</v>
+        <v>0.0003781285195145756</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0005572455120272934</v>
+        <v>6.104801286710426e-06</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.002534419763833284</v>
+        <v>1.599900497240014e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.00167192961089313</v>
+        <v>0.0002179807052016258</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.001633196836337447</v>
+        <v>0.0001368246739730239</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0066493796184659</v>
+        <v>0.0003991440462414175</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.002266791881993413</v>
+        <v>0.0001871223212219775</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.003173732897266746</v>
+        <v>0.0001490272406954318</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.001788226654753089</v>
+        <v>0.000447328551672399</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.002120110904797912</v>
+        <v>9.638037590775639e-05</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0005063994321972132</v>
+        <v>1.728192728478462e-06</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0009100180468522012</v>
+        <v>0.000564452086109668</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0009759398526512086</v>
+        <v>2.639384547364898e-06</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.001125335926190019</v>
+        <v>7.225033914437518e-05</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.001322707976214588</v>
+        <v>0.0005547716864384711</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.002037976402789354</v>
+        <v>0.0003830603673122823</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.001680997549556196</v>
+        <v>0.0007994977058842778</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0002009303425438702</v>
+        <v>4.497222835198045e-05</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0005151905352249742</v>
+        <v>0.000575911020860076</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.001224374515004456</v>
+        <v>0.0003061967727262527</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.003839875804260373</v>
+        <v>0.001065682037733495</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.001735886209644377</v>
+        <v>0.00025040318723768</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.00197348278015852</v>
+        <v>0.000538134656380862</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0001753219985403121</v>
+        <v>0.0001281135337194428</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0002233368577435613</v>
+        <v>0.0005530817434191704</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.0002470390172675252</v>
+        <v>0.000225216630497016</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.0004725612816400826</v>
+        <v>8.959874685388058e-05</v>
       </c>
       <c r="CC7" t="n">
-        <v>6.794289220124483e-07</v>
+        <v>8.413572504650801e-05</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0001308245409745723</v>
+        <v>0.0002631521492730826</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.001551868976093829</v>
+        <v>0.0004885275266133249</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0002888809831347317</v>
+        <v>4.224701115163043e-05</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0005621210439130664</v>
+        <v>0.0001985399867407978</v>
       </c>
       <c r="CH7" t="n">
-        <v>5.319710180629045e-05</v>
+        <v>8.798230555839837e-05</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0009564050706103444</v>
+        <v>0.0003860571305267513</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0008029872551560402</v>
+        <v>0.0002470156468916684</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.0001178361126221716</v>
+        <v>7.990412996150553e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.0001216279633808881</v>
+        <v>0.0001688256888883188</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.00164824805688113</v>
+        <v>2.844055416062474e-06</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.00105784647166729</v>
+        <v>0.0007428008830174804</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.000210873520700261</v>
+        <v>0.0004451093554962426</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.0009534770506434143</v>
+        <v>0.00015629616973456</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0005164432805031538</v>
+        <v>0.0004400612961035222</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.001338883186690509</v>
+        <v>0.000133283669129014</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.002064567757770419</v>
+        <v>0.0003734634956344962</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.002817859873175621</v>
+        <v>0.000137572264065966</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.0002777845948003232</v>
+        <v>0.0002058490208582953</v>
       </c>
       <c r="CV7" t="n">
-        <v>5.555638927035034e-05</v>
+        <v>0.0001635751104913652</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.001034120912663639</v>
+        <v>0.0004470199055504054</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.0006752763292752206</v>
+        <v>1.580261596245691e-05</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0009596961317583919</v>
+        <v>0.0001066217955667526</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.000272915989626199</v>
+        <v>5.532688737730496e-05</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.001135159283876419</v>
+        <v>0.0003876996925100684</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.0005495019722729921</v>
+        <v>4.298269777791575e-05</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.0002095616655424237</v>
+        <v>0.0001520377118140459</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0003486763162072748</v>
+        <v>0.000160397874424234</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.001432709395885468</v>
+        <v>0.0001396306324750185</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.002259104046970606</v>
+        <v>0.0005885534337721765</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.00186296587344259</v>
+        <v>0.0003067475627176464</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.0002085271989926696</v>
+        <v>0.0001831579720601439</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0005345277022570372</v>
+        <v>0.000373721937648952</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0001819635508581996</v>
+        <v>0.0003913007967639714</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.001962620532140136</v>
+        <v>0.0001081710652215406</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0005260222824290395</v>
+        <v>0.0004697320400737226</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.0005433454061858356</v>
+        <v>8.982688450487331e-05</v>
       </c>
       <c r="DN7" t="n">
-        <v>9.951909305527806e-06</v>
+        <v>0.0002486736339051276</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0004334335390012711</v>
+        <v>0.0002758268383331597</v>
       </c>
       <c r="DP7" t="n">
-        <v>1.966935815289617e-05</v>
+        <v>0.0002603575703687966</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.003632671665400267</v>
+        <v>0.0004424899525474757</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.001171520794741809</v>
+        <v>0.0001612792548257858</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.002654379466548562</v>
+        <v>0.0005070005427114666</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.00154155632480979</v>
+        <v>8.987993351183832e-05</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.0001354900741716847</v>
+        <v>0.0004303249879740179</v>
       </c>
       <c r="DV7" t="n">
-        <v>0.0001584280980750918</v>
+        <v>0.0001835859729908407</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0005886454600840807</v>
+        <v>0.0002180550654884428</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.001292012864723802</v>
+        <v>0.0002358414640184492</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.001447985181584954</v>
+        <v>8.787740080151707e-05</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.002731095999479294</v>
+        <v>9.592334390617907e-05</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.001870266743935645</v>
+        <v>8.835754852043465e-05</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.001791853224858642</v>
+        <v>0.000396675372030586</v>
       </c>
       <c r="EC7" t="n">
-        <v>0.0008384098182432353</v>
+        <v>0.0001383416238240898</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0002553578233346343</v>
+        <v>0.0003798582183662802</v>
       </c>
       <c r="EE7" t="n">
-        <v>0.0009820149280130863</v>
+        <v>0.0004527343844529241</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0009161531925201416</v>
+        <v>0.0003491665993351489</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.0009782419074326754</v>
+        <v>0.0001031971114571206</v>
       </c>
       <c r="EH7" t="n">
-        <v>5.481277185026556e-05</v>
+        <v>0.0002315267047379166</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.001034907763823867</v>
+        <v>2.246426083729602e-05</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.0004038162005599588</v>
+        <v>0.0002032242919085547</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.0002980403951369226</v>
+        <v>0.0001641796552576125</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.001758407568559051</v>
+        <v>4.29714382335078e-05</v>
       </c>
       <c r="EM7" t="n">
-        <v>0.0006361888954415917</v>
+        <v>1.211820381286088e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.0004605380527209491</v>
+        <v>4.539288056548685e-07</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.0003808183828368783</v>
+        <v>0.0001888478291220963</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0004661198181565851</v>
+        <v>0.0001239364064531401</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0.001448355382308364</v>
+        <v>3.853599628200755e-05</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.001340825809165835</v>
+        <v>0.0003700900997500867</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0005061597330495715</v>
+        <v>0.000598522019572556</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.002066373126581311</v>
+        <v>0.0004924479871988297</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.00147777353413403</v>
+        <v>5.742608482250944e-05</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.000446677760919556</v>
+        <v>8.03334332886152e-05</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.001742601743899286</v>
+        <v>0.0002113269147230312</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0001274399401154369</v>
+        <v>0.0002140813739970326</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.001098906854167581</v>
+        <v>0.0005913840141147375</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0.0003269515582360327</v>
+        <v>6.40277357888408e-06</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0008329542470164597</v>
+        <v>9.55299983615987e-05</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.0001403018686687574</v>
+        <v>0.0001585372228873894</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.001247900305315852</v>
+        <v>0.0003157711180392653</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.0009686927078291774</v>
+        <v>0.0002145781327271834</v>
       </c>
       <c r="FE7" t="n">
-        <v>0.0001808603119570762</v>
+        <v>7.683886360609904e-05</v>
       </c>
       <c r="FF7" t="n">
-        <v>6.130372639745474e-06</v>
+        <v>1.932715167640708e-05</v>
       </c>
       <c r="FG7" t="n">
-        <v>0.0004271101206541061</v>
+        <v>6.023712194291875e-05</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.0006933737313374877</v>
+        <v>0.0005836569471284747</v>
       </c>
       <c r="FI7" t="n">
-        <v>0.001124246628023684</v>
+        <v>0.0003682564129121602</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.001846995903179049</v>
+        <v>0.0003770031617023051</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.001135703991167247</v>
+        <v>0.0002143085293937474</v>
       </c>
       <c r="FL7" t="n">
-        <v>1.571199391037226e-06</v>
+        <v>0.0006099402671679854</v>
       </c>
       <c r="FM7" t="n">
-        <v>0.0008631253731437027</v>
+        <v>0.0002273858553962782</v>
       </c>
       <c r="FN7" t="n">
-        <v>4.121859092265368e-05</v>
+        <v>0.0006031101802363992</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0007680700509808958</v>
+        <v>0.0006048512877896428</v>
       </c>
       <c r="FP7" t="n">
-        <v>0.0002339118509553373</v>
+        <v>0.0002558999694883823</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.003471472533419728</v>
+        <v>6.749455496901646e-05</v>
       </c>
       <c r="FR7" t="n">
-        <v>0.001228617737069726</v>
+        <v>0.00091037672245875</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.001651680795475841</v>
+        <v>0.0002727667742874473</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.001461536041460931</v>
+        <v>0.0005633317632600665</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.002010469557717443</v>
+        <v>7.348484359681606e-06</v>
       </c>
       <c r="FV7" t="n">
-        <v>0.002835682593286037</v>
+        <v>9.349129686597735e-05</v>
       </c>
       <c r="FW7" t="n">
-        <v>0.0008070717449299991</v>
+        <v>0.0004272753139957786</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.001155569218099117</v>
+        <v>0.0001655167725402862</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.0001822917256504297</v>
+        <v>0.0002381333033554256</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0004076186160091311</v>
+        <v>0.0002805865660775453</v>
       </c>
       <c r="GA7" t="n">
-        <v>0.002031585434451699</v>
+        <v>0.0002981529978569597</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0004358796868473291</v>
+        <v>7.642918353667483e-05</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.0001676764222793281</v>
+        <v>0.0007876457530073822</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.001082819188013673</v>
+        <v>0.0007174038328230381</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.001639291411265731</v>
+        <v>7.907641702331603e-06</v>
       </c>
       <c r="GF7" t="n">
-        <v>0.0016230926848948</v>
+        <v>0.000329430476995185</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.001280793454498053</v>
+        <v>0.0004979969235137105</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.0003381061833351851</v>
+        <v>0.001934790285304189</v>
       </c>
       <c r="B8" t="n">
-        <v>0.009910088032484055</v>
+        <v>0.01122651714831591</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001199188875034451</v>
+        <v>0.002424891106784344</v>
       </c>
       <c r="D8" t="n">
-        <v>0.006047922652214766</v>
+        <v>0.006046561989933252</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003003757214173675</v>
+        <v>0.00221680267713964</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002898788312450051</v>
+        <v>0.0006274947081692517</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009682266972959042</v>
+        <v>0.002496775006875396</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009082454489544034</v>
+        <v>0.002458054106682539</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001191870658658445</v>
+        <v>3.341306182846893e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001226635999046266</v>
+        <v>0.0001308541395701468</v>
       </c>
       <c r="K8" t="n">
-        <v>0.007616777438670397</v>
+        <v>0.01217763125896454</v>
       </c>
       <c r="L8" t="n">
-        <v>3.535349242156371e-05</v>
+        <v>0.003130512544885278</v>
       </c>
       <c r="M8" t="n">
-        <v>0.006189756561070681</v>
+        <v>0.008141197264194489</v>
       </c>
       <c r="N8" t="n">
-        <v>0.003969598095864058</v>
+        <v>0.003599046031013131</v>
       </c>
       <c r="O8" t="n">
-        <v>0.003384346608072519</v>
+        <v>0.0004553811450023204</v>
       </c>
       <c r="P8" t="n">
-        <v>0.0002495398512110114</v>
+        <v>0.002035337267443538</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.00104593497235328</v>
+        <v>0.0009422048460692167</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001648177625611424</v>
+        <v>0.000594834447838366</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0004829255922231823</v>
+        <v>2.590270014479756e-05</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001986088464036584</v>
+        <v>0.001139586907811463</v>
       </c>
       <c r="U8" t="n">
-        <v>9.886972839012742e-05</v>
+        <v>0.00098555872682482</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0002313437435077503</v>
+        <v>0.0003942156035918742</v>
       </c>
       <c r="W8" t="n">
-        <v>0.0008750882698222995</v>
+        <v>0.001833246205933392</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002062995918095112</v>
+        <v>0.001094736158847809</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.00141355802770704</v>
+        <v>0.0006635599420405924</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0003138021565973759</v>
+        <v>0.001210020389407873</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0009953881381079555</v>
+        <v>0.00198984588496387</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0006469585932791233</v>
+        <v>0.00145823962520808</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.001558058895170689</v>
+        <v>0.0001674380619078875</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0004418380267452449</v>
+        <v>0.0008060444379225373</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.0007699052803218365</v>
+        <v>0.002660567406564951</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.0008802663069218397</v>
+        <v>0.0001359005691483617</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0001336142595391721</v>
+        <v>0.002163899829611182</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0006033373647369444</v>
+        <v>0.0008895783685147762</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.0001620508701307699</v>
+        <v>0.001358769950456917</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.0001877345785032958</v>
+        <v>0.0002155291149392724</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0005299276672303677</v>
+        <v>0.0002850781893357635</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001200175029225647</v>
+        <v>0.00207084696739912</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0001822842023102567</v>
+        <v>0.0006489416700787842</v>
       </c>
       <c r="AN8" t="n">
-        <v>5.14803032274358e-05</v>
+        <v>0.001884092576801777</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0005571217625401914</v>
+        <v>0.0007440882036462426</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0004847689415328205</v>
+        <v>0.001214557560160756</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0003005229809787124</v>
+        <v>0.0004847817763220519</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0004803304618690163</v>
+        <v>0.0002935874799732119</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0004955650074407458</v>
+        <v>0.0006113043637014925</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001327861566096544</v>
+        <v>0.0003163974906783551</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.006712151691317558</v>
+        <v>0.006939066108316183</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0003345290024299175</v>
+        <v>0.001053577521815896</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.001239970792084932</v>
+        <v>0.002255572471767664</v>
       </c>
       <c r="AX8" t="n">
-        <v>8.225854980992153e-05</v>
+        <v>0.004704692866653204</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.732536035589874e-05</v>
+        <v>0.0005571781657636166</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.0003268503933213651</v>
+        <v>0.0004512909799814224</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.850627738051116e-05</v>
+        <v>0.001269000116735697</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0005637436406686902</v>
+        <v>0.0003438793355599046</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.000652879592962563</v>
+        <v>0.0008285650983452797</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.001297050039283931</v>
+        <v>0.0008597279083915055</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001915286062285304</v>
+        <v>0.002056208904832602</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.001477143610827625</v>
+        <v>0.001885145902633667</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.004156950861215591</v>
+        <v>0.001004344434477389</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.001505543245002627</v>
+        <v>0.001417074352502823</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.001804050290957093</v>
+        <v>0.0005437767831608653</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.001081359456293285</v>
+        <v>0.003114900551736355</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.00115212716627866</v>
+        <v>0.0004190846811980009</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0003856709518004209</v>
+        <v>9.557735029375181e-05</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0004768300277646631</v>
+        <v>0.0001789085799828172</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.000863255059812218</v>
+        <v>0.001059777685441077</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.186010194942355e-06</v>
+        <v>0.0009105862700380385</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0002770426799543202</v>
+        <v>0.001836288254708052</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.001066635479219258</v>
+        <v>0.0002860257227439433</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.0006196509930305183</v>
+        <v>0.0004792319959960878</v>
       </c>
       <c r="BS8" t="n">
-        <v>3.350496990606189e-05</v>
+        <v>0.001217216486111283</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.000485029595438391</v>
+        <v>0.0003840823192149401</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.0009341766126453876</v>
+        <v>0.0005590151995420456</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.003610414685681462</v>
+        <v>0.005092989187687635</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.001310519408434629</v>
+        <v>0.0004634117649402469</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.001569472020491958</v>
+        <v>0.001703843357972801</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0001687200274318457</v>
+        <v>0.001729373005218804</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.00104143179487437</v>
+        <v>0.0017159772105515</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0001718919374980032</v>
+        <v>0.001225783722475171</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.0001445788802811876</v>
+        <v>0.0001262935111299157</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.0008080534753389657</v>
+        <v>0.001681457972154021</v>
       </c>
       <c r="CD8" t="n">
-        <v>5.922949640080333e-05</v>
+        <v>0.0001735172991175205</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.001634047599509358</v>
+        <v>0.003108004573732615</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.0007476451573893428</v>
+        <v>0.001096690422855318</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0006013260572217405</v>
+        <v>0.002482912968844175</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0002925138105638325</v>
+        <v>6.995569128775969e-05</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0007205278961919248</v>
+        <v>0.0002564477035775781</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.0004555433406494558</v>
+        <v>5.127355689182878e-05</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0001334750413661823</v>
+        <v>1.635194348637015e-05</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.0002937549434136599</v>
+        <v>0.000581318570766598</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.001517430762760341</v>
+        <v>0.001181996893137693</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.0001901073555927724</v>
+        <v>0.00434945710003376</v>
       </c>
       <c r="CO8" t="n">
-        <v>7.920012285467237e-05</v>
+        <v>0.001497084158472717</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.001129046780988574</v>
+        <v>0.004932580050081015</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.001417380175553262</v>
+        <v>5.169946234673262e-05</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.001113278907723725</v>
+        <v>0.002158981747925282</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.00105740618892014</v>
+        <v>0.0005114361410960555</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.001913737738505006</v>
+        <v>0.000792813953012228</v>
       </c>
       <c r="CU8" t="n">
-        <v>0.0002383915707468987</v>
+        <v>0.001287098973989487</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.260045974049717e-05</v>
+        <v>0.0001734047546051443</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.001431779121048748</v>
+        <v>0.002982704900205135</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0008404685067944229</v>
+        <v>0.0008967309258878231</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.0008560172282159328</v>
+        <v>0.002420780016109347</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0002623516484163702</v>
+        <v>0.0004167984880041331</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.0008797704940661788</v>
+        <v>0.0001659420086070895</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.000447326572611928</v>
+        <v>0.0001125360722653568</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0001714186655590311</v>
+        <v>9.478013089392334e-05</v>
       </c>
       <c r="DD8" t="n">
-        <v>8.11510399216786e-05</v>
+        <v>0.0008204581099562347</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.0008347350521944463</v>
+        <v>0.0007900559576228261</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.001875131973065436</v>
+        <v>0.002257530344650149</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.0003545529907569289</v>
+        <v>7.22067998140119e-05</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.001521214377135038</v>
+        <v>0.001488653826527297</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0004923808155581355</v>
+        <v>0.001968544442206621</v>
       </c>
       <c r="DJ8" t="n">
-        <v>1.306118065258488e-05</v>
+        <v>0.001726474729366601</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.001184684108011425</v>
+        <v>0.0003068162477575243</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0005734780570492148</v>
+        <v>0.001830114284530282</v>
       </c>
       <c r="DM8" t="n">
-        <v>0.0002014782658079639</v>
+        <v>0.001595778623595834</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.0001853926223702729</v>
+        <v>0.0001840578188421205</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.0001527485001133755</v>
+        <v>0.00242218654602766</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0004982437822036445</v>
+        <v>0.001457575708627701</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0005068979226052761</v>
+        <v>0.001672583050094545</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.001012329827062786</v>
+        <v>0.0008860043017193675</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.0004795633722096682</v>
+        <v>0.001103752641938627</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.0002556980180088431</v>
+        <v>0.001149815157987177</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0003462167805992067</v>
+        <v>0.001344036310911179</v>
       </c>
       <c r="DV8" t="n">
-        <v>0.0004836541484110057</v>
+        <v>0.002906289650127292</v>
       </c>
       <c r="DW8" t="n">
-        <v>8.342910587089136e-05</v>
+        <v>0.0009016710100695491</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.001235553761944175</v>
+        <v>0.0001595688809175044</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.0007870931876823306</v>
+        <v>0.0001809106906875968</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0001463630760554224</v>
+        <v>0.001052960753440857</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.0008699821773916483</v>
+        <v>0.0002985688915941864</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0005177303100936115</v>
+        <v>0.0006829553749412298</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0002820258087012917</v>
+        <v>0.0005254048737697303</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0005542447906918824</v>
+        <v>0.004319903906434774</v>
       </c>
       <c r="EE8" t="n">
-        <v>0.0007315456750802696</v>
+        <v>0.002472405321896076</v>
       </c>
       <c r="EF8" t="n">
-        <v>0.0005446509458124638</v>
+        <v>0.0002984032616950572</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.000867063645273447</v>
+        <v>0.003190687391906977</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0006342240958474576</v>
+        <v>0.0001150486059486866</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0005387963610701263</v>
+        <v>0.002164220903068781</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0005019312375225127</v>
+        <v>0.0004919584025628865</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.001036235364153981</v>
+        <v>0.0002698717580642551</v>
       </c>
       <c r="EL8" t="n">
-        <v>0.0007351507083512843</v>
+        <v>0.000199206464458257</v>
       </c>
       <c r="EM8" t="n">
-        <v>0.0003002943703904748</v>
+        <v>0.000108718901174143</v>
       </c>
       <c r="EN8" t="n">
-        <v>6.492043030448258e-05</v>
+        <v>0.001044618315063417</v>
       </c>
       <c r="EO8" t="n">
-        <v>0.000215647101867944</v>
+        <v>0.0001881072967080399</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.001035430585034192</v>
+        <v>0.001704660826362669</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0009090416133403778</v>
+        <v>0.00057374028256163</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.0007807589718140662</v>
+        <v>0.0008303352515213192</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0006476373528130352</v>
+        <v>0.0003802457649726421</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.002354946453124285</v>
+        <v>0.000318469712510705</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0009633284062147141</v>
+        <v>0.001266358536668122</v>
       </c>
       <c r="EV8" t="n">
-        <v>4.063778033014387e-05</v>
+        <v>1.089830766431987e-05</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0004061303625348955</v>
+        <v>0.00118020479567349</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0002979093987960368</v>
+        <v>0.000264341535512358</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.001543600577861071</v>
+        <v>0.003574996488168836</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.0004637610691133887</v>
+        <v>0.0008474004571326077</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0009297225042246282</v>
+        <v>0.002796903951093554</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.0004238935653120279</v>
+        <v>0.0002094309311360121</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.0008766959654167295</v>
+        <v>0.0006128937238827348</v>
       </c>
       <c r="FD8" t="n">
-        <v>0.0006017169216647744</v>
+        <v>0.0001719101855996996</v>
       </c>
       <c r="FE8" t="n">
-        <v>0.0001678214030107483</v>
+        <v>0.0001163999841082841</v>
       </c>
       <c r="FF8" t="n">
-        <v>0.0003256110940128565</v>
+        <v>0.0008806202095001936</v>
       </c>
       <c r="FG8" t="n">
-        <v>6.279865920078009e-05</v>
+        <v>0.0002303391229361296</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.0004892833530902863</v>
+        <v>0.001467247726395726</v>
       </c>
       <c r="FI8" t="n">
-        <v>0.0005796787445433438</v>
+        <v>0.0007446298259310424</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.001219331403262913</v>
+        <v>0.001321905641816556</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.0002351515868213028</v>
+        <v>0.0002680695324670523</v>
       </c>
       <c r="FL8" t="n">
-        <v>0.0001461857027607039</v>
+        <v>0.00090230000205338</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.0003229844151064754</v>
+        <v>0.0001887171238195151</v>
       </c>
       <c r="FN8" t="n">
-        <v>0.0002719665062613785</v>
+        <v>0.001483148662373424</v>
       </c>
       <c r="FO8" t="n">
-        <v>0.0005506122251972556</v>
+        <v>0.001133305719122291</v>
       </c>
       <c r="FP8" t="n">
-        <v>0.0002004790148930624</v>
+        <v>0.0004430192639119923</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.002791606588289142</v>
+        <v>0.001729224342852831</v>
       </c>
       <c r="FR8" t="n">
-        <v>0.0003934034903068095</v>
+        <v>0.0002019955136347562</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.001344682881608605</v>
+        <v>0.001776625169441104</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.0001535585033707321</v>
+        <v>0.002351742703467607</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.0003896905982401222</v>
+        <v>0.001490998547524214</v>
       </c>
       <c r="FV8" t="n">
-        <v>0.0002235220745205879</v>
+        <v>0.0004888002295047045</v>
       </c>
       <c r="FW8" t="n">
-        <v>7.18359078746289e-05</v>
+        <v>0.0002190727973356843</v>
       </c>
       <c r="FX8" t="n">
-        <v>0.0004664651642087847</v>
+        <v>0.002979665296152234</v>
       </c>
       <c r="FY8" t="n">
-        <v>0.001208823290653527</v>
+        <v>0.00144897261634469</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.0003774706274271011</v>
+        <v>0.002601783256977797</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.0002554989187046885</v>
+        <v>0.0008319822372868657</v>
       </c>
       <c r="GB8" t="n">
-        <v>0.0003892776439897716</v>
+        <v>0.001083905110135674</v>
       </c>
       <c r="GC8" t="n">
-        <v>0.0008507943712174892</v>
+        <v>0.004695355426520109</v>
       </c>
       <c r="GD8" t="n">
-        <v>0.0005997709231451154</v>
+        <v>0.0004312670207582414</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.002036389196291566</v>
+        <v>0.002114460803568363</v>
       </c>
       <c r="GF8" t="n">
-        <v>0.0001085933618014678</v>
+        <v>0.0003276125353295356</v>
       </c>
       <c r="GG8" t="n">
-        <v>0.0001166629226645455</v>
+        <v>0.0005414738552644849</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.640829188749194e-05</v>
+        <v>0.004580147564411163</v>
       </c>
       <c r="B9" t="n">
-        <v>0.001243086415342987</v>
+        <v>0.01547679863870144</v>
       </c>
       <c r="C9" t="n">
-        <v>5.646710997098126e-05</v>
+        <v>0.0006768092280253768</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0005005760467611253</v>
+        <v>0.001713711768388748</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0004025537054985762</v>
+        <v>0.001517318305559456</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0008855649502947927</v>
+        <v>0.004347777459770441</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002298883337061852</v>
+        <v>0.001164771965704858</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0003352721396367997</v>
+        <v>0.0007984463009051979</v>
       </c>
       <c r="I9" t="n">
-        <v>3.559118704288267e-05</v>
+        <v>0.003871941473335028</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0002576948900241405</v>
+        <v>0.001978105399757624</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009570436086505651</v>
+        <v>0.02028455398976803</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0001882316573755816</v>
+        <v>0.002028157003223896</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0004457691975403577</v>
+        <v>0.004938892088830471</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0004492540319915861</v>
+        <v>0.00337154814042151</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00102870655246079</v>
+        <v>0.003539304714649916</v>
       </c>
       <c r="P9" t="n">
-        <v>0.000121531898912508</v>
+        <v>0.004681187216192484</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001407816307619214</v>
+        <v>0.007687919773161411</v>
       </c>
       <c r="R9" t="n">
-        <v>2.644225605763495e-05</v>
+        <v>0.003323508659377694</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0001464621018385515</v>
+        <v>0.001856609946116805</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0002763273660093546</v>
+        <v>0.005366879515349865</v>
       </c>
       <c r="U9" t="n">
-        <v>4.655285010812804e-05</v>
+        <v>0.0001342660980299115</v>
       </c>
       <c r="V9" t="n">
-        <v>9.905662591336295e-05</v>
+        <v>0.003099452238529921</v>
       </c>
       <c r="W9" t="n">
-        <v>2.660063000803348e-05</v>
+        <v>0.001502087339758873</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0001306479971390218</v>
+        <v>0.001305559184402227</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.0001522081001894549</v>
+        <v>0.001596621586941183</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.94116762233898e-05</v>
+        <v>0.003222466679289937</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0001330655213678256</v>
+        <v>0.00128489441704005</v>
       </c>
       <c r="AB9" t="n">
-        <v>9.322915138909593e-05</v>
+        <v>1.434091245755553e-05</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.00026805599918589</v>
+        <v>0.0004031655553262681</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0001398948224959895</v>
+        <v>0.001226621679961681</v>
       </c>
       <c r="AE9" t="n">
-        <v>9.298275108449161e-05</v>
+        <v>0.005141338333487511</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0001876038440968841</v>
+        <v>0.009590757079422474</v>
       </c>
       <c r="AG9" t="n">
-        <v>9.803847206057981e-05</v>
+        <v>0.001045264536514878</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0001340097805950791</v>
+        <v>0.001181725529022515</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0001271334622288123</v>
+        <v>0.003649451769888401</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.559316297061741e-05</v>
+        <v>0.001438790000975132</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0001376761501887813</v>
+        <v>0.0001220960984937847</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0002430883469060063</v>
+        <v>0.005568771623075008</v>
       </c>
       <c r="AM9" t="n">
-        <v>4.595646896632388e-05</v>
+        <v>0.0005112369544804096</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.494695607107133e-05</v>
+        <v>0.002762774936854839</v>
       </c>
       <c r="AO9" t="n">
-        <v>3.386043681530282e-05</v>
+        <v>0.002911714604124427</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.0002105119201587513</v>
+        <v>2.932793722720817e-05</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.081575752934441e-05</v>
+        <v>0.003279559081420302</v>
       </c>
       <c r="AR9" t="n">
-        <v>4.618166713044047e-05</v>
+        <v>0.00382925127632916</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0001480696955695748</v>
+        <v>0.0005825278931297362</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.0001690650969976559</v>
+        <v>0.00186816870700568</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.0008623748435638845</v>
+        <v>0.01839700527489185</v>
       </c>
       <c r="AV9" t="n">
-        <v>7.759903382975608e-05</v>
+        <v>0.0006759854150004685</v>
       </c>
       <c r="AW9" t="n">
-        <v>3.484502667561173e-05</v>
+        <v>0.0006727834697812796</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0001820152101572603</v>
+        <v>0.00416832510381937</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0006045505870133638</v>
+        <v>0.001530101057142019</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.0001294719695579261</v>
+        <v>0.0006665916880592704</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.0002288967662025243</v>
+        <v>0.002385596977546811</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0002114092494593933</v>
+        <v>0.001372772036120296</v>
       </c>
       <c r="BC9" t="n">
-        <v>6.705037958454341e-05</v>
+        <v>0.002093046903610229</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0001896782632684335</v>
+        <v>0.0034479727037251</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.000397119321860373</v>
+        <v>0.0008428493747487664</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0003259257646277547</v>
+        <v>0.003980369307100773</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.000400419783545658</v>
+        <v>0.006850574631243944</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.0002551341603975743</v>
+        <v>0.002089219400659204</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0001179668470285833</v>
+        <v>0.003069580299779773</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0003394583472982049</v>
+        <v>0.0002939371624961495</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.359750502975658e-06</v>
+        <v>0.003253514179959893</v>
       </c>
       <c r="BL9" t="n">
-        <v>7.541212107753381e-05</v>
+        <v>0.002603112952783704</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0001713841193122789</v>
+        <v>0.0004454609588719904</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0001209072215715423</v>
+        <v>0.001182345906272531</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0001161237669293769</v>
+        <v>0.000570474483538419</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.770641680806875e-05</v>
+        <v>0.0009565657819621265</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0001799389865482226</v>
+        <v>0.0009742521797306836</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0002022131229750812</v>
+        <v>0.004386590793728828</v>
       </c>
       <c r="BS9" t="n">
-        <v>6.338565435726196e-05</v>
+        <v>0.0006391949136741459</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.853671245859005e-05</v>
+        <v>0.002216861583292484</v>
       </c>
       <c r="BU9" t="n">
-        <v>9.213814337272197e-05</v>
+        <v>0.003060122951865196</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.000451927917310968</v>
+        <v>0.01307374052703381</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0001525336847407743</v>
+        <v>0.0006869493518024683</v>
       </c>
       <c r="BX9" t="n">
-        <v>8.365025860257447e-05</v>
+        <v>0.002105080988258123</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0002703927457332611</v>
+        <v>0.00010064453817904</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.00012512895045802</v>
+        <v>0.0007358905277214944</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0001449420815333724</v>
+        <v>0.002135754562914371</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.0001266906474484131</v>
+        <v>0.001183652668260038</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.0001441714994143695</v>
+        <v>0.0005829724832437932</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.137703631888144e-05</v>
+        <v>0.001105229835957289</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0002243806229671463</v>
+        <v>0.004862929694354534</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0001412078854627907</v>
+        <v>0.0002890646574087441</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.000106867155409418</v>
+        <v>0.0006972658447921276</v>
       </c>
       <c r="CH9" t="n">
-        <v>6.218477210495621e-05</v>
+        <v>0.0002622485044412315</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0001562434190418571</v>
+        <v>0.001318348571658134</v>
       </c>
       <c r="CJ9" t="n">
-        <v>3.695987470564432e-05</v>
+        <v>0.000752260151784867</v>
       </c>
       <c r="CK9" t="n">
-        <v>7.086032564984635e-05</v>
+        <v>0.000864929985255003</v>
       </c>
       <c r="CL9" t="n">
-        <v>9.025315375765786e-05</v>
+        <v>0.0001035567256622016</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.0001714293757686391</v>
+        <v>0.002532684011384845</v>
       </c>
       <c r="CN9" t="n">
-        <v>7.204242137959227e-05</v>
+        <v>0.009430848062038422</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.0001451670832466334</v>
+        <v>0.001749826245941222</v>
       </c>
       <c r="CP9" t="n">
-        <v>7.457652827724814e-05</v>
+        <v>0.005971570499241352</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.314491186756641e-05</v>
+        <v>0.005773657467216253</v>
       </c>
       <c r="CR9" t="n">
-        <v>3.848497726721689e-05</v>
+        <v>0.0009395517408847809</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0001465603709220886</v>
+        <v>0.0005039017414674163</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.0002174857072532177</v>
+        <v>0.000268068048171699</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.860328666225541e-05</v>
+        <v>0.0006646793335676193</v>
       </c>
       <c r="CV9" t="n">
-        <v>3.741819818969816e-05</v>
+        <v>0.0002809345023706555</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0001672615908319131</v>
+        <v>0.0045320731587708</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.000159080809680745</v>
+        <v>0.000518164481036365</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0001827242522267625</v>
+        <v>0.0005523666040971875</v>
       </c>
       <c r="CZ9" t="n">
-        <v>4.493345477385446e-05</v>
+        <v>7.328673382289708e-05</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.0001636925153434277</v>
+        <v>0.001464191591367126</v>
       </c>
       <c r="DB9" t="n">
-        <v>4.230310878483579e-05</v>
+        <v>0.000300112966215238</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.000142499411595054</v>
+        <v>0.0007920062053017318</v>
       </c>
       <c r="DD9" t="n">
-        <v>5.776547186542302e-05</v>
+        <v>0.000146237260196358</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0001870958949439228</v>
+        <v>0.0004115418996661901</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0003059148439206183</v>
+        <v>0.0005872784531675279</v>
       </c>
       <c r="DG9" t="n">
-        <v>4.445858576218598e-05</v>
+        <v>0.001445619738660753</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.0004373114788904786</v>
+        <v>0.001318942988291383</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0002034903882304206</v>
+        <v>0.007661729119718075</v>
       </c>
       <c r="DJ9" t="n">
-        <v>4.00023018300999e-05</v>
+        <v>0.0007468726253136992</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.0001917851186590269</v>
+        <v>0.001444226130843163</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0001920893118949607</v>
+        <v>0.001303236931562424</v>
       </c>
       <c r="DM9" t="n">
-        <v>5.64714937354438e-05</v>
+        <v>0.0006046797498129308</v>
       </c>
       <c r="DN9" t="n">
-        <v>9.652931476011872e-05</v>
+        <v>0.0009321289835497737</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.0001074297324521467</v>
+        <v>0.003238765290006995</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.00010605865099933</v>
+        <v>0.0001621026312932372</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0001486272230977193</v>
+        <v>0.003448187839239836</v>
       </c>
       <c r="DR9" t="n">
-        <v>1.542904556117719e-06</v>
+        <v>0.002767600119113922</v>
       </c>
       <c r="DS9" t="n">
-        <v>1.482761399529409e-05</v>
+        <v>0.000304791028611362</v>
       </c>
       <c r="DT9" t="n">
-        <v>5.3256684623193e-05</v>
+        <v>0.001041622483171523</v>
       </c>
       <c r="DU9" t="n">
-        <v>9.83111749519594e-06</v>
+        <v>0.003060754388570786</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0001589555613463745</v>
+        <v>0.0001348049845546484</v>
       </c>
       <c r="DW9" t="n">
-        <v>7.291047222679481e-05</v>
+        <v>0.002950160298496485</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0002632239775266498</v>
+        <v>0.0002719542826525867</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.000349591369740665</v>
+        <v>0.0001632599160075188</v>
       </c>
       <c r="DZ9" t="n">
-        <v>1.221134880324826e-05</v>
+        <v>0.0005072914063930511</v>
       </c>
       <c r="EA9" t="n">
-        <v>7.530536822741851e-05</v>
+        <v>0.001478954683989286</v>
       </c>
       <c r="EB9" t="n">
-        <v>3.850748908007517e-05</v>
+        <v>0.003020107513293624</v>
       </c>
       <c r="EC9" t="n">
-        <v>4.148762855038512e-06</v>
+        <v>0.001308620208874345</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0001081097580026835</v>
+        <v>0.0002483190619386733</v>
       </c>
       <c r="EE9" t="n">
-        <v>4.299817373976111e-05</v>
+        <v>0.0003056245623156428</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0001530169392935932</v>
+        <v>0.0005744093796238303</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.0001193573261843994</v>
+        <v>0.00166499032638967</v>
       </c>
       <c r="EH9" t="n">
-        <v>3.256695708842017e-05</v>
+        <v>0.0007838880992494524</v>
       </c>
       <c r="EI9" t="n">
-        <v>4.703814192907885e-05</v>
+        <v>0.001497155288234353</v>
       </c>
       <c r="EJ9" t="n">
-        <v>1.162867920356803e-05</v>
+        <v>0.001329015474766493</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0001701704022707418</v>
+        <v>0.0008741731871850789</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0001039984781527892</v>
+        <v>0.0003187039110343903</v>
       </c>
       <c r="EM9" t="n">
-        <v>1.137977415055502e-05</v>
+        <v>0.000446942140115425</v>
       </c>
       <c r="EN9" t="n">
-        <v>1.537089519842993e-05</v>
+        <v>0.0005316798924468458</v>
       </c>
       <c r="EO9" t="n">
-        <v>1.553660695208237e-06</v>
+        <v>0.0004109730944037437</v>
       </c>
       <c r="EP9" t="n">
-        <v>9.391021740157157e-05</v>
+        <v>0.001137563027441502</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.0002497279783710837</v>
+        <v>0.0002812863094732165</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.0001369000819977373</v>
+        <v>0.0006922247703187168</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0001077365086530335</v>
+        <v>0.003623917466029525</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.000157775153638795</v>
+        <v>0.0004260078421793878</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0001049446218530647</v>
+        <v>0.0004877238825429231</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0001663291914155707</v>
+        <v>0.001187518937513232</v>
       </c>
       <c r="EW9" t="n">
-        <v>2.110837158397771e-06</v>
+        <v>0.002473748987540603</v>
       </c>
       <c r="EX9" t="n">
-        <v>2.10558318940457e-05</v>
+        <v>0.00129323173314333</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0001926757977344096</v>
+        <v>0.005086317658424377</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0001082902672351338</v>
+        <v>0.0001234944647876546</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0001002176868496463</v>
+        <v>0.0008697182056494057</v>
       </c>
       <c r="FB9" t="n">
-        <v>9.84587095445022e-05</v>
+        <v>0.0003972080885432661</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0001576415379531682</v>
+        <v>0.0006707464926876128</v>
       </c>
       <c r="FD9" t="n">
-        <v>7.727788761258125e-05</v>
+        <v>0.000684490252751857</v>
       </c>
       <c r="FE9" t="n">
-        <v>7.930041465442628e-05</v>
+        <v>0.0007186550064943731</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0001129551601479761</v>
+        <v>0.0003197766200173646</v>
       </c>
       <c r="FG9" t="n">
-        <v>4.749305844597984e-06</v>
+        <v>0.001925666467286646</v>
       </c>
       <c r="FH9" t="n">
-        <v>5.96696772845462e-05</v>
+        <v>0.00601210119202733</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.000298675149679184</v>
+        <v>8.100418199319392e-05</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0001275278773391619</v>
+        <v>0.005251951515674591</v>
       </c>
       <c r="FK9" t="n">
-        <v>7.36143410904333e-05</v>
+        <v>0.002256103558465838</v>
       </c>
       <c r="FL9" t="n">
-        <v>8.259627793449908e-05</v>
+        <v>0.002057886216789484</v>
       </c>
       <c r="FM9" t="n">
-        <v>5.181815504329279e-05</v>
+        <v>0.002740466501563787</v>
       </c>
       <c r="FN9" t="n">
-        <v>1.704564238025341e-05</v>
+        <v>0.003523130435496569</v>
       </c>
       <c r="FO9" t="n">
-        <v>4.793890184373595e-05</v>
+        <v>0.003057257505133748</v>
       </c>
       <c r="FP9" t="n">
-        <v>3.199804632458836e-05</v>
+        <v>0.002033153548836708</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.0002723563520703465</v>
+        <v>0.007751243188977242</v>
       </c>
       <c r="FR9" t="n">
-        <v>7.310046203201637e-05</v>
+        <v>0.0005751064163632691</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.000117622475954704</v>
+        <v>0.003250590059906244</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.0002378683711867779</v>
+        <v>0.004000039771199226</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0001639997062738985</v>
+        <v>0.0005292885471135378</v>
       </c>
       <c r="FV9" t="n">
-        <v>2.794439933495596e-05</v>
+        <v>0.0001694466336630285</v>
       </c>
       <c r="FW9" t="n">
-        <v>0.0001569821470184252</v>
+        <v>0.001558691496029496</v>
       </c>
       <c r="FX9" t="n">
-        <v>5.473328565130942e-05</v>
+        <v>0.001786672393791378</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0002801483497023582</v>
+        <v>0.00250073941424489</v>
       </c>
       <c r="FZ9" t="n">
-        <v>5.772133590653539e-05</v>
+        <v>0.002519073430448771</v>
       </c>
       <c r="GA9" t="n">
-        <v>9.216301987180486e-05</v>
+        <v>0.0001654464285820723</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0001191649935208261</v>
+        <v>0.00291440449655056</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0001438180479453877</v>
+        <v>0.001605827361345291</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.0001519857760285959</v>
+        <v>0.0001409572432748973</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.0005325718084350228</v>
+        <v>0.0002096693497151136</v>
       </c>
       <c r="GF9" t="n">
-        <v>3.404383096494712e-05</v>
+        <v>0.002483389340341091</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0001588000741321594</v>
+        <v>0.002301926491782069</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.002752043539658189</v>
+        <v>0.003912529442459345</v>
       </c>
       <c r="B10" t="n">
-        <v>0.03437234088778496</v>
+        <v>0.02211934328079224</v>
       </c>
       <c r="C10" t="n">
-        <v>0.004126399289816618</v>
+        <v>0.001602831529453397</v>
       </c>
       <c r="D10" t="n">
-        <v>0.01638187654316425</v>
+        <v>0.01344978623092175</v>
       </c>
       <c r="E10" t="n">
-        <v>0.005367912352085114</v>
+        <v>0.007246519438922405</v>
       </c>
       <c r="F10" t="n">
-        <v>0.007625462953001261</v>
+        <v>0.002622200408950448</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0008555504027754068</v>
+        <v>0.006013540551066399</v>
       </c>
       <c r="H10" t="n">
-        <v>0.001519157318398356</v>
+        <v>0.00565791130065918</v>
       </c>
       <c r="I10" t="n">
-        <v>6.315545761026442e-05</v>
+        <v>0.0007011634297668934</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00362052908167243</v>
+        <v>0.0009267576970160007</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02655144780874252</v>
+        <v>0.02745258808135986</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0009695371263660491</v>
+        <v>0.003001499455422163</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01312403753399849</v>
+        <v>0.01889472827315331</v>
       </c>
       <c r="N10" t="n">
-        <v>0.006325225345790386</v>
+        <v>0.01064350642263889</v>
       </c>
       <c r="O10" t="n">
-        <v>0.006270705722272396</v>
+        <v>0.0008997925906442106</v>
       </c>
       <c r="P10" t="n">
-        <v>0.001180827151983976</v>
+        <v>0.002682842081412673</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.005637604277580976</v>
+        <v>0.004623214714229107</v>
       </c>
       <c r="R10" t="n">
-        <v>0.001801079139113426</v>
+        <v>0.001457742298953235</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0009039416909217834</v>
+        <v>0.000344073458109051</v>
       </c>
       <c r="T10" t="n">
-        <v>0.005236712750047445</v>
+        <v>0.0004585519782267511</v>
       </c>
       <c r="U10" t="n">
-        <v>0.000809942779596895</v>
+        <v>0.001223474508151412</v>
       </c>
       <c r="V10" t="n">
-        <v>0.003470316296443343</v>
+        <v>0.002427349099889398</v>
       </c>
       <c r="W10" t="n">
-        <v>0.001807330641895533</v>
+        <v>0.003977162763476372</v>
       </c>
       <c r="X10" t="n">
-        <v>0.004782644100487232</v>
+        <v>0.00321681797504425</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.002222185488790274</v>
+        <v>0.002821875037625432</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.002501707756891847</v>
+        <v>0.003564378479495645</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.00298143201507628</v>
+        <v>0.002724114106968045</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.0006454219110310078</v>
+        <v>0.0013820476597175</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.001565839629620314</v>
+        <v>0.0007787409704178572</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0004923063679598272</v>
+        <v>0.001114856102503836</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.001998615218326449</v>
+        <v>0.004632466938346624</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.001264531747438014</v>
+        <v>0.003033370710909367</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0008002696558833122</v>
+        <v>0.006510966923087835</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.00162030674982816</v>
+        <v>0.0003524896455928683</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.00196673022583127</v>
+        <v>0.006735620088875294</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.001280477503314614</v>
+        <v>0.0002776363398879766</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.00357401417568326</v>
+        <v>0.0005360236391425133</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.003112540580332279</v>
+        <v>0.004115661140531301</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0008487955783493817</v>
+        <v>0.0008695544674992561</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.00293960259296</v>
+        <v>0.004501442890614271</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.001680176006630063</v>
+        <v>0.0001880862982943654</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.003701107576489449</v>
+        <v>0.003034893423318863</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0006117210723459721</v>
+        <v>0.0001849990803748369</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.001688794349320233</v>
+        <v>0.001875778660178185</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.002318394370377064</v>
+        <v>0.001400086213834584</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.001083271810784936</v>
+        <v>0.0002494794316589832</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.02098497562110424</v>
+        <v>0.02280361764132977</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.001233982387930155</v>
+        <v>0.001542083919048309</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.003305185586214066</v>
+        <v>0.004784389864653349</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.002995004411786795</v>
+        <v>0.008822374977171421</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.00187951885163784</v>
+        <v>0.002147679682821035</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.0001443251385353506</v>
+        <v>0.001220382051542401</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.003993903286755085</v>
+        <v>0.003043768927454948</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.00118339667096734</v>
+        <v>0.0006038312567397952</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.00256014964543283</v>
+        <v>0.0007942402153275907</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.005321674980223179</v>
+        <v>0.0003401387366466224</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.006015641614794731</v>
+        <v>0.003403076436370611</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.00395767530426383</v>
+        <v>0.002020775806158781</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.01159981451928616</v>
+        <v>0.004030521027743816</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.001926892902702093</v>
+        <v>0.0009283794206567109</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.003151130164042115</v>
+        <v>0.0004293370293453336</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.005534520372748375</v>
+        <v>0.006651362869888544</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.0008637016289867461</v>
+        <v>0.0004078830243088305</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.002482493873685598</v>
+        <v>0.0004660645499825478</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.001806694432161748</v>
+        <v>0.003785209730267525</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.001665507559664547</v>
+        <v>0.001724759698845446</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.001382421934977174</v>
+        <v>0.002638134174048901</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.002871184144169092</v>
+        <v>0.006322681903839111</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.003021464915946126</v>
+        <v>0.0007307464256882668</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.00156379968393594</v>
+        <v>0.004786234349012375</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.001463583670556545</v>
+        <v>0.002964254235848784</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.002099159639328718</v>
+        <v>0.0003100811736658216</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.001628314726985991</v>
+        <v>2.650848182383925e-05</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.0113053061068058</v>
+        <v>0.01361096557229757</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.002574013313278556</v>
+        <v>0.0005399452638812363</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.00121979066170752</v>
+        <v>0.006306023336946964</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.001624275930225849</v>
+        <v>0.003370661521330476</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.002911630552262068</v>
+        <v>0.00323277828283608</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.0008942519198171794</v>
+        <v>0.00393117917701602</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0004371609538793564</v>
+        <v>0.0002062767744064331</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.001467360183596611</v>
+        <v>0.00224392581731081</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.857093932107091e-05</v>
+        <v>0.001196869648993015</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.00569989113137126</v>
+        <v>0.007263231556862593</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.002046610461547971</v>
+        <v>0.00151484296657145</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.002096587559208274</v>
+        <v>0.004141515120863914</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.001838491996750236</v>
+        <v>0.001740182633511722</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.001572297653183341</v>
+        <v>0.0009355724905617535</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.00202870718203485</v>
+        <v>0.0004461742646526545</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.001466165180318058</v>
+        <v>0.000713500427082181</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.001472495729103684</v>
+        <v>0.0008959965198300779</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.005774985533207655</v>
+        <v>0.003609171835705638</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.000656997668556869</v>
+        <v>0.01420072373002768</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.001357569126412272</v>
+        <v>0.004807186778634787</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.003920948598533869</v>
+        <v>0.006350643932819366</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.005955907981842756</v>
+        <v>0.003950906451791525</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.006278532557189465</v>
+        <v>0.002920215483754873</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.002800699090585113</v>
+        <v>0.003626916091889143</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.001972049241885543</v>
+        <v>0.0006705816485919058</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.002345280954614282</v>
+        <v>0.001278135925531387</v>
       </c>
       <c r="CV10" t="n">
-        <v>4.587231887853704e-05</v>
+        <v>0.0002561099827289581</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.005595562979578972</v>
+        <v>0.007073490880429745</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.002156871603801847</v>
+        <v>0.001498436438851058</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.003005341626703739</v>
+        <v>0.005205682478845119</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.002186577068641782</v>
+        <v>0.00123751733917743</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.001763991545885801</v>
+        <v>0.0007964971009641886</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.002072504255920649</v>
+        <v>0.000275921105640009</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.001884924946352839</v>
+        <v>0.0006348444730974734</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0009458224521949887</v>
+        <v>0.001241243910044432</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.002366889035329223</v>
+        <v>0.004357121884822845</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.007137762382626534</v>
+        <v>0.00376944849267602</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0006629519630223513</v>
+        <v>0.0009984583593904972</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.01029263529926538</v>
+        <v>0.006311891134828329</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.003378367749974132</v>
+        <v>0.004378463607281446</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0005009674350731075</v>
+        <v>0.003718587337061763</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.001349126570858061</v>
+        <v>0.003610443789511919</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0004634826327674091</v>
+        <v>0.006647073663771152</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.001986265182495117</v>
+        <v>0.002361010294407606</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.002448531799018383</v>
+        <v>9.702032548375428e-05</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.001337900408543646</v>
+        <v>0.003734502475708723</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0003212662995792925</v>
+        <v>0.001711762044578791</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.002149272477254272</v>
+        <v>0.0005576602416113019</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.003860908560454845</v>
+        <v>0.0008116826647892594</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.00155823165550828</v>
+        <v>0.001996865030378103</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.001748092006891966</v>
+        <v>0.003301397897303104</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.001978013198822737</v>
+        <v>0.003842710051685572</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.001429340103641152</v>
+        <v>0.005310262553393841</v>
       </c>
       <c r="DW10" t="n">
-        <v>3.590686537791044e-05</v>
+        <v>0.001325056189671159</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.001527266926132143</v>
+        <v>0.004360852297395468</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.00294253439642489</v>
+        <v>0.001359071582555771</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.0007340360898524523</v>
+        <v>0.001585487741976976</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.003837255761027336</v>
+        <v>0.004808828234672546</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.002052466152235866</v>
+        <v>0.00145542377140373</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.001228612032718956</v>
+        <v>0.0001631350023671985</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.0003952042607124895</v>
+        <v>0.009352682158350945</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.001557300565764308</v>
+        <v>0.005101463291794062</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.003419132204726338</v>
+        <v>0.001118956948630512</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.005381172988563776</v>
+        <v>0.002995011396706104</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.002803656505420804</v>
+        <v>0.0002897469676099718</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.002116062678396702</v>
+        <v>0.003386930795386434</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.001784130348823965</v>
+        <v>0.001878109527751803</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.001841151621192694</v>
+        <v>0.001662932918407023</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.002592487260699272</v>
+        <v>0.0006458408897742629</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.0003962893388234079</v>
+        <v>0.0006104562198743224</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0003517734003253281</v>
+        <v>0.002232625149190426</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0002166911726817489</v>
+        <v>0.0003751289914362133</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.004245306365191936</v>
+        <v>0.00378189655020833</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.001638318761251867</v>
+        <v>0.001943199429661036</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.002597828395664692</v>
+        <v>0.003176056314259768</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.002451258478686213</v>
+        <v>0.00277431053109467</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.005513104610145092</v>
+        <v>0.0003464006586000323</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.002952744718641043</v>
+        <v>0.002037519821897149</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.001980755478143692</v>
+        <v>0.0005059548420831561</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.001214029733091593</v>
+        <v>0.002662545070052147</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.000714220164809376</v>
+        <v>0.0008583160815760493</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.005606648977845907</v>
+        <v>0.0082762585952878</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.001225366722792387</v>
+        <v>0.001132571254856884</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.002815679414197803</v>
+        <v>0.005133033264428377</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.001963396556675434</v>
+        <v>0.0008259518654085696</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.001287406077608466</v>
+        <v>0.001652953447774053</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.00232892925851047</v>
+        <v>0.000874876044690609</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.001674545230343938</v>
+        <v>2.075731754302979e-05</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.001811653492040932</v>
+        <v>0.001663450850173831</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.001070998376235366</v>
+        <v>0.0003597487229853868</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.001987454481422901</v>
+        <v>0.002359371166676283</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.001014249864965677</v>
+        <v>0.001931724837049842</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.00443100742995739</v>
+        <v>0.00556033244356513</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.002589472336694598</v>
+        <v>5.554846575250849e-05</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.001215467695146799</v>
+        <v>0.001022707903757691</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.000839469488710165</v>
+        <v>0.00179457338526845</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.0007264767773449421</v>
+        <v>0.002797253429889679</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.00100331474095583</v>
+        <v>0.0005848316941410303</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.001319274655543268</v>
+        <v>0.00247187539935112</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.004382777493447065</v>
+        <v>0.001810307265259326</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.004874219186604023</v>
+        <v>0.001544841099530458</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.0002624376793392003</v>
+        <v>0.0001488709822297096</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.0005778712802566588</v>
+        <v>0.006411845330148935</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.001305157435126603</v>
+        <v>0.002633383963257074</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.0002614480326883495</v>
+        <v>0.0007954432512633502</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0008358116028830409</v>
+        <v>0.0006614344310946763</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.003242116887122393</v>
+        <v>0.005071793682873249</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.002910368144512177</v>
+        <v>0.001313895802013576</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.000323788815876469</v>
+        <v>0.003247893648222089</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.0008679182501509786</v>
+        <v>0.001653979765251279</v>
       </c>
       <c r="GB10" t="n">
-        <v>6.756233051419258e-05</v>
+        <v>0.003475639969110489</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.003223142353817821</v>
+        <v>0.003355255350470543</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.002779169473797083</v>
+        <v>0.00315138278529048</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.006852867547422647</v>
+        <v>0.005977844819426537</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.000245401228312403</v>
+        <v>0.002216032240539789</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.003052511950954795</v>
+        <v>0.0008908616728149354</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.06239230185747147</v>
+        <v>0.2120890766382217</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4775137305259705</v>
+        <v>0.5748030543327332</v>
       </c>
       <c r="C11" t="n">
-        <v>0.03997117653489113</v>
+        <v>0.03028074465692043</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3258570432662964</v>
+        <v>0.01577985659241676</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07773273438215256</v>
+        <v>0.2258669883012772</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3516118228435516</v>
+        <v>0.4054436385631561</v>
       </c>
       <c r="G11" t="n">
-        <v>0.02235058695077896</v>
+        <v>0.0621139295399189</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1191519200801849</v>
+        <v>0.08796869218349457</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1022151336073875</v>
+        <v>0.1038335338234901</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1349563896656036</v>
+        <v>0.0881277322769165</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3723869621753693</v>
+        <v>0.8055158257484436</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01225994434207678</v>
+        <v>0.07870479673147202</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2927703261375427</v>
+        <v>0.193349152803421</v>
       </c>
       <c r="N11" t="n">
-        <v>0.06845726072788239</v>
+        <v>0.1108063459396362</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3948026299476624</v>
+        <v>0.4855723083019257</v>
       </c>
       <c r="P11" t="n">
-        <v>0.02084315195679665</v>
+        <v>0.1990048289299011</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.002122536301612854</v>
+        <v>0.2223776280879974</v>
       </c>
       <c r="R11" t="n">
-        <v>0.08778797835111618</v>
+        <v>0.1091251447796822</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0263722762465477</v>
+        <v>0.08445632457733154</v>
       </c>
       <c r="T11" t="n">
-        <v>0.05278322473168373</v>
+        <v>0.2081972509622574</v>
       </c>
       <c r="U11" t="n">
-        <v>0.05565597116947174</v>
+        <v>0.01233560778200626</v>
       </c>
       <c r="V11" t="n">
-        <v>0.06240377947688103</v>
+        <v>0.255946159362793</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03730044513940811</v>
+        <v>0.1583144962787628</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02254104055464268</v>
+        <v>0.02569497749209404</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.06047048792243004</v>
+        <v>0.02764363586902618</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.04834572225809097</v>
+        <v>0.1202315017580986</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.05994464829564095</v>
+        <v>0.04013232886791229</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01299616321921349</v>
+        <v>0.08390168845653534</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.06295590102672577</v>
+        <v>0.0711100846529007</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.03153176978230476</v>
+        <v>0.03901832923293114</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.003793851472437382</v>
+        <v>0.1514804065227509</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02413059026002884</v>
+        <v>0.4853640794754028</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01557295396924019</v>
+        <v>0.2143542766571045</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.03768769279122353</v>
+        <v>0.01872182637453079</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0216086283326149</v>
+        <v>0.1772659718990326</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.01961969397962093</v>
+        <v>0.03596460074186325</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0550069734454155</v>
+        <v>0.01534144952893257</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.07799077033996582</v>
+        <v>0.1472852826118469</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.035630002617836</v>
+        <v>0.03067555651068687</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.02521161735057831</v>
+        <v>0.148701548576355</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.02667383290827274</v>
+        <v>0.04793530702590942</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.05666913092136383</v>
+        <v>0.1972402334213257</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.01042989082634449</v>
+        <v>0.08766498416662216</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.04052666947245598</v>
+        <v>0.2534637749195099</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.05684990063309669</v>
+        <v>0.02720451354980469</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.02959808520972729</v>
+        <v>0.04873557016253471</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.3145270049571991</v>
+        <v>0.8990334868431091</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.03008307889103889</v>
+        <v>0.08519862592220306</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.08142591267824173</v>
+        <v>0.07884898781776428</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.03591533750295639</v>
+        <v>0.006093695759773254</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.1723142713308334</v>
+        <v>0.3595900237560272</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.02061637304723263</v>
+        <v>0.01968299224972725</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.04027825221419334</v>
+        <v>0.04738799482584</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.08853109180927277</v>
+        <v>0.0361999124288559</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.05838973075151443</v>
+        <v>0.029747374355793</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.08109086751937866</v>
+        <v>0.1470955461263657</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.1343742161989212</v>
+        <v>0.01621823757886887</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.07625028491020203</v>
+        <v>0.06261874735355377</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.1447088867425919</v>
+        <v>0.2954891324043274</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.08499904721975327</v>
+        <v>0.1355316638946533</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.04402821883559227</v>
+        <v>0.09986476600170135</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.08271673321723938</v>
+        <v>0.09880524128675461</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.05821149796247482</v>
+        <v>0.03444273769855499</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.002689192071557045</v>
+        <v>0.005964227020740509</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.07734065502882004</v>
+        <v>0.1556953489780426</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.05564424768090248</v>
+        <v>0.09043628722429276</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.04395483806729317</v>
+        <v>0.05607448890805244</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.03341106697916985</v>
+        <v>0.1679327487945557</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.005296962335705757</v>
+        <v>0.05875489115715027</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.04178690910339355</v>
+        <v>0.1219240874052048</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.02816553972661495</v>
+        <v>0.02861753292381763</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.005362097173929214</v>
+        <v>0.03345335647463799</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.02586342021822929</v>
+        <v>0.08847746253013611</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.1651022881269455</v>
+        <v>0.5396659970283508</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.08017192035913467</v>
+        <v>0.05121759325265884</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.1006928384304047</v>
+        <v>0.1642089188098907</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.05344735458493233</v>
+        <v>3.133714199066162e-05</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.08925934135913849</v>
+        <v>0.2546413540840149</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.02444958686828613</v>
+        <v>0.08935858309268951</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.03028369136154652</v>
+        <v>0.05805253237485886</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.06991073489189148</v>
+        <v>0.07562978565692902</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.01021907851099968</v>
+        <v>0.05882038548588753</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.07450780272483826</v>
+        <v>0.1952795088291168</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.06605113297700882</v>
+        <v>0.003066600300371647</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0431252047419548</v>
+        <v>0.01129631511867046</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.02695345133543015</v>
+        <v>0.02134345471858978</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.06012680381536484</v>
+        <v>0.136384442448616</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.02410006895661354</v>
+        <v>0.0472920760512352</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0291234627366066</v>
+        <v>0.01860745437443256</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.03650611266493797</v>
+        <v>0.04203232377767563</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.07064752280712128</v>
+        <v>0.20003941655159</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.001811021007597446</v>
+        <v>0.5179702639579773</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.01708073168992996</v>
+        <v>0.02664540149271488</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.03676712512969971</v>
+        <v>0.2514471709728241</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.02936184965074062</v>
+        <v>0.2699108123779297</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.01898211613297462</v>
+        <v>0.3568575084209442</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.08387894928455353</v>
+        <v>0.08629579842090607</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.06464227288961411</v>
+        <v>0.04016443341970444</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.008027065545320511</v>
+        <v>0.1439289599657059</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0008927257731556892</v>
+        <v>0.01569603383541107</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.06451572477817535</v>
+        <v>0.1840652376413345</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.06954891234636307</v>
+        <v>0.01209717616438866</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.06539703160524368</v>
+        <v>0.02919338829815388</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.02378853783011436</v>
+        <v>0.05073638260364532</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.06825098395347595</v>
+        <v>0.1179429367184639</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.02425219491124153</v>
+        <v>0.01449955441057682</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.05368014425039291</v>
+        <v>0.02352141588926315</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.01692923717200756</v>
+        <v>0.06681796163320541</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.02662784792482853</v>
+        <v>0.01950240880250931</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.02830357477068901</v>
+        <v>0.002330349758267403</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.01626577042043209</v>
+        <v>0.05455005913972855</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.1442970335483551</v>
+        <v>0.1059942990541458</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.001822483260184526</v>
+        <v>0.2713199555873871</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.02530935779213905</v>
+        <v>0.01888924837112427</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.06275463104248047</v>
+        <v>0.07945071160793304</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.05341711267828941</v>
+        <v>0.09145951271057129</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.02096093073487282</v>
+        <v>0.09780849516391754</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.001078092958778143</v>
+        <v>0.003773439675569534</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.008718441240489483</v>
+        <v>0.06661752611398697</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.03783819824457169</v>
+        <v>0.05074405670166016</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.03583440557122231</v>
+        <v>0.1634116768836975</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.01280797459185123</v>
+        <v>0.03896017372608185</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.004218555986881256</v>
+        <v>0.06385551393032074</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.03928002715110779</v>
+        <v>0.07976351678371429</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.007189773488789797</v>
+        <v>0.04021228849887848</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.06736589968204498</v>
+        <v>0.01099521666765213</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.01324041467159986</v>
+        <v>0.1459628045558929</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.006158202420920134</v>
+        <v>0.05810927599668503</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.09473182260990143</v>
+        <v>0.03287889808416367</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.01798520423471928</v>
+        <v>0.04440376162528992</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01408624276518822</v>
+        <v>0.03669269010424614</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.02015507221221924</v>
+        <v>0.05603629350662231</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.01173909194767475</v>
+        <v>0.05192980170249939</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.03672982379794121</v>
+        <v>0.05365990847349167</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.0327904000878334</v>
+        <v>0.2536773681640625</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.03389495238661766</v>
+        <v>0.02341918647289276</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.05409074574708939</v>
+        <v>0.05253185331821442</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.05245408415794373</v>
+        <v>0.02840717136859894</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.006175078917294741</v>
+        <v>0.02826191112399101</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.002555401064455509</v>
+        <v>0.1306861639022827</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.06139381974935532</v>
+        <v>0.01218164712190628</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.03982513025403023</v>
+        <v>0.001727608032524586</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.007719691842794418</v>
+        <v>0.08197823166847229</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0138073991984129</v>
+        <v>0.06300449371337891</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.003245741128921509</v>
+        <v>0.003006275743246078</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.03290591388940811</v>
+        <v>0.05042228847742081</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.06252787262201309</v>
+        <v>0.02205231413245201</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.06040818616747856</v>
+        <v>0.02351711317896843</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.00646737776696682</v>
+        <v>0.1460592448711395</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.0598708800971508</v>
+        <v>0.08263988792896271</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.05992137640714645</v>
+        <v>0.0569281280040741</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.1031137183308601</v>
+        <v>0.05963462218642235</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.00943000428378582</v>
+        <v>0.01793661713600159</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.003827946726232767</v>
+        <v>0.06148998439311981</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0583166629076004</v>
+        <v>0.209320142865181</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.05476232618093491</v>
+        <v>0.0001208616886287928</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.06239199638366699</v>
+        <v>0.0127430371940136</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.03350201994180679</v>
+        <v>0.07992380857467651</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.05527964234352112</v>
+        <v>0.1341948062181473</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.04460403695702553</v>
+        <v>0.06652840971946716</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.03505676239728928</v>
+        <v>0.01433672849088907</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.03605581820011139</v>
+        <v>0.07434119284152985</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.01146515086293221</v>
+        <v>0.008580442517995834</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.04139905422925949</v>
+        <v>0.2005354911088943</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.06121933087706566</v>
+        <v>0.009868517518043518</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.07847204804420471</v>
+        <v>0.1716862320899963</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.01200236193835735</v>
+        <v>0.1265259385108948</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.03826349228620529</v>
+        <v>0.1403025537729263</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.03606424480676651</v>
+        <v>0.1147526279091835</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.02106244117021561</v>
+        <v>0.1940292418003082</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.03744634985923767</v>
+        <v>0.1144469082355499</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.02998076938092709</v>
+        <v>0.0151805579662323</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.08948909491300583</v>
+        <v>0.3088214099407196</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.03663917630910873</v>
+        <v>0.005235984921455383</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.1127233877778053</v>
+        <v>0.3743999898433685</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.03677715733647346</v>
+        <v>0.12418382614851</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.05654402822256088</v>
+        <v>0.06042198836803436</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.08893405646085739</v>
+        <v>0.1520688235759735</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.02938944101333618</v>
+        <v>0.1485798060894012</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.004035155288875103</v>
+        <v>0.1031807959079742</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.08910998702049255</v>
+        <v>0.1278917193412781</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.02057969011366367</v>
+        <v>0.07563488185405731</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.03397370874881744</v>
+        <v>0.04250341653823853</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.01932745613157749</v>
+        <v>0.1417197734117508</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.001611866056919098</v>
+        <v>0.01271121203899384</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.02767490595579147</v>
+        <v>0.07461695373058319</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.2359067648649216</v>
+        <v>0.1645174026489258</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.009840585291385651</v>
+        <v>0.04007738456130028</v>
       </c>
       <c r="GG11" t="n">
-        <v>0.01163219567388296</v>
+        <v>0.157390758395195</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.6210363507270813</v>
+        <v>0.1362040042877197</v>
       </c>
       <c r="B12" t="n">
-        <v>3.084881782531738</v>
+        <v>0.2931225895881653</v>
       </c>
       <c r="C12" t="n">
-        <v>0.001793771982192993</v>
+        <v>0.01033314317464828</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2168883234262466</v>
+        <v>0.139729380607605</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7192234396934509</v>
+        <v>0.07097460329532623</v>
       </c>
       <c r="F12" t="n">
-        <v>0.04804230108857155</v>
+        <v>0.179429903626442</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02585422992706299</v>
+        <v>0.07768286764621735</v>
       </c>
       <c r="H12" t="n">
-        <v>0.2220072448253632</v>
+        <v>0.06236641854047775</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2726484537124634</v>
+        <v>0.1599952131509781</v>
       </c>
       <c r="J12" t="n">
-        <v>0.09111317992210388</v>
+        <v>0.1128124222159386</v>
       </c>
       <c r="K12" t="n">
-        <v>2.649087905883789</v>
+        <v>0.3997197151184082</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1149931475520134</v>
+        <v>0.0792594775557518</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01689071953296661</v>
+        <v>0.136367604136467</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6462322473526001</v>
+        <v>0.1083468794822693</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06191601976752281</v>
+        <v>0.1997831761837006</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2746526896953583</v>
+        <v>0.05151227116584778</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2742573022842407</v>
+        <v>0.08761005103588104</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5024678111076355</v>
+        <v>0.2434724569320679</v>
       </c>
       <c r="S12" t="n">
-        <v>0.316215842962265</v>
+        <v>0.0005895532667636871</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6743816137313843</v>
+        <v>0.03481168672442436</v>
       </c>
       <c r="U12" t="n">
-        <v>0.05559059232473373</v>
+        <v>0.0006680972874164581</v>
       </c>
       <c r="V12" t="n">
-        <v>0.07103681564331055</v>
+        <v>0.03784525394439697</v>
       </c>
       <c r="W12" t="n">
-        <v>0.003023442346602678</v>
+        <v>0.1789345890283585</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3708235025405884</v>
+        <v>0.04859713092446327</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0841631144285202</v>
+        <v>0.07774963974952698</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.4974862039089203</v>
+        <v>0.01071781478822231</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.1832580715417862</v>
+        <v>0.001510283909738064</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.2265720963478088</v>
+        <v>0.02041034027934074</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.286051332950592</v>
+        <v>0.1331594735383987</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.6189700961112976</v>
+        <v>0.06584224849939346</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.1699221432209015</v>
+        <v>0.09035535156726837</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.4923559129238129</v>
+        <v>0.213114857673645</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.2886625528335571</v>
+        <v>0.04614993929862976</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.2019239366054535</v>
+        <v>0.02511903457343578</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.003138527274131775</v>
+        <v>0.04644647240638733</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.08031757175922394</v>
+        <v>0.04594912007451057</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.5553463101387024</v>
+        <v>0.03006809204816818</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.4050622582435608</v>
+        <v>0.0882561206817627</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.005509369075298309</v>
+        <v>0.1039755269885063</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.4421018362045288</v>
+        <v>0.02662450075149536</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.3801522254943848</v>
+        <v>0.234326958656311</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.3480143547058105</v>
+        <v>0.05225067213177681</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.04988615214824677</v>
+        <v>0.03248519450426102</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.06323389708995819</v>
+        <v>0.1282622814178467</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.1538877189159393</v>
+        <v>0.02518399432301521</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.3592904806137085</v>
+        <v>0.08664276450872421</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.837326407432556</v>
+        <v>0.1607974916696548</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.421075850725174</v>
+        <v>0.02628924697637558</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.4424105286598206</v>
+        <v>0.006812196224927902</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.2426373064517975</v>
+        <v>0.3047339618206024</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.4488123059272766</v>
+        <v>0.05187632888555527</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.6983082294464111</v>
+        <v>0.008833328261971474</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.1394527852535248</v>
+        <v>0.122991755604744</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.075572669506073</v>
+        <v>0.07310783863067627</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.5105975866317749</v>
+        <v>0.1131850033998489</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.7537487149238586</v>
+        <v>0.1673520505428314</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.6288542747497559</v>
+        <v>0.07997690141201019</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.1663847863674164</v>
+        <v>0.1262141764163971</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.2968908548355103</v>
+        <v>0.2830597162246704</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.2102456837892532</v>
+        <v>0.1764113456010818</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.6608889102935791</v>
+        <v>0.06238386780023575</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.172759935259819</v>
+        <v>0.205536887049675</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.1612317860126495</v>
+        <v>0.07668371498584747</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.3558110892772675</v>
+        <v>0.01232181675732136</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.3719953596591949</v>
+        <v>0.0737052857875824</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.0930761992931366</v>
+        <v>0.01917109079658985</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.2248188853263855</v>
+        <v>0.02854372747242451</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.4741796851158142</v>
+        <v>0.2180142253637314</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.5981764793395996</v>
+        <v>0.00872756727039814</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.3528130650520325</v>
+        <v>0.02771923318505287</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.3177075684070587</v>
+        <v>0.07484529167413712</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.1622390449047089</v>
+        <v>0.01760229095816612</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.1955883800983429</v>
+        <v>0.04371001943945885</v>
       </c>
       <c r="BV12" t="n">
-        <v>1.256551861763</v>
+        <v>0.05053341388702393</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.2652512788772583</v>
+        <v>0.03765840455889702</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.1141249537467957</v>
+        <v>0.002141300588846207</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.07269394397735596</v>
+        <v>0.1777765899896622</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.1897494196891785</v>
+        <v>0.106386810541153</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.01064217835664749</v>
+        <v>0.103418156504631</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.1087504997849464</v>
+        <v>0.04561777412891388</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.007260244339704514</v>
+        <v>0.05571728944778442</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.1514151692390442</v>
+        <v>0.06181440874934196</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.5150463581085205</v>
+        <v>0.05525371432304382</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.09509006142616272</v>
+        <v>0.02108700200915337</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.1086369305849075</v>
+        <v>0.01833521015942097</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.03979034349322319</v>
+        <v>0.04710528254508972</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.01999048888683319</v>
+        <v>0.06585123389959335</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.07345014065504074</v>
+        <v>0.02261818945407867</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.08882627636194229</v>
+        <v>0.002144637517631054</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.1546290516853333</v>
+        <v>0.03041807003319263</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.6952013969421387</v>
+        <v>0.0346473902463913</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.3589754402637482</v>
+        <v>0.05969979241490364</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.08724144846200943</v>
+        <v>0.0505804643034935</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.4057481586933136</v>
+        <v>0.02558869123458862</v>
       </c>
       <c r="CQ12" t="n">
-        <v>1.762102127075195</v>
+        <v>0.03871573135256767</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.04723547771573067</v>
+        <v>0.2266261279582977</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.1720583140850067</v>
+        <v>0.04833657294511795</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.3112317621707916</v>
+        <v>0.09635896235704422</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.4167501330375671</v>
+        <v>0.04366984218358994</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.1386246234178543</v>
+        <v>0.05094164609909058</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.4838724732398987</v>
+        <v>0.05182557553052902</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.2364494651556015</v>
+        <v>0.01183745823800564</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.1025603041052818</v>
+        <v>0.02739953808486462</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.1890183538198471</v>
+        <v>0.03249605000019073</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.005719392560422421</v>
+        <v>0.07543171942234039</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.006334485486149788</v>
+        <v>0.01479197572916746</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.071080282330513</v>
+        <v>0.02866754308342934</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.1488631218671799</v>
+        <v>0.02397190034389496</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.4762522578239441</v>
+        <v>0.01483738049864769</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.851125180721283</v>
+        <v>0.002013197168707848</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.1925594955682755</v>
+        <v>0.1746192276477814</v>
       </c>
       <c r="DH12" t="n">
-        <v>1.168369770050049</v>
+        <v>0.05879461020231247</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.1670258790254593</v>
+        <v>0.03285419195890427</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.701443612575531</v>
+        <v>0.06473736464977264</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.02113917469978333</v>
+        <v>0.03935607522726059</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.0927412360906601</v>
+        <v>0.05352093651890755</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.2115118205547333</v>
+        <v>0.1724323928356171</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.07416039705276489</v>
+        <v>0.03336522728204727</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.1637503951787949</v>
+        <v>0.07843117415904999</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.2064395844936371</v>
+        <v>0.0004708915948867798</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.163597047328949</v>
+        <v>0.07018361240625381</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.4565722048282623</v>
+        <v>0.06916968524456024</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.04862621426582336</v>
+        <v>0.1049379333853722</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.493719220161438</v>
+        <v>0.06699880212545395</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.2342701554298401</v>
+        <v>0.04941922426223755</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.01235826872289181</v>
+        <v>0.1022385060787201</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.124605804681778</v>
+        <v>0.02458557672798634</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.9700543880462646</v>
+        <v>0.1239684522151947</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.1493907570838928</v>
+        <v>0.02401276491582394</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.2910878658294678</v>
+        <v>0.03742660954594612</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.4136559963226318</v>
+        <v>0.153206467628479</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.03710832446813583</v>
+        <v>0.06378671526908875</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.1303586661815643</v>
+        <v>0.03743379563093185</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.2775605320930481</v>
+        <v>0.186793252825737</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.273174911737442</v>
+        <v>0.02636455371975899</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.3792506754398346</v>
+        <v>0.03107642382383347</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.3574309647083282</v>
+        <v>0.03727244958281517</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.05618356168270111</v>
+        <v>0.01236909721046686</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.1858528852462769</v>
+        <v>0.03905457258224487</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.2075646072626114</v>
+        <v>0.008354190737009048</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.03623557463288307</v>
+        <v>0.0721968337893486</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.197004109621048</v>
+        <v>0.00320053193718195</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.0829429104924202</v>
+        <v>0.009841182269155979</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.04044549912214279</v>
+        <v>0.1004204452037811</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.01246899366378784</v>
+        <v>0.03732642531394958</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.04601854830980301</v>
+        <v>0.01906511746346951</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.4821224212646484</v>
+        <v>0.06460977345705032</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.1952608823776245</v>
+        <v>0.01134569011628628</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.2361821830272675</v>
+        <v>0.001597016584128141</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.2858168482780457</v>
+        <v>0.07513736188411713</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.2458271086215973</v>
+        <v>0.04621033743023872</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.2859359085559845</v>
+        <v>0.01349147781729698</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.1812542825937271</v>
+        <v>0.01365149952471256</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.1771570891141891</v>
+        <v>0.07126790285110474</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.5205134153366089</v>
+        <v>0.0580856092274189</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.1287244111299515</v>
+        <v>0.01995630376040936</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.060902439057827</v>
+        <v>0.008598247542977333</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.1646067351102829</v>
+        <v>0.01214533671736717</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.08125506341457367</v>
+        <v>0.05708976835012436</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.06986752152442932</v>
+        <v>0.009952342137694359</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.0480257160961628</v>
+        <v>0.01951118372380733</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.1790652275085449</v>
+        <v>0.04984349012374878</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.1302095502614975</v>
+        <v>0.02414745837450027</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.2003283500671387</v>
+        <v>0.08750759065151215</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.2531380355358124</v>
+        <v>0.03119419515132904</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.1026039496064186</v>
+        <v>0.02384265884757042</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.2017216235399246</v>
+        <v>0.01919877901673317</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.2851121425628662</v>
+        <v>0.02528316713869572</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.2983740270137787</v>
+        <v>0.04766213148832321</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.1449934989213943</v>
+        <v>0.06551670283079147</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.01918060705065727</v>
+        <v>0.1351235657930374</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.05750198662281036</v>
+        <v>0.1134765893220901</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.04093743860721588</v>
+        <v>0.1154326647520065</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.3335252404212952</v>
+        <v>0.1930466592311859</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.2063997983932495</v>
+        <v>0.1967207491397858</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.3416220545768738</v>
+        <v>0.2003787457942963</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.01789044588804245</v>
+        <v>0.08502107858657837</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.2188222110271454</v>
+        <v>0.01083766669034958</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.07680967450141907</v>
+        <v>0.1140288412570953</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.1382395476102829</v>
+        <v>0.07734556496143341</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.487260103225708</v>
+        <v>0.01981191337108612</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.03438343480229378</v>
+        <v>0.04545122385025024</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.01862826198339462</v>
+        <v>0.005602177232503891</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.1570651829242706</v>
+        <v>0.0394548699259758</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.5746109485626221</v>
+        <v>0.06801660358905792</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.4971432089805603</v>
+        <v>0.1549521684646606</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.363138347864151</v>
+        <v>0.0578526072204113</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.02532966621220112</v>
+        <v>0.06014030799269676</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.1190427020192146</v>
+        <v>0.08133815973997116</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.0004423977225087583</v>
+        <v>0.0002450106258038431</v>
       </c>
       <c r="B13" t="n">
-        <v>0.002720593474805355</v>
+        <v>0.003236538032069802</v>
       </c>
       <c r="C13" t="n">
-        <v>0.001103228190913796</v>
+        <v>0.000357689248630777</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0008038835367187858</v>
+        <v>0.0004723120655398816</v>
       </c>
       <c r="E13" t="n">
-        <v>1.234703086083755e-05</v>
+        <v>0.001673977938480675</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0001681346038822085</v>
+        <v>0.0003979566099587828</v>
       </c>
       <c r="G13" t="n">
-        <v>5.426781717687845e-05</v>
+        <v>0.0002024792192969471</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0005826178239658475</v>
+        <v>0.0003884868929162621</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0007358287693932652</v>
+        <v>0.0003733296762220562</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0004009778203908354</v>
+        <v>0.0002569836215116084</v>
       </c>
       <c r="K13" t="n">
-        <v>0.002035234123468399</v>
+        <v>0.004267968237400055</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0006773346103727818</v>
+        <v>0.0002998971031047404</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0008397717028856277</v>
+        <v>0.001112241763621569</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0004919846542179585</v>
+        <v>0.002032986609265208</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0002769131679087877</v>
+        <v>0.0004141596728004515</v>
       </c>
       <c r="P13" t="n">
-        <v>5.04566851304844e-05</v>
+        <v>0.0002244926581624895</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.0001091496451408602</v>
+        <v>0.0003274741466157138</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0004270084027666599</v>
+        <v>0.0004623923450708389</v>
       </c>
       <c r="S13" t="n">
-        <v>4.670709131460171e-06</v>
+        <v>0.0001197524543385953</v>
       </c>
       <c r="T13" t="n">
-        <v>0.000413580855820328</v>
+        <v>0.0004382458864711225</v>
       </c>
       <c r="U13" t="n">
-        <v>0.000163715667440556</v>
+        <v>0.0003314686473459005</v>
       </c>
       <c r="V13" t="n">
-        <v>2.568276249803603e-05</v>
+        <v>0.0004832345293834805</v>
       </c>
       <c r="W13" t="n">
-        <v>2.474414941389114e-05</v>
+        <v>0.0003029127838090062</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0009112699190154672</v>
+        <v>3.366316741448827e-05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.0001216631280840375</v>
+        <v>0.0001444914232706651</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.0001896623871289194</v>
+        <v>0.0002455536741763353</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.000143599885632284</v>
+        <v>0.0005659215385094285</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.0001283975871047005</v>
+        <v>0.0001184653519885615</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.0007151676691137254</v>
+        <v>0.0002966610190924257</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.0003514423733577132</v>
+        <v>0.000317651400109753</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.000192163250176236</v>
+        <v>0.0003382008871994913</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0002007869188673794</v>
+        <v>0.0004576205974444747</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.382034916896373e-05</v>
+        <v>0.0004058428457938135</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.0001579255767865106</v>
+        <v>2.556684194132686e-06</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.0002659213496372104</v>
+        <v>0.0004191803163848817</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0001451201969757676</v>
+        <v>0.0003861683362629265</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0001853542780736461</v>
+        <v>7.99411500338465e-05</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.0006246585980989039</v>
+        <v>0.001070568105205894</v>
       </c>
       <c r="AM13" t="n">
-        <v>4.412811904330738e-06</v>
+        <v>0.0002050090988632292</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.0001417546300217509</v>
+        <v>0.000320464139804244</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.0001810684188967571</v>
+        <v>0.00035134531208314</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.769903797656298e-05</v>
+        <v>0.000158472714247182</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.554188202135265e-06</v>
+        <v>0.0002333738812012598</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.990451710298657e-05</v>
+        <v>0.0002724775695241988</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.000391546287573874</v>
+        <v>0.0001328841026406735</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.0001188768219435588</v>
+        <v>0.0002223027113359421</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.002328423084691167</v>
+        <v>0.003495169803500175</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.0003995274018961936</v>
+        <v>0.0004740735748782754</v>
       </c>
       <c r="AW13" t="n">
-        <v>8.608817734057084e-05</v>
+        <v>0.0001540144585305825</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.0007660094415768981</v>
+        <v>0.0002889074676204473</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.0002923213760368526</v>
+        <v>0.0001296220143558457</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.0002997444535139948</v>
+        <v>2.301577478647232e-05</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0006079791928641498</v>
+        <v>0.0002579946594778448</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.0002285741793457419</v>
+        <v>3.4626733395271e-05</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.0001077863416867331</v>
+        <v>0.0004929127753712237</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.0003140184562653303</v>
+        <v>0.000747132464312017</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.0006933818804100156</v>
+        <v>0.0006058250437490642</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.0003370646736584604</v>
+        <v>0.0004457584582269192</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.001279184129089117</v>
+        <v>0.00123885425273329</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.0005237337318249047</v>
+        <v>0.0002570256183389574</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.0001986755232792348</v>
+        <v>0.0001154236524598673</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.0001522961392765865</v>
+        <v>0.0002697730087675154</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.0004520810325630009</v>
+        <v>0.0001138289662776515</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0007226244197227061</v>
+        <v>7.418821041937917e-05</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0002240711328340694</v>
+        <v>0.0002640752063598484</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.0003448037605267018</v>
+        <v>0.0002144160971511155</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.068224082700908e-05</v>
+        <v>6.083232801756822e-05</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.001103774178773165</v>
+        <v>0.0007668234757147729</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0003407956101000309</v>
+        <v>0.0001835228322306648</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.0005624489858746529</v>
+        <v>0.000706886756233871</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.0008369488641619682</v>
+        <v>0.0002262792258989066</v>
       </c>
       <c r="BT13" t="n">
-        <v>3.626850229920819e-05</v>
+        <v>0.000309248804114759</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.0001595063804415986</v>
+        <v>0.0005845497362315655</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.001099388464353979</v>
+        <v>0.00220569921657443</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.0007216322119347751</v>
+        <v>0.0001521356170997024</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.0001738216378726065</v>
+        <v>0.0004758829600177705</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.0008294074796140194</v>
+        <v>0.0003003578458447009</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.0007744083995930851</v>
+        <v>3.53202449332457e-06</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.0003060206072404981</v>
+        <v>0.0003570128174033016</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.071644798386842e-05</v>
+        <v>2.648652298375964e-05</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0002687209052965045</v>
+        <v>0.0003632494772318751</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.0002113850496243685</v>
+        <v>3.86036372219678e-05</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.0004899601917713881</v>
+        <v>0.001207651570439339</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.647373548825271e-05</v>
+        <v>0.0002166357589885592</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0001247965556103736</v>
+        <v>0.0001571033499203622</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.0001963181712199003</v>
+        <v>0.0002355794131290168</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.0001289905194425955</v>
+        <v>0.0003124595095869154</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.0002441697288304567</v>
+        <v>6.677105557173491e-05</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.0001010914274957031</v>
+        <v>0.0001424939691787586</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.0001843692880356684</v>
+        <v>0.0001393648126395419</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.0005792363663204014</v>
+        <v>0.0005993755767121911</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.0005459861131384969</v>
+        <v>0.002204183023422956</v>
       </c>
       <c r="CO13" t="n">
-        <v>0.0002599525905679911</v>
+        <v>0.0003755601937882602</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.0003621659707278013</v>
+        <v>0.0009763967827893794</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.0004079086647834629</v>
+        <v>0.0001562947145430371</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.0001468673290219158</v>
+        <v>0.000321996834827587</v>
       </c>
       <c r="CS13" t="n">
-        <v>8.145933679770678e-05</v>
+        <v>0.0001269524072995409</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.362729330547154e-06</v>
+        <v>0.0001077429551514797</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.000269106007181108</v>
+        <v>4.346938658272848e-05</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.0002351995935896412</v>
+        <v>0.0001526102132629603</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.000414143200032413</v>
+        <v>0.001178776612505317</v>
       </c>
       <c r="CX13" t="n">
-        <v>5.038538802182302e-06</v>
+        <v>0.00015113408153411</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.000126938073663041</v>
+        <v>0.0002264435461256653</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.000186411605682224</v>
+        <v>0.0001513039896963164</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.0001813182752812281</v>
+        <v>0.0002959198027383536</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.0002666646905709058</v>
+        <v>1.257925396203063e-05</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.549780037952587e-05</v>
+        <v>0.0001351135579170659</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.0001980165397981182</v>
+        <v>0.0002646770444698632</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.0001504468091297895</v>
+        <v>0.0001861317432485521</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.0006821585702709854</v>
+        <v>0.000618719554040581</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.0002645894710440189</v>
+        <v>5.217637226451188e-05</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.001001633238047361</v>
+        <v>3.587500395951793e-05</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.001208543428219855</v>
+        <v>0.0003401664725970477</v>
       </c>
       <c r="DJ13" t="n">
-        <v>7.726356125203893e-05</v>
+        <v>0.00120445538777858</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.0001139372398029082</v>
+        <v>0.0001094647886930034</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0003297520743217319</v>
+        <v>1.314302971877623e-05</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.000227872165851295</v>
+        <v>0.0002479111135471612</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.0001336927380179986</v>
+        <v>4.953680036123842e-05</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.000146778256748803</v>
+        <v>0.000703807978425175</v>
       </c>
       <c r="DP13" t="n">
-        <v>2.371630762354471e-05</v>
+        <v>0.0001874751760624349</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.0003387305187061429</v>
+        <v>0.0004426677478477359</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.0001936327898874879</v>
+        <v>4.728763087769039e-05</v>
       </c>
       <c r="DS13" t="n">
-        <v>9.623401274438947e-05</v>
+        <v>0.0001138957450166345</v>
       </c>
       <c r="DT13" t="n">
-        <v>4.124718543607742e-06</v>
+        <v>7.447953976225108e-05</v>
       </c>
       <c r="DU13" t="n">
-        <v>6.807074532844126e-05</v>
+        <v>0.0005952881765551865</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.0002454408095218241</v>
+        <v>0.0004658087273128331</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.0002593372773844749</v>
+        <v>0.0003349392209202051</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.0002013613993767649</v>
+        <v>0.0003905654302798212</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.545740663772449e-05</v>
+        <v>2.155752372345887e-05</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.0001403209316777065</v>
+        <v>0.0001233070361195132</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.0005185318877920508</v>
+        <v>3.958490196964704e-06</v>
       </c>
       <c r="EB13" t="n">
-        <v>7.204434950836003e-07</v>
+        <v>0.0008922339184209704</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.0001608385937288404</v>
+        <v>0.000212106533581391</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.0003720436943694949</v>
+        <v>0.0007893028086982667</v>
       </c>
       <c r="EE13" t="n">
-        <v>9.326876170234755e-05</v>
+        <v>0.0003269183216616511</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.0001450067211408168</v>
+        <v>0.0002444504061713815</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0003073281841352582</v>
+        <v>0.0007916952599771321</v>
       </c>
       <c r="EH13" t="n">
-        <v>4.001444176537916e-05</v>
+        <v>0.0001666764437686652</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.000173736727447249</v>
+        <v>9.860045975074172e-05</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.000158255803398788</v>
+        <v>5.408348079072312e-05</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.0001615860819583759</v>
+        <v>0.0004628344322554767</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.0004516593762673438</v>
+        <v>8.549086487619206e-06</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.0001602527336217463</v>
+        <v>0.0001625923614483327</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.0002287793322466314</v>
+        <v>7.476126484107226e-05</v>
       </c>
       <c r="EO13" t="n">
-        <v>3.009736974490806e-05</v>
+        <v>0.000111471235868521</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.000520499364938587</v>
+        <v>0.0007967419223859906</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.0002027924929279834</v>
+        <v>9.408282494405285e-06</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.0001073276944225654</v>
+        <v>7.541378727182746e-05</v>
       </c>
       <c r="ES13" t="n">
-        <v>8.699685167812277e-06</v>
+        <v>0.00023379955382552</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.000420468277297914</v>
+        <v>5.587321356870234e-05</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.0005507127498276532</v>
+        <v>4.165876816841774e-05</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.0004111688758712262</v>
+        <v>0.0001930273429024965</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.0008643317851237953</v>
+        <v>3.720131280715577e-05</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.0001737738639349118</v>
+        <v>5.887986480956897e-05</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.0005327442777343094</v>
+        <v>0.001372258877381682</v>
       </c>
       <c r="EZ13" t="n">
-        <v>9.918215801008046e-05</v>
+        <v>0.0002077831159112975</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.0001868357940111309</v>
+        <v>0.0002091416972689331</v>
       </c>
       <c r="FB13" t="n">
-        <v>9.251331357518211e-05</v>
+        <v>0.0001862488425103948</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0001941703085321933</v>
+        <v>0.0003156484162900597</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.0002932593051809818</v>
+        <v>7.667405589018017e-05</v>
       </c>
       <c r="FE13" t="n">
-        <v>5.282607162371278e-05</v>
+        <v>2.687788764887955e-05</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.0001680937421042472</v>
+        <v>0.0002568986092228442</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.0003446410410106182</v>
+        <v>0.0002236996369902045</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.0002454308851156384</v>
+        <v>0.00057367910631001</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.0001607360027264804</v>
+        <v>0.0005020963144488633</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0003151755954604596</v>
+        <v>0.0006228023557923734</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.0006070555537007749</v>
+        <v>0.0001071522274287418</v>
       </c>
       <c r="FL13" t="n">
-        <v>8.220413292292506e-05</v>
+        <v>8.792013977654278e-05</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.000309436465613544</v>
+        <v>0.0002561768342275172</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.000168986662174575</v>
+        <v>0.0001245388411916792</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.0004024838854093105</v>
+        <v>0.0006071703392080963</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.0003062065807171166</v>
+        <v>0.0001182805208372883</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.0004432300920598209</v>
+        <v>0.0006957784062251449</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.0004655091906897724</v>
+        <v>9.232029697159305e-05</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.0001429999829269946</v>
+        <v>0.000486258213641122</v>
       </c>
       <c r="FT13" t="n">
-        <v>9.413560474058613e-05</v>
+        <v>0.0007696507964283228</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.0006545752985402942</v>
+        <v>0.0004281176079530269</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.0001778381993062794</v>
+        <v>4.031222488265485e-05</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.0007341532618738711</v>
+        <v>0.0005870815366506577</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.0003576233284547925</v>
+        <v>0.000679856981150806</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.0003320243558846414</v>
+        <v>0.0001875137677416205</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.0001905409153550863</v>
+        <v>0.0007742403540760279</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.0001745418703649193</v>
+        <v>0.0002192135143559426</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.0001764562912285328</v>
+        <v>0.0001344671036349609</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.0001549720327602699</v>
+        <v>0.000743507465813309</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.0005348482518456876</v>
+        <v>8.576922118663788e-05</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.0007659352850168943</v>
+        <v>0.0002112034271704033</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0006436946569010615</v>
+        <v>0.0004867639509029686</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.0002628852962516248</v>
+        <v>0.0003200337814632803</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.005096462089568377</v>
+        <v>0.0005659094313159585</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01452082488685846</v>
+        <v>0.0008750189444981515</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0009257447673007846</v>
+        <v>0.0002229841193184257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.001674993894994259</v>
+        <v>0.0002377345226705074</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000941739184781909</v>
+        <v>0.0005299526965245605</v>
       </c>
       <c r="F14" t="n">
-        <v>0.006340477615594864</v>
+        <v>0.0003415928513277322</v>
       </c>
       <c r="G14" t="n">
-        <v>0.003392074722796679</v>
+        <v>0.000122475394164212</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0003247043641749769</v>
+        <v>2.659685196704231e-05</v>
       </c>
       <c r="I14" t="n">
-        <v>0.001472840318456292</v>
+        <v>0.0002272700221510604</v>
       </c>
       <c r="J14" t="n">
-        <v>0.004337824881076813</v>
+        <v>0.0002591274678707123</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01023000199347734</v>
+        <v>0.00142419314943254</v>
       </c>
       <c r="L14" t="n">
-        <v>0.001674646977335215</v>
+        <v>0.000161840405780822</v>
       </c>
       <c r="M14" t="n">
-        <v>0.001156921032816172</v>
+        <v>0.0003979541943408549</v>
       </c>
       <c r="N14" t="n">
-        <v>0.002177807502448559</v>
+        <v>0.000774538260884583</v>
       </c>
       <c r="O14" t="n">
-        <v>0.005850270390510559</v>
+        <v>0.0002254135615658015</v>
       </c>
       <c r="P14" t="n">
-        <v>0.002916292985901237</v>
+        <v>0.0001873321161838248</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.002197500318288803</v>
+        <v>0.0005751021672040224</v>
       </c>
       <c r="R14" t="n">
-        <v>0.002765697194263339</v>
+        <v>0.0003779825055971742</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0001545804407214746</v>
+        <v>4.960288788424805e-05</v>
       </c>
       <c r="T14" t="n">
-        <v>0.002264206996187568</v>
+        <v>0.0002827275602612644</v>
       </c>
       <c r="U14" t="n">
-        <v>0.002255890984088182</v>
+        <v>7.066631951602176e-06</v>
       </c>
       <c r="V14" t="n">
-        <v>0.001442861859686673</v>
+        <v>0.000115569680929184</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0009198497282341123</v>
+        <v>8.629980584373698e-05</v>
       </c>
       <c r="X14" t="n">
-        <v>0.004342800937592983</v>
+        <v>0.000104540515167173</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.001115962048061192</v>
+        <v>3.503406333038583e-05</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.000912324758246541</v>
+        <v>1.234675255545881e-05</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.001193194766528904</v>
+        <v>1.969595541595481e-05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.0006436843541450799</v>
+        <v>5.923192657064646e-05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.002828273689374328</v>
+        <v>3.804593507084064e-05</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.002144695026800036</v>
+        <v>0.0002010085590882227</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0005108289187774062</v>
+        <v>0.0003065792261622846</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0007444171933457255</v>
+        <v>0.0002049337490461767</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.001768668531440198</v>
+        <v>5.183770917938091e-05</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.001835268456488848</v>
+        <v>4.03080994146876e-05</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0003322549746371806</v>
+        <v>0.0003304285637568682</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0007006722153164446</v>
+        <v>4.680486745201051e-05</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0008383343229070306</v>
+        <v>0.000104138562164735</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.002536492887884378</v>
+        <v>0.0003746713045984507</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.0005993495578877628</v>
+        <v>9.875450632534921e-05</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.0004095047479495406</v>
+        <v>2.783280433504842e-05</v>
       </c>
       <c r="AO14" t="n">
-        <v>5.092177161714062e-05</v>
+        <v>0.0001183483982458711</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.00248913443647325</v>
+        <v>0.0001559209922561422</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0004866714880336076</v>
+        <v>0.0001358419976895675</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.0005315921152941883</v>
+        <v>0.0003152316494379193</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.001201152219437063</v>
+        <v>2.346641849726439e-05</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.001150363241322339</v>
+        <v>2.048984606517479e-05</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.009288445115089417</v>
+        <v>0.00121845630928874</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.0002213424595538527</v>
+        <v>0.0001440516207367182</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.0002153426175937057</v>
+        <v>0.0001040671777445823</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.002624263055622578</v>
+        <v>0.000228595978114754</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0001763357140589505</v>
+        <v>0.0001148359224316664</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.0003574290312826633</v>
+        <v>1.490161594119854e-07</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.0003757768427021801</v>
+        <v>8.194406109396368e-05</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.001342804986052215</v>
+        <v>7.514277967857197e-06</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.002324854955077171</v>
+        <v>0.0005095291999168694</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.003448975505307317</v>
+        <v>0.0001910826686071232</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.001640480360947549</v>
+        <v>0.0003821872815024108</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.0005370526341721416</v>
+        <v>7.046527025522664e-05</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.002616359619423747</v>
+        <v>0.0003619515337049961</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.004260574001818895</v>
+        <v>9.53463459154591e-05</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.00174826558213681</v>
+        <v>0.0001107941861846484</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.001956050982698798</v>
+        <v>0.0001660088746575639</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.002191226929426193</v>
+        <v>8.237832662416622e-05</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.00123516982421279</v>
+        <v>1.25783626572229e-05</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.001910330378450453</v>
+        <v>0.0001511366135673597</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.0009344645659439266</v>
+        <v>7.380403985735029e-05</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0006811257917433977</v>
+        <v>1.664336195972282e-05</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.001672972459346056</v>
+        <v>0.000283257570117712</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.00350512657314539</v>
+        <v>0.000217811917536892</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.001283998950384557</v>
+        <v>0.0003430547658354044</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.002212209161370993</v>
+        <v>2.022599437623285e-05</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.002255439525470138</v>
+        <v>4.349178925622255e-05</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0003824165905825794</v>
+        <v>0.0001965691189980134</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.006030614953488111</v>
+        <v>0.001039719209074974</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.0008952255011536181</v>
+        <v>0.0001239528355654329</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.002131470246240497</v>
+        <v>0.0001649358164286241</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.001102924579754472</v>
+        <v>0.0001033192384056747</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.002735476708039641</v>
+        <v>7.029904372757301e-05</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.0008960614795796573</v>
+        <v>0.0002093314978992566</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.0006349622271955013</v>
+        <v>0.0001738713763188571</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.0005678322049789131</v>
+        <v>8.318905747728422e-05</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.001242568250745535</v>
+        <v>0.0001010664709610865</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.001829162007197738</v>
+        <v>0.0003025869955308735</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.0003689855802804232</v>
+        <v>8.292954589705914e-05</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.000632608775049448</v>
+        <v>7.862047641538084e-05</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.001404861453920603</v>
+        <v>0.0001021231146296486</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.001540221739560366</v>
+        <v>9.221924847224727e-05</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.0001039346243487671</v>
+        <v>1.015296220430173e-06</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.0003173333825543523</v>
+        <v>1.4636634659837e-07</v>
       </c>
       <c r="CL14" t="n">
-        <v>8.048550807870924e-05</v>
+        <v>6.701204256387427e-05</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.0007563268882222474</v>
+        <v>0.0002507804310880601</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.001541835255920887</v>
+        <v>0.0008104756125248969</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.0009865931933745742</v>
+        <v>6.969462265260518e-05</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.0002072507631964982</v>
+        <v>9.985207725549117e-05</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.003076067892834544</v>
+        <v>0.000167934107594192</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.0004860771005041897</v>
+        <v>0.000195114262169227</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.00154484563972801</v>
+        <v>0.0002185559424106032</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.0009016319527290761</v>
+        <v>0.0003087511286139488</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.001209879177622497</v>
+        <v>3.128972457488999e-05</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0006116810254752636</v>
+        <v>2.04370662686415e-05</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.001975019229575992</v>
+        <v>0.0003110213729087263</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.0004438167670741677</v>
+        <v>7.363912300206721e-05</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0006268426077440381</v>
+        <v>4.365315544418991e-05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.001020957133732736</v>
+        <v>2.955164745799266e-05</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.002842637477442622</v>
+        <v>6.620022031711414e-05</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.0002141429140465334</v>
+        <v>4.676590469898656e-05</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.0002919842081610113</v>
+        <v>8.867871656548232e-06</v>
       </c>
       <c r="DD14" t="n">
-        <v>1.819421595428139e-05</v>
+        <v>5.739543485105969e-05</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.001530601643025875</v>
+        <v>1.317539135925472e-05</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.004220990929752588</v>
+        <v>0.0006650303257629275</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.001858257572166622</v>
+        <v>2.947432221844792e-05</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.002234314568340778</v>
+        <v>3.76324460376054e-05</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.004928800277411938</v>
+        <v>1.85615735972533e-05</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.00473423209041357</v>
+        <v>8.751643326831982e-05</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.000317342288326472</v>
+        <v>4.703506419900805e-06</v>
       </c>
       <c r="DL14" t="n">
-        <v>2.563487214501947e-06</v>
+        <v>0.0001414230646332726</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.002382416510954499</v>
+        <v>0.0001201818959088996</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.0004794494598172605</v>
+        <v>0.0001007057289825752</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.414494520053267e-05</v>
+        <v>0.000142851029522717</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.0006338655948638916</v>
+        <v>1.998290463234298e-05</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.00195042381528765</v>
+        <v>1.61363605002407e-05</v>
       </c>
       <c r="DR14" t="n">
-        <v>1.094619801733643e-05</v>
+        <v>0.0001050885693985038</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.0003616630856413394</v>
+        <v>3.447368726483546e-05</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.0003972184204030782</v>
+        <v>8.428278306382708e-07</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.001256697112694383</v>
+        <v>0.0001021057250909507</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.001971959136426449</v>
+        <v>7.738528438494541e-06</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0006800915580242872</v>
+        <v>0.0002260194451082498</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.001162219210527837</v>
+        <v>0.0003670791629701853</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.001226567663252354</v>
+        <v>5.679234163835645e-06</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.0007439870969392359</v>
+        <v>7.553812611149624e-05</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.0003576047893147916</v>
+        <v>0.0001161861582659185</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.00253986893221736</v>
+        <v>9.051247616298497e-06</v>
       </c>
       <c r="EC14" t="n">
-        <v>6.668528658337891e-05</v>
+        <v>3.378827386768535e-05</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.0007867139647714794</v>
+        <v>2.405310442554764e-05</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.001415924169123173</v>
+        <v>0.0001714384852675721</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.0001333153049927205</v>
+        <v>3.379257395863533e-05</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.0005641237366944551</v>
+        <v>1.160028114099987e-05</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.000407014274969697</v>
+        <v>2.040634717559442e-05</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.001468521310016513</v>
+        <v>0.000109049811726436</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.001137910527177155</v>
+        <v>1.76913345057983e-05</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.003508308669552207</v>
+        <v>0.0001589564781170338</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.0004830615362152457</v>
+        <v>6.779566319892183e-06</v>
       </c>
       <c r="EM14" t="n">
-        <v>4.760501178679988e-05</v>
+        <v>1.896064713946544e-05</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.0002444314595777541</v>
+        <v>7.765883492538705e-05</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.0005322230281308293</v>
+        <v>0.0001759949664119631</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.001976479310542345</v>
+        <v>4.682772851083428e-05</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.0003987998061347753</v>
+        <v>8.617564162705094e-05</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.0009628940606489778</v>
+        <v>0.0001137630897574127</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.00125376577489078</v>
+        <v>0.000247945892624557</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.00365735124796629</v>
+        <v>7.142545655369759e-06</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.000104966398794204</v>
+        <v>0.0001187902234960347</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.002013314748182893</v>
+        <v>3.032619861187413e-05</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.0009072042885236442</v>
+        <v>5.884217171114869e-05</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.0008201942546293139</v>
+        <v>6.905773625476286e-05</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.002275896025821567</v>
+        <v>0.0003842873265966773</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.0003638849884737283</v>
+        <v>6.419247802114114e-05</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.0008555224630981684</v>
+        <v>5.697944652638398e-05</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.001872364897280931</v>
+        <v>2.363514067837968e-05</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.002296597231179476</v>
+        <v>6.877161649754271e-05</v>
       </c>
       <c r="FD14" t="n">
-        <v>9.906268678605556e-05</v>
+        <v>1.956561754923314e-05</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.0002030163304880261</v>
+        <v>2.875603786378633e-05</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.0002601180167403072</v>
+        <v>9.825445886235684e-05</v>
       </c>
       <c r="FG14" t="n">
-        <v>4.1089893784374e-05</v>
+        <v>2.885959111154079e-05</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.000905168941244483</v>
+        <v>0.0002080910635413602</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.0001835149305406958</v>
+        <v>2.201545066782273e-05</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.001673851627856493</v>
+        <v>0.0001396143634337932</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.001387950265780091</v>
+        <v>0.000336798868374899</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.001385065610520542</v>
+        <v>6.188053521327674e-05</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.001567155006341636</v>
+        <v>8.993859228212386e-05</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.0004149394808337092</v>
+        <v>0.0002268238895339891</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0008589130593463778</v>
+        <v>5.676130967913195e-05</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.001662649912759662</v>
+        <v>5.022144614486024e-05</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.003932030405849218</v>
+        <v>2.32042875722982e-05</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.00126069167163223</v>
+        <v>3.482362808426842e-05</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.002149239415302873</v>
+        <v>0.000145848243846558</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.000188711826922372</v>
+        <v>0.001079610083252192</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0007708329358138144</v>
+        <v>0.0001647502358537167</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.0007451046258211136</v>
+        <v>8.40922148199752e-05</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.001742690103128552</v>
+        <v>9.168325050268322e-06</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.001231344416737556</v>
+        <v>0.0001529664878034964</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.001220005331560969</v>
+        <v>9.522204345557839e-05</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.001132052508182824</v>
+        <v>0.0002291115961270407</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.0004679912817664444</v>
+        <v>5.947702447883785e-05</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.0008807388367131352</v>
+        <v>0.0002020543324761093</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.007243209518492222</v>
+        <v>0.0002405234408797696</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.001765634515322745</v>
+        <v>0.0002120617136824876</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.005996008403599262</v>
+        <v>0.0001455377787351608</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.000126754748634994</v>
+        <v>0.0001487681438447908</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.00129481207113713</v>
+        <v>3.245545667596161e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5.398706889536697e-06</v>
+        <v>0.2260994911193848</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0001701334986137226</v>
+        <v>0.8281870484352112</v>
       </c>
       <c r="C15" t="n">
-        <v>2.589160430943593e-05</v>
+        <v>0.05392694473266602</v>
       </c>
       <c r="D15" t="n">
-        <v>5.97347752773203e-06</v>
+        <v>0.01955033466219902</v>
       </c>
       <c r="E15" t="n">
-        <v>3.953740088036284e-05</v>
+        <v>0.7017801403999329</v>
       </c>
       <c r="F15" t="n">
-        <v>3.02100415865425e-05</v>
+        <v>0.5383400917053223</v>
       </c>
       <c r="G15" t="n">
-        <v>8.107529720291495e-05</v>
+        <v>0.02743701636791229</v>
       </c>
       <c r="H15" t="n">
-        <v>3.872156867146259e-06</v>
+        <v>0.005519717931747437</v>
       </c>
       <c r="I15" t="n">
-        <v>4.353209988039453e-06</v>
+        <v>0.3326360881328583</v>
       </c>
       <c r="J15" t="n">
-        <v>5.960046109976247e-06</v>
+        <v>0.3511799275875092</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0001316095440415666</v>
+        <v>1.119663119316101</v>
       </c>
       <c r="L15" t="n">
-        <v>1.020063245960046e-05</v>
+        <v>0.1346198618412018</v>
       </c>
       <c r="M15" t="n">
-        <v>6.175755697768182e-05</v>
+        <v>0.2199408113956451</v>
       </c>
       <c r="N15" t="n">
-        <v>3.867164923576638e-05</v>
+        <v>1.057914018630981</v>
       </c>
       <c r="O15" t="n">
-        <v>2.195417255279608e-05</v>
+        <v>0.6749969720840454</v>
       </c>
       <c r="P15" t="n">
-        <v>6.967773515498266e-05</v>
+        <v>0.1535580456256866</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.646612145123072e-05</v>
+        <v>0.3648690283298492</v>
       </c>
       <c r="R15" t="n">
-        <v>6.034300895407796e-06</v>
+        <v>0.4132764637470245</v>
       </c>
       <c r="S15" t="n">
-        <v>5.551737558562309e-06</v>
+        <v>0.2343072295188904</v>
       </c>
       <c r="T15" t="n">
-        <v>4.775061825057492e-05</v>
+        <v>0.3196750283241272</v>
       </c>
       <c r="U15" t="n">
-        <v>6.863966518722009e-06</v>
+        <v>0.03277843073010445</v>
       </c>
       <c r="V15" t="n">
-        <v>2.634279007907026e-05</v>
+        <v>0.1390950828790665</v>
       </c>
       <c r="W15" t="n">
-        <v>4.581758184940554e-05</v>
+        <v>0.06146173179149628</v>
       </c>
       <c r="X15" t="n">
-        <v>2.880063948396128e-05</v>
+        <v>0.1327257454395294</v>
       </c>
       <c r="Y15" t="n">
-        <v>7.004196049820166e-07</v>
+        <v>0.07693527638912201</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.640043956285808e-05</v>
+        <v>0.2659407258033752</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.679835107410327e-06</v>
+        <v>0.06737304478883743</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.596399826870766e-05</v>
+        <v>0.3684146404266357</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.851551082334481e-05</v>
+        <v>0.0781840980052948</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.009042898658663e-05</v>
+        <v>0.1573654413223267</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.225923824677011e-06</v>
+        <v>0.09885390102863312</v>
       </c>
       <c r="AF15" t="n">
-        <v>3.997187377535738e-06</v>
+        <v>0.442432165145874</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.853098001447506e-05</v>
+        <v>0.3136702477931976</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.783665197763185e-07</v>
+        <v>0.07389505952596664</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.278834345925134e-06</v>
+        <v>0.3703822493553162</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2.591552402009256e-06</v>
+        <v>0.04087924212217331</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.217720611952245e-05</v>
+        <v>0.2045647501945496</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.081664504454238e-05</v>
+        <v>0.3510442078113556</v>
       </c>
       <c r="AM15" t="n">
-        <v>2.40712165577861e-06</v>
+        <v>0.0760224312543869</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.520090154372156e-05</v>
+        <v>0.01743809133768082</v>
       </c>
       <c r="AO15" t="n">
-        <v>6.966692126297858e-06</v>
+        <v>0.08269133418798447</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.546121893625241e-05</v>
+        <v>0.08977679908275604</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.663322321604937e-06</v>
+        <v>0.03445570915937424</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.626734956516884e-06</v>
+        <v>0.3528801798820496</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.745593171013752e-06</v>
+        <v>0.04229339584708214</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.727833089011256e-05</v>
+        <v>0.2417357861995697</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.0001280023425351828</v>
+        <v>1.132926106452942</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.610647586858249e-06</v>
+        <v>0.03446590900421143</v>
       </c>
       <c r="AW15" t="n">
-        <v>3.497651778161526e-05</v>
+        <v>0.1242323368787766</v>
       </c>
       <c r="AX15" t="n">
-        <v>8.343131412402727e-06</v>
+        <v>0.2464496493339539</v>
       </c>
       <c r="AY15" t="n">
-        <v>2.138652234862093e-05</v>
+        <v>0.4765160083770752</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.208235623082146e-05</v>
+        <v>0.04441655054688454</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.896545993280597e-06</v>
+        <v>0.02573633939027786</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.118751348869409e-06</v>
+        <v>0.1179349645972252</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.854059286823031e-06</v>
+        <v>0.05458240211009979</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.063760909251869e-05</v>
+        <v>0.3583347797393799</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.082049079239368e-05</v>
+        <v>0.04149875789880753</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.691468969511334e-05</v>
+        <v>0.01344310492277145</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.117909414460883e-05</v>
+        <v>0.2443744689226151</v>
       </c>
       <c r="BH15" t="n">
-        <v>1.473100928706117e-05</v>
+        <v>0.1561374366283417</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.142011726391502e-05</v>
+        <v>0.1120516508817673</v>
       </c>
       <c r="BJ15" t="n">
-        <v>2.311714524694253e-06</v>
+        <v>0.1004181355237961</v>
       </c>
       <c r="BK15" t="n">
-        <v>1.149401850852882e-05</v>
+        <v>0.02772320806980133</v>
       </c>
       <c r="BL15" t="n">
-        <v>9.660508112574462e-06</v>
+        <v>0.05991809070110321</v>
       </c>
       <c r="BM15" t="n">
-        <v>3.921624374925159e-05</v>
+        <v>0.1498366743326187</v>
       </c>
       <c r="BN15" t="n">
-        <v>2.557226616772823e-05</v>
+        <v>0.05330178886651993</v>
       </c>
       <c r="BO15" t="n">
-        <v>2.281614251842257e-05</v>
+        <v>0.1730035990476608</v>
       </c>
       <c r="BP15" t="n">
-        <v>6.241426308406517e-05</v>
+        <v>0.4093134105205536</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.409505784977227e-05</v>
+        <v>0.3321793377399445</v>
       </c>
       <c r="BR15" t="n">
-        <v>7.12264773028437e-06</v>
+        <v>0.08115030080080032</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.359271118417382e-05</v>
+        <v>0.07274927198886871</v>
       </c>
       <c r="BT15" t="n">
-        <v>3.147225015709409e-06</v>
+        <v>0.08213073015213013</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.177735884994036e-05</v>
+        <v>0.2812659442424774</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.026444316376001e-05</v>
+        <v>0.9504214525222778</v>
       </c>
       <c r="BW15" t="n">
-        <v>2.834707265719771e-05</v>
+        <v>0.1966835856437683</v>
       </c>
       <c r="BX15" t="n">
-        <v>2.96578582492657e-05</v>
+        <v>0.270143985748291</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.138834795710864e-05</v>
+        <v>0.1681308597326279</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.376735028519761e-05</v>
+        <v>0.2572726309299469</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.785390850272961e-05</v>
+        <v>0.1228465214371681</v>
       </c>
       <c r="CB15" t="n">
-        <v>1.688887277850881e-05</v>
+        <v>0.003262355923652649</v>
       </c>
       <c r="CC15" t="n">
-        <v>1.327678091911366e-07</v>
+        <v>0.15227110683918</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.959612851962447e-06</v>
+        <v>0.156419575214386</v>
       </c>
       <c r="CE15" t="n">
-        <v>3.449357609497383e-05</v>
+        <v>0.3609298467636108</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.386523192399181e-06</v>
+        <v>0.02368327975273132</v>
       </c>
       <c r="CG15" t="n">
-        <v>9.015521754918154e-06</v>
+        <v>0.100988358259201</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.646201212679443e-06</v>
+        <v>0.2434675991535187</v>
       </c>
       <c r="CI15" t="n">
-        <v>3.402836910026963e-06</v>
+        <v>0.1685074716806412</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.373212671751389e-05</v>
+        <v>0.02487456426024437</v>
       </c>
       <c r="CK15" t="n">
-        <v>2.201593360950937e-06</v>
+        <v>0.0754607692360878</v>
       </c>
       <c r="CL15" t="n">
-        <v>6.812284709667438e-07</v>
+        <v>0.0667140930891037</v>
       </c>
       <c r="CM15" t="n">
-        <v>3.954713611165062e-05</v>
+        <v>0.1027891933917999</v>
       </c>
       <c r="CN15" t="n">
-        <v>5.562650767387822e-05</v>
+        <v>0.6524562835693359</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.298072675126605e-06</v>
+        <v>0.04968447238206863</v>
       </c>
       <c r="CP15" t="n">
-        <v>4.907263246423099e-06</v>
+        <v>0.4509775638580322</v>
       </c>
       <c r="CQ15" t="n">
-        <v>6.481770833488554e-05</v>
+        <v>0.09095557034015656</v>
       </c>
       <c r="CR15" t="n">
-        <v>3.48960020346567e-05</v>
+        <v>0.06504438072443008</v>
       </c>
       <c r="CS15" t="n">
-        <v>1.309306207986083e-05</v>
+        <v>0.06835172325372696</v>
       </c>
       <c r="CT15" t="n">
-        <v>9.436894288228359e-06</v>
+        <v>0.1303896009922028</v>
       </c>
       <c r="CU15" t="n">
-        <v>2.528785444155801e-05</v>
+        <v>0.01237417384982109</v>
       </c>
       <c r="CV15" t="n">
-        <v>7.620062206115108e-06</v>
+        <v>0.0816868469119072</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.67479208559962e-05</v>
+        <v>0.3234639465808868</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.108016567741288e-05</v>
+        <v>0.009630724787712097</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.643181894905865e-05</v>
+        <v>0.1766014248132706</v>
       </c>
       <c r="CZ15" t="n">
-        <v>4.214321904782992e-07</v>
+        <v>0.2111124396324158</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.519215513530071e-06</v>
+        <v>0.1879944205284119</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.160779629572062e-05</v>
+        <v>0.04421724379062653</v>
       </c>
       <c r="DC15" t="n">
-        <v>3.207506551916595e-06</v>
+        <v>0.1095681563019753</v>
       </c>
       <c r="DD15" t="n">
-        <v>1.276031298402813e-06</v>
+        <v>0.08016057312488556</v>
       </c>
       <c r="DE15" t="n">
-        <v>1.640818481973838e-05</v>
+        <v>0.01425917446613312</v>
       </c>
       <c r="DF15" t="n">
-        <v>9.595372102921829e-05</v>
+        <v>0.4607200026512146</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.943810795841273e-05</v>
+        <v>0.00303986668586731</v>
       </c>
       <c r="DH15" t="n">
-        <v>1.878701004898176e-05</v>
+        <v>0.08490445464849472</v>
       </c>
       <c r="DI15" t="n">
-        <v>1.936489024956245e-05</v>
+        <v>0.158826157450676</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.270353979838546e-05</v>
+        <v>0.2204921692609787</v>
       </c>
       <c r="DK15" t="n">
-        <v>1.422186869604047e-05</v>
+        <v>0.1031866744160652</v>
       </c>
       <c r="DL15" t="n">
-        <v>1.113202324631857e-05</v>
+        <v>0.2647860646247864</v>
       </c>
       <c r="DM15" t="n">
-        <v>2.498074718459975e-05</v>
+        <v>0.07464951276779175</v>
       </c>
       <c r="DN15" t="n">
-        <v>9.043717000167817e-06</v>
+        <v>0.1190391182899475</v>
       </c>
       <c r="DO15" t="n">
-        <v>3.346415178384632e-05</v>
+        <v>0.1441310346126556</v>
       </c>
       <c r="DP15" t="n">
-        <v>8.788509148871526e-06</v>
+        <v>0.03702143952250481</v>
       </c>
       <c r="DQ15" t="n">
-        <v>1.063553827407304e-05</v>
+        <v>0.1771582961082458</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.949869657546515e-06</v>
+        <v>0.2722383737564087</v>
       </c>
       <c r="DS15" t="n">
-        <v>9.174596925731748e-06</v>
+        <v>0.1934257000684738</v>
       </c>
       <c r="DT15" t="n">
-        <v>1.840869481384289e-05</v>
+        <v>0.09331168234348297</v>
       </c>
       <c r="DU15" t="n">
-        <v>7.892111170804128e-06</v>
+        <v>0.2339181751012802</v>
       </c>
       <c r="DV15" t="n">
-        <v>8.793030247034039e-06</v>
+        <v>0.1651138812303543</v>
       </c>
       <c r="DW15" t="n">
-        <v>8.759634511079639e-07</v>
+        <v>0.1657560467720032</v>
       </c>
       <c r="DX15" t="n">
-        <v>2.052308991551399e-05</v>
+        <v>0.3059813380241394</v>
       </c>
       <c r="DY15" t="n">
-        <v>5.000496912543895e-06</v>
+        <v>0.08128936588764191</v>
       </c>
       <c r="DZ15" t="n">
-        <v>1.439155767002376e-05</v>
+        <v>0.04586588591337204</v>
       </c>
       <c r="EA15" t="n">
-        <v>2.786322511383332e-05</v>
+        <v>0.1998011916875839</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.596896618138999e-05</v>
+        <v>0.1482878178358078</v>
       </c>
       <c r="EC15" t="n">
-        <v>6.386061613739002e-06</v>
+        <v>0.0459560826420784</v>
       </c>
       <c r="ED15" t="n">
-        <v>1.667302285568439e-06</v>
+        <v>0.004654122516512871</v>
       </c>
       <c r="EE15" t="n">
-        <v>4.367196197563317e-06</v>
+        <v>0.452820748090744</v>
       </c>
       <c r="EF15" t="n">
-        <v>1.61407733685337e-05</v>
+        <v>0.01374697685241699</v>
       </c>
       <c r="EG15" t="n">
-        <v>9.502798093308229e-06</v>
+        <v>0.1211285889148712</v>
       </c>
       <c r="EH15" t="n">
-        <v>2.949432428067666e-06</v>
+        <v>0.07441487908363342</v>
       </c>
       <c r="EI15" t="n">
-        <v>3.527346780174412e-05</v>
+        <v>0.07480394095182419</v>
       </c>
       <c r="EJ15" t="n">
-        <v>8.819518370728474e-06</v>
+        <v>0.08963429182767868</v>
       </c>
       <c r="EK15" t="n">
-        <v>3.343410298839444e-06</v>
+        <v>0.2313106954097748</v>
       </c>
       <c r="EL15" t="n">
-        <v>1.01830610219622e-05</v>
+        <v>0.0760624036192894</v>
       </c>
       <c r="EM15" t="n">
-        <v>6.992698899921379e-07</v>
+        <v>0.08878844976425171</v>
       </c>
       <c r="EN15" t="n">
-        <v>6.464650255111337e-07</v>
+        <v>0.07914168387651443</v>
       </c>
       <c r="EO15" t="n">
-        <v>1.651973252592143e-05</v>
+        <v>0.1007655635476112</v>
       </c>
       <c r="EP15" t="n">
-        <v>6.166460480017122e-06</v>
+        <v>0.209413930773735</v>
       </c>
       <c r="EQ15" t="n">
-        <v>1.742235144774895e-05</v>
+        <v>0.04169151932001114</v>
       </c>
       <c r="ER15" t="n">
-        <v>1.575316673552152e-05</v>
+        <v>0.2431246638298035</v>
       </c>
       <c r="ES15" t="n">
-        <v>1.116227576858364e-05</v>
+        <v>0.04311555996537209</v>
       </c>
       <c r="ET15" t="n">
-        <v>2.656683136592619e-06</v>
+        <v>0.07577234506607056</v>
       </c>
       <c r="EU15" t="n">
-        <v>4.176684342382941e-06</v>
+        <v>0.05799388885498047</v>
       </c>
       <c r="EV15" t="n">
-        <v>1.480334617554036e-06</v>
+        <v>0.08423983305692673</v>
       </c>
       <c r="EW15" t="n">
-        <v>2.000642325583613e-06</v>
+        <v>0.01421879045665264</v>
       </c>
       <c r="EX15" t="n">
-        <v>7.670948434679303e-06</v>
+        <v>0.1320495158433914</v>
       </c>
       <c r="EY15" t="n">
-        <v>2.735355337790679e-05</v>
+        <v>0.3856686949729919</v>
       </c>
       <c r="EZ15" t="n">
-        <v>4.761916898132768e-06</v>
+        <v>0.005964754149317741</v>
       </c>
       <c r="FA15" t="n">
-        <v>1.154731580754742e-05</v>
+        <v>0.1317620277404785</v>
       </c>
       <c r="FB15" t="n">
-        <v>2.18358604797686e-06</v>
+        <v>0.1631848812103271</v>
       </c>
       <c r="FC15" t="n">
-        <v>6.509535069199046e-06</v>
+        <v>0.1405971944332123</v>
       </c>
       <c r="FD15" t="n">
-        <v>1.224784136866219e-05</v>
+        <v>0.02955600619316101</v>
       </c>
       <c r="FE15" t="n">
-        <v>6.595845661649946e-06</v>
+        <v>0.1542651653289795</v>
       </c>
       <c r="FF15" t="n">
-        <v>5.355789198802086e-07</v>
+        <v>0.134689062833786</v>
       </c>
       <c r="FG15" t="n">
-        <v>9.506155947747175e-06</v>
+        <v>0.06965547800064087</v>
       </c>
       <c r="FH15" t="n">
-        <v>3.160843334626406e-06</v>
+        <v>0.1546080261468887</v>
       </c>
       <c r="FI15" t="n">
-        <v>4.515286491368897e-06</v>
+        <v>0.04193835332989693</v>
       </c>
       <c r="FJ15" t="n">
-        <v>1.14582526293816e-05</v>
+        <v>0.3309506773948669</v>
       </c>
       <c r="FK15" t="n">
-        <v>3.039612420252524e-05</v>
+        <v>0.0183066613972187</v>
       </c>
       <c r="FL15" t="n">
-        <v>1.986770439543761e-05</v>
+        <v>0.07834832370281219</v>
       </c>
       <c r="FM15" t="n">
-        <v>7.340208867390174e-06</v>
+        <v>0.2010427862405777</v>
       </c>
       <c r="FN15" t="n">
-        <v>1.026860081765335e-05</v>
+        <v>0.07025653123855591</v>
       </c>
       <c r="FO15" t="n">
-        <v>4.279809218132868e-06</v>
+        <v>0.06691312789916992</v>
       </c>
       <c r="FP15" t="n">
-        <v>1.188237183669116e-05</v>
+        <v>0.1524829268455505</v>
       </c>
       <c r="FQ15" t="n">
-        <v>2.219252928625792e-05</v>
+        <v>0.1231459826231003</v>
       </c>
       <c r="FR15" t="n">
-        <v>1.195840013679117e-05</v>
+        <v>0.1219900697469711</v>
       </c>
       <c r="FS15" t="n">
-        <v>3.646427285275422e-05</v>
+        <v>0.4098575711250305</v>
       </c>
       <c r="FT15" t="n">
-        <v>7.653775355720427e-06</v>
+        <v>0.1721003502607346</v>
       </c>
       <c r="FU15" t="n">
-        <v>1.062970795828733e-06</v>
+        <v>0.1285487413406372</v>
       </c>
       <c r="FV15" t="n">
-        <v>2.879111343645491e-05</v>
+        <v>0.09353923797607422</v>
       </c>
       <c r="FW15" t="n">
-        <v>3.25471737596672e-05</v>
+        <v>0.2217815965414047</v>
       </c>
       <c r="FX15" t="n">
-        <v>8.425331543548964e-08</v>
+        <v>0.1517863571643829</v>
       </c>
       <c r="FY15" t="n">
-        <v>7.04646845406387e-06</v>
+        <v>0.2774087488651276</v>
       </c>
       <c r="FZ15" t="n">
-        <v>2.096716161759105e-05</v>
+        <v>0.1690239310264587</v>
       </c>
       <c r="GA15" t="n">
-        <v>1.667060132604092e-05</v>
+        <v>0.0723181739449501</v>
       </c>
       <c r="GB15" t="n">
-        <v>2.046216832241043e-05</v>
+        <v>0.1274771690368652</v>
       </c>
       <c r="GC15" t="n">
-        <v>8.850494850776158e-06</v>
+        <v>0.1062582433223724</v>
       </c>
       <c r="GD15" t="n">
-        <v>1.391830664942972e-05</v>
+        <v>0.3374999463558197</v>
       </c>
       <c r="GE15" t="n">
-        <v>9.219809726346284e-06</v>
+        <v>0.1183241158723831</v>
       </c>
       <c r="GF15" t="n">
-        <v>2.388520806562155e-05</v>
+        <v>0.1339783221483231</v>
       </c>
       <c r="GG15" t="n">
-        <v>2.994071337525384e-06</v>
+        <v>0.1930817365646362</v>
       </c>
     </row>
     <row r="16">
@@ -9534,571 +9534,571 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.003691310063004494</v>
+        <v>0.009833017364144325</v>
       </c>
       <c r="B17" t="n">
-        <v>0.03285301849246025</v>
+        <v>0.08299810439348221</v>
       </c>
       <c r="C17" t="n">
-        <v>0.009637106209993362</v>
+        <v>0.03686355426907539</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00437565054744482</v>
+        <v>0.03521646559238434</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06435952335596085</v>
+        <v>0.04870659485459328</v>
       </c>
       <c r="F17" t="n">
-        <v>0.009351183660328388</v>
+        <v>0.05391603708267212</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0246356800198555</v>
+        <v>0.002619946375489235</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01915368624031544</v>
+        <v>0.05632400512695312</v>
       </c>
       <c r="I17" t="n">
-        <v>0.009005802683532238</v>
+        <v>0.005705167539417744</v>
       </c>
       <c r="J17" t="n">
-        <v>0.009018959477543831</v>
+        <v>0.0179845504462719</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0187781285494566</v>
+        <v>0.08778173476457596</v>
       </c>
       <c r="L17" t="n">
-        <v>0.004888697527348995</v>
+        <v>0.03177230432629585</v>
       </c>
       <c r="M17" t="n">
-        <v>0.003046846017241478</v>
+        <v>0.07385306805372238</v>
       </c>
       <c r="N17" t="n">
-        <v>0.05590394511818886</v>
+        <v>0.07488519698381424</v>
       </c>
       <c r="O17" t="n">
-        <v>0.006198430433869362</v>
+        <v>0.03007200360298157</v>
       </c>
       <c r="P17" t="n">
-        <v>0.01239414885640144</v>
+        <v>0.002636499237269163</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.02138173580169678</v>
+        <v>0.03737520053982735</v>
       </c>
       <c r="R17" t="n">
-        <v>0.01504057459533215</v>
+        <v>0.005611893255263567</v>
       </c>
       <c r="S17" t="n">
-        <v>0.005156927742063999</v>
+        <v>0.009568352252244949</v>
       </c>
       <c r="T17" t="n">
-        <v>0.002546505304053426</v>
+        <v>0.01514619030058384</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0045714913867414</v>
+        <v>0.004445286002010107</v>
       </c>
       <c r="V17" t="n">
-        <v>0.009894684888422489</v>
+        <v>0.01610637083649635</v>
       </c>
       <c r="W17" t="n">
-        <v>0.02680009044706821</v>
+        <v>0.0003350600600242615</v>
       </c>
       <c r="X17" t="n">
-        <v>0.004868544638156891</v>
+        <v>0.0245021041482687</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.009719434194266796</v>
+        <v>0.008292598649859428</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.003615378635004163</v>
+        <v>0.006935395300388336</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0004398580640554428</v>
+        <v>0.01725276745855808</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.00203522783704102</v>
+        <v>0.01409054268151522</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.007363473065197468</v>
+        <v>0.01894604600965977</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.0009932585526257753</v>
+        <v>0.01422743313014507</v>
       </c>
       <c r="AE17" t="n">
-        <v>0.01017113402485847</v>
+        <v>0.003631815779954195</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.007476140279322863</v>
+        <v>0.03620696440339088</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.006316661834716797</v>
+        <v>0.03480081260204315</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.00150047882925719</v>
+        <v>0.009464241564273834</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.004303152672946453</v>
+        <v>0.04313690215349197</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.005069179460406303</v>
+        <v>0.006669532507658005</v>
       </c>
       <c r="AK17" t="n">
-        <v>0.001620264491066337</v>
+        <v>0.00388882914558053</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.01499222312122583</v>
+        <v>0.03789063543081284</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.006326977163553238</v>
+        <v>0.007594539783895016</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.01360508985817432</v>
+        <v>0.001050589140504599</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.002340633422136307</v>
+        <v>0.06130756437778473</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.008510024286806583</v>
+        <v>0.01704290695488453</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.006050919182598591</v>
+        <v>0.01478375680744648</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.0006069489754736423</v>
+        <v>0.02316385880112648</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.0001997650979319587</v>
+        <v>0.006365567445755005</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.0004948361311107874</v>
+        <v>0.01181953214108944</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.02167940884828568</v>
+        <v>0.08526872098445892</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.005355491302907467</v>
+        <v>0.009273359552025795</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.00832027941942215</v>
+        <v>0.01862164959311485</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.03962846100330353</v>
+        <v>0.01696666143834591</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.01033537741750479</v>
+        <v>0.03101912513375282</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.009901511482894421</v>
+        <v>0.01062591001391411</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.006248476915061474</v>
+        <v>0.008805877529084682</v>
       </c>
       <c r="BB17" t="n">
-        <v>0.005526914726942778</v>
+        <v>0.01423002500087023</v>
       </c>
       <c r="BC17" t="n">
-        <v>0.002285311231389642</v>
+        <v>0.01022606901824474</v>
       </c>
       <c r="BD17" t="n">
-        <v>0.0004603606648743153</v>
+        <v>0.043363306671381</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.01264334563165903</v>
+        <v>0.0423211008310318</v>
       </c>
       <c r="BF17" t="n">
-        <v>0.02280539087951183</v>
+        <v>0.0169841330498457</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.04522626847028732</v>
+        <v>0.05479423701763153</v>
       </c>
       <c r="BH17" t="n">
-        <v>0.0004514867905527353</v>
+        <v>0.005110902711749077</v>
       </c>
       <c r="BI17" t="n">
-        <v>0.00770110497251153</v>
+        <v>0.00397187564522028</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.01685077138245106</v>
+        <v>0.01157420501112938</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.003678599605336785</v>
+        <v>0.003523292951285839</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.008036239072680473</v>
+        <v>0.004995630122721195</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.01008350774645805</v>
+        <v>0.01537776552140713</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.009946098551154137</v>
+        <v>0.001474320888519287</v>
       </c>
       <c r="BO17" t="n">
-        <v>0.01311728917062283</v>
+        <v>0.003385287011042237</v>
       </c>
       <c r="BP17" t="n">
-        <v>0.01370138954371214</v>
+        <v>0.00630817748606205</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0.006074828561395407</v>
+        <v>0.002345444168895483</v>
       </c>
       <c r="BR17" t="n">
-        <v>0.01077057048678398</v>
+        <v>0.007127712480723858</v>
       </c>
       <c r="BS17" t="n">
-        <v>0.01346674375236034</v>
+        <v>0.02069767937064171</v>
       </c>
       <c r="BT17" t="n">
-        <v>0.0005680351750925183</v>
+        <v>0.01169918570667505</v>
       </c>
       <c r="BU17" t="n">
-        <v>0.003080518217757344</v>
+        <v>0.008289679884910583</v>
       </c>
       <c r="BV17" t="n">
-        <v>0.02176864817738533</v>
+        <v>0.05841569602489471</v>
       </c>
       <c r="BW17" t="n">
-        <v>0.004500612150877714</v>
+        <v>0.01211983058601618</v>
       </c>
       <c r="BX17" t="n">
-        <v>0.000400289602112025</v>
+        <v>0.03725704550743103</v>
       </c>
       <c r="BY17" t="n">
-        <v>0.02357691898941994</v>
+        <v>0.01284909807145596</v>
       </c>
       <c r="BZ17" t="n">
-        <v>0.005284410435706377</v>
+        <v>0.02472180873155594</v>
       </c>
       <c r="CA17" t="n">
-        <v>0.004810811951756477</v>
+        <v>0.008267149329185486</v>
       </c>
       <c r="CB17" t="n">
-        <v>0.0001715529360808432</v>
+        <v>0.004947818350046873</v>
       </c>
       <c r="CC17" t="n">
-        <v>0.004042143933475018</v>
+        <v>0.009549472481012344</v>
       </c>
       <c r="CD17" t="n">
-        <v>0.002016685903072357</v>
+        <v>0.008990819565951824</v>
       </c>
       <c r="CE17" t="n">
-        <v>0.002192578511312604</v>
+        <v>0.04011350125074387</v>
       </c>
       <c r="CF17" t="n">
-        <v>0.007467273157089949</v>
+        <v>0.01033624447882175</v>
       </c>
       <c r="CG17" t="n">
-        <v>0.007999761961400509</v>
+        <v>0.01432418078184128</v>
       </c>
       <c r="CH17" t="n">
-        <v>0.008814679458737373</v>
+        <v>0.002844530623406172</v>
       </c>
       <c r="CI17" t="n">
-        <v>0.00186417973600328</v>
+        <v>0.01243502926081419</v>
       </c>
       <c r="CJ17" t="n">
-        <v>0.000947197200730443</v>
+        <v>0.004548699595034122</v>
       </c>
       <c r="CK17" t="n">
-        <v>0.0004857349849771708</v>
+        <v>0.009692331776022911</v>
       </c>
       <c r="CL17" t="n">
-        <v>0.002561022527515888</v>
+        <v>0.001460521365515888</v>
       </c>
       <c r="CM17" t="n">
-        <v>0.0003640632494352758</v>
+        <v>0.0172383151948452</v>
       </c>
       <c r="CN17" t="n">
-        <v>0.007351938169449568</v>
+        <v>0.03780249133706093</v>
       </c>
       <c r="CO17" t="n">
-        <v>0.002423223108053207</v>
+        <v>0.04858750104904175</v>
       </c>
       <c r="CP17" t="n">
-        <v>0.03200944885611534</v>
+        <v>0.06478752940893173</v>
       </c>
       <c r="CQ17" t="n">
-        <v>0.03149474784731865</v>
+        <v>0.03757472336292267</v>
       </c>
       <c r="CR17" t="n">
-        <v>0.005909531377255917</v>
+        <v>0.003053738735616207</v>
       </c>
       <c r="CS17" t="n">
-        <v>0.0162998866289854</v>
+        <v>0.009345851838588715</v>
       </c>
       <c r="CT17" t="n">
-        <v>0.002006105612963438</v>
+        <v>0.005615283269435167</v>
       </c>
       <c r="CU17" t="n">
-        <v>0.006170055363327265</v>
+        <v>0.01144618727266788</v>
       </c>
       <c r="CV17" t="n">
-        <v>0.002805095165967941</v>
+        <v>0.01260180491954088</v>
       </c>
       <c r="CW17" t="n">
-        <v>0.00083694834029302</v>
+        <v>0.03774196282029152</v>
       </c>
       <c r="CX17" t="n">
-        <v>0.007307462394237518</v>
+        <v>0.01098336558789015</v>
       </c>
       <c r="CY17" t="n">
-        <v>0.003365966491401196</v>
+        <v>0.01879734732210636</v>
       </c>
       <c r="CZ17" t="n">
-        <v>0.009069132618606091</v>
+        <v>0.006624005269259214</v>
       </c>
       <c r="DA17" t="n">
-        <v>0.005127304699271917</v>
+        <v>0.01315332483500242</v>
       </c>
       <c r="DB17" t="n">
-        <v>0.002358099911361933</v>
+        <v>0.003078227629885077</v>
       </c>
       <c r="DC17" t="n">
-        <v>0.0008459843811579049</v>
+        <v>0.006450362503528595</v>
       </c>
       <c r="DD17" t="n">
-        <v>0.004931782372295856</v>
+        <v>0.006205954123288393</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.001779540674760938</v>
+        <v>0.000914459815248847</v>
       </c>
       <c r="DF17" t="n">
-        <v>0.01234076917171478</v>
+        <v>0.01977795362472534</v>
       </c>
       <c r="DG17" t="n">
-        <v>0.007075993344187737</v>
+        <v>0.002231958787888288</v>
       </c>
       <c r="DH17" t="n">
-        <v>0.005452126264572144</v>
+        <v>0.03889225423336029</v>
       </c>
       <c r="DI17" t="n">
-        <v>0.03519259765744209</v>
+        <v>0.001706237904727459</v>
       </c>
       <c r="DJ17" t="n">
-        <v>0.008428367786109447</v>
+        <v>0.04411761462688446</v>
       </c>
       <c r="DK17" t="n">
-        <v>0.01414991449564695</v>
+        <v>0.02459700778126717</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.0232841968536377</v>
+        <v>0.04481568560004234</v>
       </c>
       <c r="DM17" t="n">
-        <v>0.00948125496506691</v>
+        <v>0.005155940540134907</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.01007058657705784</v>
+        <v>0.01306522637605667</v>
       </c>
       <c r="DO17" t="n">
-        <v>0.006456479895859957</v>
+        <v>0.02001316472887993</v>
       </c>
       <c r="DP17" t="n">
-        <v>0.01376697141677141</v>
+        <v>0.003284080885350704</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.02502709813416004</v>
+        <v>0.0106909116730094</v>
       </c>
       <c r="DR17" t="n">
-        <v>0.01761998794972897</v>
+        <v>0.0107644023373723</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.0009425271418876946</v>
+        <v>0.01039545051753521</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.003581241006031632</v>
+        <v>7.510045543313026e-05</v>
       </c>
       <c r="DU17" t="n">
-        <v>0.008996397256851196</v>
+        <v>0.02827630937099457</v>
       </c>
       <c r="DV17" t="n">
-        <v>0.001334686297923326</v>
+        <v>0.03117835149168968</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.002968584420159459</v>
+        <v>0.0009821546263992786</v>
       </c>
       <c r="DX17" t="n">
-        <v>0.007684271316975355</v>
+        <v>0.004680950194597244</v>
       </c>
       <c r="DY17" t="n">
-        <v>0.006273928098380566</v>
+        <v>0.02035229094326496</v>
       </c>
       <c r="DZ17" t="n">
-        <v>0.001220782520249486</v>
+        <v>0.002805435564368963</v>
       </c>
       <c r="EA17" t="n">
-        <v>0.003512651892378926</v>
+        <v>0.0207112543284893</v>
       </c>
       <c r="EB17" t="n">
-        <v>0.01178785692900419</v>
+        <v>0.02687314338982105</v>
       </c>
       <c r="EC17" t="n">
-        <v>0.0112916836515069</v>
+        <v>0.01647531427443027</v>
       </c>
       <c r="ED17" t="n">
-        <v>0.0172226894646883</v>
+        <v>0.03520491719245911</v>
       </c>
       <c r="EE17" t="n">
-        <v>0.001450450043193996</v>
+        <v>0.03992676734924316</v>
       </c>
       <c r="EF17" t="n">
-        <v>0.002384645398706198</v>
+        <v>0.01234465278685093</v>
       </c>
       <c r="EG17" t="n">
-        <v>0.001804560655727983</v>
+        <v>0.03189500793814659</v>
       </c>
       <c r="EH17" t="n">
-        <v>0.001847232109867036</v>
+        <v>0.01124631799757481</v>
       </c>
       <c r="EI17" t="n">
-        <v>0.007626327220350504</v>
+        <v>0.003756464691832662</v>
       </c>
       <c r="EJ17" t="n">
-        <v>0.008515843190252781</v>
+        <v>0.01433478109538555</v>
       </c>
       <c r="EK17" t="n">
-        <v>0.001963167684152722</v>
+        <v>0.01911600679159164</v>
       </c>
       <c r="EL17" t="n">
-        <v>0.004535346291959286</v>
+        <v>0.002367237815633416</v>
       </c>
       <c r="EM17" t="n">
-        <v>0.003875192254781723</v>
+        <v>0.00114463665522635</v>
       </c>
       <c r="EN17" t="n">
-        <v>0.004928899928927422</v>
+        <v>0.003351144958287477</v>
       </c>
       <c r="EO17" t="n">
-        <v>0.0005894743953831494</v>
+        <v>0.006561590824276209</v>
       </c>
       <c r="EP17" t="n">
-        <v>0.004094384610652924</v>
+        <v>0.03171578049659729</v>
       </c>
       <c r="EQ17" t="n">
-        <v>0.003815934527665377</v>
+        <v>0.002552955178543925</v>
       </c>
       <c r="ER17" t="n">
-        <v>0.003594171954318881</v>
+        <v>0.01481920201331377</v>
       </c>
       <c r="ES17" t="n">
-        <v>0.002907785354182124</v>
+        <v>0.01636968739330769</v>
       </c>
       <c r="ET17" t="n">
-        <v>0.02003925479948521</v>
+        <v>0.007150815799832344</v>
       </c>
       <c r="EU17" t="n">
-        <v>0.004367796704173088</v>
+        <v>0.0001796456053853035</v>
       </c>
       <c r="EV17" t="n">
-        <v>0.001595492009073496</v>
+        <v>0.01307519152760506</v>
       </c>
       <c r="EW17" t="n">
-        <v>0.001191878225654364</v>
+        <v>0.001909684389829636</v>
       </c>
       <c r="EX17" t="n">
-        <v>0.003702521324157715</v>
+        <v>0.01131446473300457</v>
       </c>
       <c r="EY17" t="n">
-        <v>0.001872071297839284</v>
+        <v>0.04527311772108078</v>
       </c>
       <c r="EZ17" t="n">
-        <v>0.007653862237930298</v>
+        <v>0.01244199555367231</v>
       </c>
       <c r="FA17" t="n">
-        <v>0.006249615922570229</v>
+        <v>0.02495742216706276</v>
       </c>
       <c r="FB17" t="n">
-        <v>0.007100202608853579</v>
+        <v>0.005895795300602913</v>
       </c>
       <c r="FC17" t="n">
-        <v>0.003118427470326424</v>
+        <v>0.01418762933462858</v>
       </c>
       <c r="FD17" t="n">
-        <v>0.0002948454348370433</v>
+        <v>0.00455007515847683</v>
       </c>
       <c r="FE17" t="n">
-        <v>0.003595009446144104</v>
+        <v>0.01304447371512651</v>
       </c>
       <c r="FF17" t="n">
-        <v>0.002809168072417378</v>
+        <v>0.00431374553591013</v>
       </c>
       <c r="FG17" t="n">
-        <v>0.003726283088326454</v>
+        <v>0.008599963039159775</v>
       </c>
       <c r="FH17" t="n">
-        <v>0.02121712081134319</v>
+        <v>0.02786931209266186</v>
       </c>
       <c r="FI17" t="n">
-        <v>0.008365153335034847</v>
+        <v>0.01460436917841434</v>
       </c>
       <c r="FJ17" t="n">
-        <v>0.0008451670873910189</v>
+        <v>0.02744796313345432</v>
       </c>
       <c r="FK17" t="n">
-        <v>0.007234991993755102</v>
+        <v>0.003893828019499779</v>
       </c>
       <c r="FL17" t="n">
-        <v>0.001730120275169611</v>
+        <v>0.01719558425247669</v>
       </c>
       <c r="FM17" t="n">
-        <v>0.009492751210927963</v>
+        <v>0.0009703107643872499</v>
       </c>
       <c r="FN17" t="n">
-        <v>0.005629715044051409</v>
+        <v>0.02262861095368862</v>
       </c>
       <c r="FO17" t="n">
-        <v>0.002147657098248601</v>
+        <v>0.01138278469443321</v>
       </c>
       <c r="FP17" t="n">
-        <v>0.003625574987381697</v>
+        <v>0.02972887642681599</v>
       </c>
       <c r="FQ17" t="n">
-        <v>0.0155944311991334</v>
+        <v>0.05326103791594505</v>
       </c>
       <c r="FR17" t="n">
-        <v>0.005461765453219414</v>
+        <v>0.009180355817079544</v>
       </c>
       <c r="FS17" t="n">
-        <v>0.01572473160922527</v>
+        <v>0.01310100592672825</v>
       </c>
       <c r="FT17" t="n">
-        <v>0.02522667124867439</v>
+        <v>0.01593802124261856</v>
       </c>
       <c r="FU17" t="n">
-        <v>0.003314519533887506</v>
+        <v>0.0374470129609108</v>
       </c>
       <c r="FV17" t="n">
-        <v>0.0154313500970602</v>
+        <v>0.00260786572471261</v>
       </c>
       <c r="FW17" t="n">
-        <v>0.01088814344257116</v>
+        <v>0.002106451895087957</v>
       </c>
       <c r="FX17" t="n">
-        <v>0.004651794675737619</v>
+        <v>0.029932901263237</v>
       </c>
       <c r="FY17" t="n">
-        <v>0.01041767001152039</v>
+        <v>0.005386527627706528</v>
       </c>
       <c r="FZ17" t="n">
-        <v>0.003366722958162427</v>
+        <v>0.0165933221578598</v>
       </c>
       <c r="GA17" t="n">
-        <v>0.01280129700899124</v>
+        <v>0.01743961125612259</v>
       </c>
       <c r="GB17" t="n">
-        <v>0.005668715573847294</v>
+        <v>0.008595027029514313</v>
       </c>
       <c r="GC17" t="n">
-        <v>0.03148693218827248</v>
+        <v>0.0006708800792694092</v>
       </c>
       <c r="GD17" t="n">
-        <v>0.008654342964291573</v>
+        <v>0.008684122003614902</v>
       </c>
       <c r="GE17" t="n">
-        <v>0.004793319385498762</v>
+        <v>0.006519547197967768</v>
       </c>
       <c r="GF17" t="n">
-        <v>0.005207810085266829</v>
+        <v>0.02039607055485249</v>
       </c>
       <c r="GG17" t="n">
-        <v>0.00327953090891242</v>
+        <v>0.002225335687398911</v>
       </c>
     </row>
   </sheetData>
